--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlier\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC83604F-F17F-444A-B4D7-8A1260BEE1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75031AC7-F426-493E-BC1D-12ED32CEC3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="1193">
   <si>
     <t>#</t>
   </si>
@@ -2481,9 +2481,6 @@
     <t>Effect_Buff_Burn_Self_Desc</t>
   </si>
   <si>
-    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-  </si>
-  <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}层[Card_Burn]</t>
   </si>
   <si>
@@ -3492,35 +3489,35 @@
   </si>
   <si>
     <t>UI_Button_Volume</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>UI_Button_CameraShakeSensitivity</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>CameraShakeSensitivity</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>镜头晃动</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Burn</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3536,7 +3533,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3552,15 +3549,15 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Lable_HighTemp_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3586,7 +3583,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3612,7 +3609,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3639,7 +3636,7 @@
       </rPr>
       <t>Sample</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3666,42 +3663,42 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Formal experiment</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>正式实验</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>在空白样本上尝试一下手头的药剂，或许会有新的收获。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>直面拥有特殊能力的造物，击败后即可进入下一阶段。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>休息一下。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Try the potionon the blank sample, maybe you will get something new.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Face the pureatures with special abilities, and defeat them to enter the next stage.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Take a break.</t>
   </si>
   <si>
     <t>Prototype_1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Prototype_2</t>
@@ -3768,21 +3765,21 @@
   </si>
   <si>
     <t>这部分是为了新教程准备的叙事大纲迭代</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tutorial_BranchTest_1</t>
   </si>
   <si>
     <t>卡牌分支测试</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
   </si>
   <si>
     <t>分支测试1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>分支测试2</t>
@@ -3792,19 +3789,19 @@
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3836,7 +3833,7 @@
       </rPr>
       <t>4</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3858,7 +3855,7 @@
       </rPr>
       <t>大地之子</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3940,7 +3937,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4021,7 +4018,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4052,100 +4049,100 @@
       </rPr>
       <t>Watcher</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
 Initial hand size: 4
 maximum hand size: 5
 Element meter capacity: 10</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 6</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>不动如山的守望者。灵魂来自大地，也将归于大地。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：6</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Sturdy</t>
@@ -4155,148 +4152,148 @@
   </si>
   <si>
     <t>坚固</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>反射</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Earth Element Bottle</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Basic Earth Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Earth Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Earth Core Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
   </si>
   <si>
     <t>Greater Earth Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
   </si>
   <si>
     <t>Vitality Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4309,120 +4306,120 @@
       </rPr>
       <t>健体药剂</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Ironbone Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
   </si>
   <si>
     <t>Shackle Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Reflection Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
   </si>
   <si>
     <t>Stoneskin Potion</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>下一场实验：</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4434,22 +4431,22 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind</t>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>顺风</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4465,50 +4462,166 @@
       </rPr>
       <t>精炼或抽牌后顺风归零。</t>
     </r>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Tailwind]不小于效果值时触发。</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Gain tailwind by using cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Triggers when [Card_Tailwind] is greater than or equal to the effect value.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
   </si>
   <si>
     <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>FocusPotion</t>
+  </si>
+  <si>
+    <t>集中药剂</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Focus Potion</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpikePotion</t>
+  </si>
+  <si>
+    <t>Spike Potion</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>地刺药剂</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy_Self_Focus_Desc</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Self_Focus_Desc</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPowerPotion</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrustPotion</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfEarth</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth Power Potion</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crust Potion</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breath of Earth</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>地能药剂</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>地壳药剂</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>息壤</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfTheWild</t>
+  </si>
+  <si>
+    <t>Breath of the wild</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒野之息</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoarOfTheEarth</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Roar of the Earth</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>土石咆哮</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4775,86 +4888,89 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5131,22 +5247,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.8984375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="25.69921875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="30.296875" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="11"/>
+    <col min="1" max="1" width="12.88671875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -5219,17 +5335,17 @@
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="39"/>
+      <c r="C9" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5239,9 +5355,9 @@
   <dimension ref="A1:H102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.296875" customWidth="1"/>
-    <col min="2" max="2" width="53.69921875" customWidth="1"/>
-    <col min="3" max="3" width="58.19921875" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="53.6640625" customWidth="1"/>
+    <col min="3" max="3" width="58.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5257,461 +5373,461 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B2" t="s">
         <v>778</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>779</v>
-      </c>
-      <c r="C2" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>780</v>
+      </c>
+      <c r="B3" t="s">
         <v>781</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>782</v>
-      </c>
-      <c r="C3" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>783</v>
+      </c>
+      <c r="B4" t="s">
         <v>784</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>785</v>
-      </c>
-      <c r="C4" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B5" t="s">
         <v>787</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>788</v>
-      </c>
-      <c r="C5" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>789</v>
+      </c>
+      <c r="B6" t="s">
         <v>790</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>791</v>
-      </c>
-      <c r="C6" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>792</v>
+      </c>
+      <c r="B7" t="s">
         <v>793</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>794</v>
-      </c>
-      <c r="C7" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>795</v>
+      </c>
+      <c r="B9" t="s">
         <v>796</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>797</v>
-      </c>
-      <c r="C9" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>798</v>
+      </c>
+      <c r="B10" t="s">
         <v>799</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>800</v>
-      </c>
-      <c r="C10" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>801</v>
+      </c>
+      <c r="B11" t="s">
         <v>802</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>803</v>
-      </c>
-      <c r="C11" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>804</v>
+      </c>
+      <c r="B12" t="s">
         <v>805</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>806</v>
-      </c>
-      <c r="C12" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>807</v>
+      </c>
+      <c r="B14" t="s">
         <v>808</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>809</v>
-      </c>
-      <c r="C14" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>810</v>
+      </c>
+      <c r="B15" t="s">
         <v>811</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>812</v>
-      </c>
-      <c r="C15" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>813</v>
+      </c>
+      <c r="B16" t="s">
         <v>814</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>815</v>
-      </c>
-      <c r="C16" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>816</v>
+      </c>
+      <c r="B17" t="s">
         <v>817</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>818</v>
-      </c>
-      <c r="C17" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>819</v>
+      </c>
+      <c r="B18" t="s">
         <v>820</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>821</v>
-      </c>
-      <c r="C18" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>822</v>
+      </c>
+      <c r="B19" t="s">
         <v>823</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>824</v>
-      </c>
-      <c r="C19" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>825</v>
+      </c>
+      <c r="B20" t="s">
         <v>826</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>827</v>
-      </c>
-      <c r="C20" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B21" t="s">
+        <v>826</v>
+      </c>
+      <c r="C21" t="s">
         <v>827</v>
-      </c>
-      <c r="C21" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B22" t="s">
+        <v>826</v>
+      </c>
+      <c r="C22" t="s">
         <v>827</v>
-      </c>
-      <c r="C22" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B23" t="s">
+        <v>826</v>
+      </c>
+      <c r="C23" t="s">
         <v>827</v>
-      </c>
-      <c r="C23" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>831</v>
+      </c>
+      <c r="B24" t="s">
         <v>832</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>833</v>
-      </c>
-      <c r="C24" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>834</v>
+      </c>
+      <c r="B25" t="s">
         <v>835</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>836</v>
-      </c>
-      <c r="C25" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>837</v>
+      </c>
+      <c r="B27" t="s">
         <v>838</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>839</v>
-      </c>
-      <c r="C27" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>840</v>
+      </c>
+      <c r="B28" t="s">
         <v>841</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>842</v>
-      </c>
-      <c r="C28" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>843</v>
+      </c>
+      <c r="B29" t="s">
         <v>844</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>845</v>
-      </c>
-      <c r="C29" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>846</v>
+      </c>
+      <c r="B30" t="s">
         <v>847</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>848</v>
-      </c>
-      <c r="C30" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>849</v>
+      </c>
+      <c r="B31" t="s">
         <v>850</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>851</v>
-      </c>
-      <c r="C31" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>852</v>
+      </c>
+      <c r="B32" t="s">
         <v>853</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>854</v>
-      </c>
-      <c r="C32" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>855</v>
+      </c>
+      <c r="B33" t="s">
         <v>856</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>857</v>
-      </c>
-      <c r="C33" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>858</v>
+      </c>
+      <c r="B34" t="s">
         <v>859</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>860</v>
-      </c>
-      <c r="C34" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>861</v>
+      </c>
+      <c r="B35" t="s">
         <v>862</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>863</v>
-      </c>
-      <c r="C35" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>864</v>
+      </c>
+      <c r="B36" t="s">
         <v>865</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>866</v>
-      </c>
-      <c r="C36" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>867</v>
+      </c>
+      <c r="B37" t="s">
         <v>868</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>869</v>
-      </c>
-      <c r="C37" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>870</v>
+      </c>
+      <c r="B38" t="s">
         <v>871</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>872</v>
-      </c>
-      <c r="C38" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>873</v>
+      </c>
+      <c r="B39" t="s">
         <v>874</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>875</v>
-      </c>
-      <c r="C39" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>876</v>
+      </c>
+      <c r="B40" t="s">
         <v>877</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>878</v>
-      </c>
-      <c r="C40" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>879</v>
+      </c>
+      <c r="B41" t="s">
         <v>880</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>881</v>
-      </c>
-      <c r="C41" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>883</v>
+      </c>
+      <c r="B43" t="s">
         <v>884</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>885</v>
-      </c>
-      <c r="C43" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>886</v>
+      </c>
+      <c r="B44" t="s">
         <v>887</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>888</v>
-      </c>
-      <c r="C44" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>889</v>
+      </c>
+      <c r="B45" t="s">
         <v>890</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>891</v>
-      </c>
-      <c r="C45" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C46" t="s">
         <v>331</v>
@@ -5719,18 +5835,18 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>893</v>
+      </c>
+      <c r="B47" t="s">
         <v>894</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>895</v>
-      </c>
-      <c r="C47" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B48" t="s">
         <v>319</v>
@@ -5741,182 +5857,182 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>902</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G51" s="30"/>
       <c r="H51" s="30"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="30" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G52" s="30"/>
       <c r="H52" s="30"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="30" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G55" s="30"/>
       <c r="H55" s="30"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="30" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="40" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B57" s="40" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>1156</v>
+      <c r="A57" s="36" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C57" s="36" t="s">
+        <v>1155</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
-    <row r="58" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A58" s="40" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B58" s="42" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C58" s="41" t="s">
-        <v>1157</v>
+    <row r="58" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A58" s="36" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B58" s="38" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C58" s="37" t="s">
+        <v>1156</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="40" t="s">
+      <c r="A59" s="36" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="36" t="s">
         <v>1154</v>
       </c>
-      <c r="B59" s="40" t="s">
+      <c r="B60" s="36" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C60" s="37" t="s">
         <v>1158</v>
       </c>
-      <c r="C59" s="40" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="40" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B60" s="40" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C60" s="41" t="s">
-        <v>1159</v>
-      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="40"/>
-      <c r="B61" s="40"/>
+      <c r="A61" s="36"/>
+      <c r="B61" s="36"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>903</v>
+      </c>
+      <c r="B62" t="s">
         <v>904</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>905</v>
-      </c>
-      <c r="C62" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>906</v>
+      </c>
+      <c r="B63" t="s">
         <v>907</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>908</v>
-      </c>
-      <c r="C63" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>909</v>
+      </c>
+      <c r="B64" t="s">
         <v>910</v>
-      </c>
-      <c r="B64" t="s">
-        <v>911</v>
       </c>
       <c r="C64" t="s">
         <v>65</v>
@@ -5924,128 +6040,128 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>911</v>
+      </c>
+      <c r="B65" t="s">
         <v>912</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>913</v>
-      </c>
-      <c r="C65" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>914</v>
+      </c>
+      <c r="B66" t="s">
         <v>915</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>916</v>
-      </c>
-      <c r="C66" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>917</v>
+      </c>
+      <c r="B67" t="s">
         <v>918</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>919</v>
-      </c>
-      <c r="C67" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>920</v>
+      </c>
+      <c r="B68" t="s">
         <v>921</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>922</v>
-      </c>
-      <c r="C68" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>923</v>
+      </c>
+      <c r="B69" t="s">
         <v>924</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>925</v>
-      </c>
-      <c r="C69" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>926</v>
+      </c>
+      <c r="B70" t="s">
         <v>927</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>928</v>
-      </c>
-      <c r="C70" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>929</v>
+      </c>
+      <c r="B71" t="s">
         <v>930</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>931</v>
-      </c>
-      <c r="C71" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>932</v>
+      </c>
+      <c r="B73" t="s">
         <v>933</v>
       </c>
-      <c r="B73" t="s">
-        <v>934</v>
-      </c>
       <c r="C73" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>934</v>
+      </c>
+      <c r="B74" t="s">
         <v>935</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>936</v>
-      </c>
-      <c r="C74" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>937</v>
+      </c>
+      <c r="B76" t="s">
         <v>938</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>939</v>
-      </c>
-      <c r="C76" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>940</v>
+      </c>
+      <c r="B77" t="s">
         <v>941</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>942</v>
-      </c>
-      <c r="C77" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B78" t="s">
         <v>52</v>
@@ -6056,65 +6172,65 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>944</v>
+      </c>
+      <c r="B79" t="s">
         <v>945</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>946</v>
-      </c>
-      <c r="C79" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>947</v>
+      </c>
+      <c r="B81" t="s">
         <v>948</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>949</v>
-      </c>
-      <c r="C81" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>950</v>
+      </c>
+      <c r="B82" t="s">
         <v>951</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>952</v>
-      </c>
-      <c r="C82" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>953</v>
+      </c>
+      <c r="B83" t="s">
         <v>954</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>955</v>
-      </c>
-      <c r="C83" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>956</v>
+      </c>
+      <c r="B84" t="s">
         <v>957</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>958</v>
-      </c>
-      <c r="C84" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>959</v>
+      </c>
+      <c r="B85" t="s">
         <v>960</v>
-      </c>
-      <c r="B85" t="s">
-        <v>961</v>
       </c>
       <c r="C85" t="s">
         <v>39</v>
@@ -6122,109 +6238,109 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>961</v>
+      </c>
+      <c r="B86" t="s">
         <v>962</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>963</v>
-      </c>
-      <c r="C86" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>964</v>
+      </c>
+      <c r="B88" t="s">
         <v>965</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>966</v>
-      </c>
-      <c r="C88" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>967</v>
+      </c>
+      <c r="B89" t="s">
         <v>968</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>969</v>
-      </c>
-      <c r="C89" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>970</v>
+      </c>
+      <c r="B90" t="s">
         <v>971</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>972</v>
-      </c>
-      <c r="C90" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>973</v>
+      </c>
+      <c r="B91" t="s">
         <v>974</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>975</v>
-      </c>
-      <c r="C91" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>976</v>
+      </c>
+      <c r="B92" t="s">
         <v>977</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>978</v>
-      </c>
-      <c r="C92" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B93" t="s">
+        <v>979</v>
+      </c>
+      <c r="C93" t="s">
         <v>980</v>
-      </c>
-      <c r="C93" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>981</v>
+      </c>
+      <c r="B94" t="s">
         <v>982</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>983</v>
-      </c>
-      <c r="C94" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>984</v>
+      </c>
+      <c r="B95" t="s">
         <v>985</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>986</v>
-      </c>
-      <c r="C95" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A97" s="25" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C97" t="s">
         <v>396</v>
@@ -6232,43 +6348,43 @@
     </row>
     <row r="98" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A98" s="25" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B98" s="26" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C98" s="29" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A99" s="26" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B99" s="26" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C99" s="28" t="s">
         <v>1016</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A100" s="26" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B100" s="26" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A101" s="26" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C101" t="s">
         <v>399</v>
@@ -6276,17 +6392,17 @@
     </row>
     <row r="102" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A102" s="26" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B102" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6294,10 +6410,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.296875" customWidth="1"/>
-    <col min="2" max="2" width="31.796875" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6314,50 +6430,50 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>987</v>
+      </c>
+      <c r="B2" t="s">
         <v>988</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>989</v>
-      </c>
-      <c r="C2" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>990</v>
+      </c>
+      <c r="B3" t="s">
         <v>991</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>992</v>
-      </c>
-      <c r="C3" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>993</v>
+      </c>
+      <c r="B4" t="s">
         <v>994</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>995</v>
-      </c>
-      <c r="C4" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>996</v>
+      </c>
+      <c r="B5" t="s">
         <v>997</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>998</v>
       </c>
-      <c r="C5" t="s">
-        <v>999</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6367,9 +6483,9 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.69921875" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="67.796875" customWidth="1"/>
+    <col min="3" max="3" width="67.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6385,119 +6501,119 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="24" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6508,8 +6624,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="22.296875" customWidth="1"/>
-    <col min="3" max="3" width="15.69921875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6657,7 +6773,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -6668,13 +6784,13 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>1001</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="C15" s="24" t="s">
         <v>1002</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -6809,7 +6925,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="138" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -6910,17 +7026,17 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="34" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C42" s="34" t="s">
         <v>1147</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>1148</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6930,9 +7046,9 @@
   <dimension ref="A1:C90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.09765625" customWidth="1"/>
-    <col min="2" max="2" width="16.296875" customWidth="1"/>
-    <col min="3" max="3" width="15.296875" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7000,18 +7116,18 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>1049</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -7610,148 +7726,190 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="33" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="33" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="33" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B71" s="33" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C71" s="33" t="s">
         <v>1110</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>1121</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B74" s="35" t="s">
         <v>1123</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="C74" s="35" t="s">
         <v>1124</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B75" s="35" t="s">
         <v>1126</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="C75" s="35" t="s">
         <v>1127</v>
-      </c>
-      <c r="C75" s="35" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B76" s="35" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C76" s="35" t="s">
         <v>1135</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B77" s="35" t="s">
         <v>1144</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>1145</v>
       </c>
-      <c r="C77" s="35" t="s">
-        <v>1146</v>
-      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
+      <c r="A78" s="8" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B78" s="43" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C78" s="43" t="s">
+        <v>1166</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
+      <c r="A79" s="8" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B79" s="43" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C79" s="43" t="s">
+        <v>1170</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
+      <c r="A80" s="43" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B80" s="43" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C80" s="43" t="s">
+        <v>1184</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
+      <c r="A81" s="43" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B81" s="43" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C81" s="43" t="s">
+        <v>1185</v>
+      </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
+      <c r="A82" s="44" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B82" s="44" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C82" s="43" t="s">
+        <v>1186</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>1117</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>1118</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>1119</v>
-      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
+      <c r="A85" s="9" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B85" s="45" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C85" s="45" t="s">
+        <v>1189</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
+      <c r="A86" s="45" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B86" s="45" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C86" s="45" t="s">
+        <v>1192</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="9"/>
@@ -7774,7 +7932,7 @@
       <c r="C90" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7784,9 +7942,9 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.296875" customWidth="1"/>
-    <col min="3" max="3" width="17.09765625" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -7838,10 +7996,10 @@
         <v>287</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>1059</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7877,7 +8035,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="153.6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" ht="195" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>297</v>
       </c>
@@ -7900,7 +8058,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="151.80000000000001" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>303</v>
       </c>
@@ -7922,12 +8080,12 @@
         <v>308</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="207" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="248.4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>309</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>310</v>
@@ -7935,24 +8093,24 @@
     </row>
     <row r="14" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
         <v>1055</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>1056</v>
-      </c>
       <c r="B15" s="32" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>1063</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -7962,7 +8120,7 @@
       <c r="C17" s="32"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7972,9 +8130,9 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.8984375" customWidth="1"/>
-    <col min="2" max="2" width="46.8984375" customWidth="1"/>
-    <col min="3" max="3" width="41.296875" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7993,7 +8151,7 @@
         <v>311</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C2" t="s">
         <v>312</v>
@@ -8007,7 +8165,7 @@
         <v>314</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -8062,7 +8220,7 @@
         <v>328</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -8078,46 +8236,46 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>1004</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>1005</v>
-      </c>
       <c r="C10" s="24" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -8165,7 +8323,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8175,9 +8333,9 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.796875" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" customWidth="1"/>
-    <col min="3" max="3" width="9.296875" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -8350,10 +8508,10 @@
         <v>384</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -8412,7 +8570,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8422,9 +8580,9 @@
   <dimension ref="A1:D96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.296875" customWidth="1"/>
-    <col min="2" max="2" width="76.796875" customWidth="1"/>
-    <col min="3" max="3" width="54.19921875" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="76.77734375" customWidth="1"/>
+    <col min="3" max="3" width="54.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -8446,7 +8604,7 @@
         <v>401</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -8596,8 +8754,8 @@
       <c r="A16" t="s">
         <v>441</v>
       </c>
-      <c r="B16" s="41" t="s">
-        <v>1160</v>
+      <c r="B16" s="37" t="s">
+        <v>1159</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>442</v>
@@ -9381,14 +9539,14 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C96" s="24" t="s">
         <v>1047</v>
       </c>
-      <c r="C96" s="24" t="s">
-        <v>1048</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait"/>
 </worksheet>
@@ -9399,8 +9557,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" customWidth="1"/>
-    <col min="3" max="3" width="69.796875" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="3" max="3" width="69.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9426,18 +9584,18 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.69921875" customWidth="1"/>
-    <col min="2" max="3" width="53.69921875" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="3" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9598,413 +9756,435 @@
       <c r="A15" t="s">
         <v>693</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="37" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C15" t="s">
         <v>694</v>
-      </c>
-      <c r="C15" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>695</v>
+      </c>
+      <c r="B16" t="s">
         <v>696</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>697</v>
-      </c>
-      <c r="C16" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>698</v>
+      </c>
+      <c r="B17" t="s">
         <v>699</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>700</v>
-      </c>
-      <c r="C17" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
+        <v>763</v>
+      </c>
+      <c r="B18" t="s">
         <v>764</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>766</v>
+      </c>
+      <c r="B19" t="s">
         <v>767</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>768</v>
-      </c>
-      <c r="C19" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>770</v>
+      </c>
+      <c r="B22" t="s">
         <v>771</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>772</v>
-      </c>
-      <c r="C22" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>701</v>
+      </c>
+      <c r="B28" t="s">
         <v>702</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>703</v>
-      </c>
-      <c r="C28" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>704</v>
+      </c>
+      <c r="B29" t="s">
         <v>705</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>706</v>
-      </c>
-      <c r="C29" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>707</v>
+      </c>
+      <c r="B30" t="s">
         <v>708</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>709</v>
-      </c>
-      <c r="C30" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>710</v>
+      </c>
+      <c r="B31" t="s">
         <v>711</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>712</v>
-      </c>
-      <c r="C31" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>713</v>
+      </c>
+      <c r="B32" t="s">
         <v>714</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>715</v>
-      </c>
-      <c r="C32" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>716</v>
+      </c>
+      <c r="B33" t="s">
         <v>717</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>718</v>
-      </c>
-      <c r="C33" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>719</v>
+      </c>
+      <c r="B34" t="s">
         <v>720</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>721</v>
-      </c>
-      <c r="C34" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>722</v>
+      </c>
+      <c r="B35" t="s">
         <v>723</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>724</v>
-      </c>
-      <c r="C35" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>725</v>
+      </c>
+      <c r="B36" t="s">
         <v>726</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>727</v>
-      </c>
-      <c r="C36" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
+        <v>728</v>
+      </c>
+      <c r="B37" t="s">
         <v>729</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>730</v>
-      </c>
-      <c r="C37" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>774</v>
+      </c>
+      <c r="B38" t="s">
         <v>775</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>776</v>
-      </c>
-      <c r="C38" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>731</v>
+      </c>
+      <c r="B39" t="s">
         <v>732</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>733</v>
-      </c>
-      <c r="C39" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>734</v>
+      </c>
+      <c r="B40" t="s">
         <v>735</v>
       </c>
-      <c r="B40" t="s">
-        <v>736</v>
-      </c>
       <c r="C40" s="34" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>736</v>
+      </c>
+      <c r="B41" t="s">
         <v>737</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>738</v>
-      </c>
-      <c r="C41" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>739</v>
+      </c>
+      <c r="B42" t="s">
         <v>740</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>741</v>
-      </c>
-      <c r="C42" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>742</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C43" t="s">
         <v>743</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C43" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>744</v>
+      </c>
+      <c r="B44" t="s">
         <v>745</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>746</v>
-      </c>
-      <c r="C44" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>747</v>
+      </c>
+      <c r="B45" t="s">
         <v>748</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>750</v>
+      </c>
+      <c r="B46" t="s">
         <v>751</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>752</v>
-      </c>
-      <c r="C46" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>754</v>
+      </c>
+      <c r="B48" t="s">
         <v>755</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>756</v>
-      </c>
-      <c r="C48" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>757</v>
+      </c>
+      <c r="B49" t="s">
         <v>758</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>759</v>
-      </c>
-      <c r="C49" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>760</v>
+      </c>
+      <c r="B50" t="s">
         <v>761</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>762</v>
-      </c>
-      <c r="C50" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C51" s="24" t="s">
         <v>1107</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>1139</v>
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="34" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>1173</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="41" t="s">
+      <c r="A54" s="34" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="37" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B56" s="37" t="s">
         <v>1163</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="C56" s="37" t="s">
         <v>1164</v>
       </c>
-      <c r="C54" s="41" t="s">
-        <v>1165</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75031AC7-F426-493E-BC1D-12ED32CEC3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D23A3A-96EE-4368-AE1A-8013A53DAFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="1197">
   <si>
     <t>#</t>
   </si>
@@ -1195,9 +1195,6 @@
   </si>
   <si>
     <t>Buff_Calm</t>
-  </si>
-  <si>
-    <t>[Intro_Buff] Calm</t>
   </si>
   <si>
     <t>Buff_Calm_Desc</t>
@@ -4604,12 +4601,32 @@
     <t>土石咆哮</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
+  <si>
+    <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff] Calm</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]Sturdy</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]Reflect</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4956,6 +4973,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4968,12 +4988,9 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5247,7 +5264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="11" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" style="11" customWidth="1"/>
@@ -5255,16 +5272,16 @@
     <col min="4" max="16384" width="8.6640625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="87" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40"/>
-    </row>
-    <row r="2" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="C1" s="43"/>
+    </row>
+    <row r="2" spans="1:3" ht="20.399999999999999">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -5275,7 +5292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="20.399999999999999">
       <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
@@ -5286,7 +5303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="20.399999999999999">
       <c r="A4" s="17" t="s">
         <v>7</v>
       </c>
@@ -5297,7 +5314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="20.399999999999999">
       <c r="A5" s="17" t="s">
         <v>0</v>
       </c>
@@ -5308,7 +5325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="20.399999999999999">
       <c r="A6" s="17" t="s">
         <v>8</v>
       </c>
@@ -5319,26 +5336,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="19.5" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="21"/>
     </row>
-    <row r="8" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="20.399999999999999">
       <c r="A8" s="22"/>
       <c r="B8" s="23"/>
       <c r="C8" s="22"/>
     </row>
-    <row r="9" spans="1:3" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="94.5" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="42"/>
+      <c r="C9" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5353,14 +5370,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H102"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
     <col min="2" max="2" width="53.6640625" customWidth="1"/>
     <col min="3" max="3" width="58.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5371,482 +5388,482 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B2" t="s">
         <v>777</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>778</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>780</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>781</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>783</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>784</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>786</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>787</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>789</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>790</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>792</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>793</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>795</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>796</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>798</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>799</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>801</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>802</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>804</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>805</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>807</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>808</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>810</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>811</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>813</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>814</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>816</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>817</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>819</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>820</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>822</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>823</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>825</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>826</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>825</v>
+      </c>
+      <c r="C21" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>828</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
+        <v>825</v>
+      </c>
+      <c r="C22" t="s">
         <v>826</v>
       </c>
-      <c r="C21" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>829</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
+        <v>825</v>
+      </c>
+      <c r="C23" t="s">
         <v>826</v>
       </c>
-      <c r="C22" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>830</v>
       </c>
-      <c r="B23" t="s">
-        <v>826</v>
-      </c>
-      <c r="C23" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>831</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>832</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>834</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>835</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>837</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>838</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>840</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>841</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>843</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>844</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>846</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>847</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>849</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>850</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>852</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>853</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>855</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>856</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>858</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>859</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>861</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>862</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>864</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>865</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>867</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>868</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>870</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>871</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>873</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>874</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>876</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>877</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>879</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>880</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B42" s="34" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>882</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C42" s="34" t="s">
+      <c r="B43" t="s">
+        <v>883</v>
+      </c>
+      <c r="C43" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>885</v>
+      </c>
+      <c r="B44" t="s">
+        <v>886</v>
+      </c>
+      <c r="C44" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>888</v>
+      </c>
+      <c r="B45" t="s">
+        <v>889</v>
+      </c>
+      <c r="C45" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>891</v>
+      </c>
+      <c r="B46" s="34" t="s">
         <v>1128</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>883</v>
-      </c>
-      <c r="B43" t="s">
-        <v>884</v>
-      </c>
-      <c r="C43" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>886</v>
-      </c>
-      <c r="B44" t="s">
-        <v>887</v>
-      </c>
-      <c r="C44" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>889</v>
-      </c>
-      <c r="B45" t="s">
-        <v>890</v>
-      </c>
-      <c r="C45" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="C46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>892</v>
       </c>
-      <c r="B46" s="34" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C46" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>893</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>894</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>895</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>896</v>
       </c>
       <c r="B48" t="s">
         <v>319</v>
@@ -5855,313 +5872,313 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="C49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="30" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G51" s="30"/>
       <c r="H51" s="30"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="30" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G52" s="30"/>
       <c r="H52" s="30"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="30" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="30" t="s">
         <v>1080</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="30" t="s">
-        <v>1081</v>
-      </c>
       <c r="B54" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="30" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G55" s="30"/>
       <c r="H55" s="30"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="30" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="36" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
-    <row r="58" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="27.6">
       <c r="A58" s="36" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="36" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="36" t="s">
         <v>1153</v>
       </c>
-      <c r="B59" s="36" t="s">
+      <c r="B60" s="36" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C60" s="37" t="s">
         <v>1157</v>
       </c>
-      <c r="C59" s="36" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="36" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B60" s="36" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C60" s="37" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="36"/>
       <c r="B61" s="36"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
+        <v>902</v>
+      </c>
+      <c r="B62" t="s">
         <v>903</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>904</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>906</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>907</v>
       </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>909</v>
-      </c>
-      <c r="B64" t="s">
-        <v>910</v>
       </c>
       <c r="C64" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>910</v>
+      </c>
+      <c r="B65" t="s">
         <v>911</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>912</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>914</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>915</v>
       </c>
-      <c r="C66" t="s">
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>917</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>918</v>
       </c>
-      <c r="C67" t="s">
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>919</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>920</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>921</v>
       </c>
-      <c r="C68" t="s">
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>923</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>924</v>
       </c>
-      <c r="C69" t="s">
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>926</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>927</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>929</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>930</v>
       </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>931</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>932</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>933</v>
       </c>
-      <c r="C73" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>934</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>935</v>
       </c>
-      <c r="C74" t="s">
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>937</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>938</v>
       </c>
-      <c r="C76" t="s">
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
         <v>939</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>940</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>941</v>
       </c>
-      <c r="C77" t="s">
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>942</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>943</v>
       </c>
       <c r="B78" t="s">
         <v>52</v>
@@ -6170,235 +6187,235 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
+        <v>943</v>
+      </c>
+      <c r="B79" t="s">
         <v>944</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>945</v>
       </c>
-      <c r="C79" t="s">
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>947</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>948</v>
       </c>
-      <c r="C81" t="s">
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
         <v>949</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>950</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>951</v>
       </c>
-      <c r="C82" t="s">
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>952</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>953</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>954</v>
       </c>
-      <c r="C83" t="s">
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
         <v>955</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>956</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>957</v>
       </c>
-      <c r="C84" t="s">
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
         <v>958</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>959</v>
-      </c>
-      <c r="B85" t="s">
-        <v>960</v>
       </c>
       <c r="C85" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
+        <v>960</v>
+      </c>
+      <c r="B86" t="s">
         <v>961</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>962</v>
       </c>
-      <c r="C86" t="s">
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>963</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>964</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>965</v>
       </c>
-      <c r="C88" t="s">
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B89" t="s">
         <v>967</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>968</v>
       </c>
-      <c r="C89" t="s">
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>970</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>971</v>
       </c>
-      <c r="C90" t="s">
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
         <v>973</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>974</v>
       </c>
-      <c r="C91" t="s">
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>976</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>977</v>
       </c>
-      <c r="C92" t="s">
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="26" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B93" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="26" t="s">
+      <c r="C93" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>980</v>
+      </c>
+      <c r="B94" t="s">
+        <v>981</v>
+      </c>
+      <c r="C94" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>983</v>
+      </c>
+      <c r="B95" t="s">
+        <v>984</v>
+      </c>
+      <c r="C95" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15.6">
+      <c r="A97" s="25" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C97" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15.6">
+      <c r="A98" s="25" t="s">
         <v>1009</v>
       </c>
-      <c r="B93" t="s">
-        <v>979</v>
-      </c>
-      <c r="C93" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>981</v>
-      </c>
-      <c r="B94" t="s">
-        <v>982</v>
-      </c>
-      <c r="C94" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>984</v>
-      </c>
-      <c r="B95" t="s">
-        <v>985</v>
-      </c>
-      <c r="C95" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A97" s="25" t="s">
+      <c r="B98" s="26" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C98" s="29" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15.6">
+      <c r="A99" s="26" t="s">
         <v>1006</v>
       </c>
-      <c r="B97" s="27" t="s">
+      <c r="B99" s="26" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C99" s="28" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15.6">
+      <c r="A100" s="26" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15.6">
+      <c r="A101" s="26" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B101" s="27" t="s">
         <v>1013</v>
       </c>
-      <c r="C97" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A98" s="25" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B98" s="26" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C98" s="29" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A99" s="26" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B99" s="26" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A100" s="26" t="s">
+      <c r="C101" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15.6">
+      <c r="A102" s="26" t="s">
         <v>1011</v>
       </c>
-      <c r="B100" s="26" t="s">
+      <c r="B102" t="s">
         <v>1021</v>
       </c>
-      <c r="C100" s="28" t="s">
+      <c r="C102" s="28" t="s">
         <v>1018</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A101" s="26" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C101" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A102" s="26" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B102" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>1019</v>
       </c>
     </row>
   </sheetData>
@@ -6410,14 +6427,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
     <col min="2" max="2" width="31.77734375" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6428,48 +6445,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B2" t="s">
         <v>987</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>988</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>989</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>990</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>991</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>993</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>994</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>996</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>997</v>
-      </c>
-      <c r="C5" t="s">
-        <v>998</v>
       </c>
     </row>
   </sheetData>
@@ -6481,14 +6498,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B11783-37A9-4040-A90F-3CA8B07177F6}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="67.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6499,117 +6516,117 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="24" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24" t="s">
         <v>1023</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="24" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="24" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="24" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="24" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="24" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="24" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="24" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="24" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="24" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="24" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="24" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="24" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="24" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" s="24" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="24" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="24" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="24" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="24" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+    <row r="22" spans="1:1">
+      <c r="A22" s="24" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="24" t="s">
         <v>1043</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
-        <v>1044</v>
       </c>
     </row>
   </sheetData>
@@ -6621,14 +6638,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6639,7 +6656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6650,7 +6667,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6661,7 +6678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6672,7 +6689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -6683,7 +6700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -6694,7 +6711,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -6705,7 +6722,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -6716,7 +6733,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -6727,7 +6744,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -6738,7 +6755,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -6749,7 +6766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -6760,7 +6777,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -6771,9 +6788,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -6782,18 +6799,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
+        <v>999</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>1000</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="C15" s="24" t="s">
         <v>1001</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -6804,7 +6821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -6815,7 +6832,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -6826,7 +6843,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -6837,7 +6854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -6848,7 +6865,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -6859,7 +6876,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="27.6">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -6870,7 +6887,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -6881,7 +6898,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -6892,7 +6909,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -6903,7 +6920,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -6914,7 +6931,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -6925,7 +6942,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="151.80000000000001" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="151.80000000000001">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -6936,7 +6953,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -6947,7 +6964,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -6958,7 +6975,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>96</v>
       </c>
@@ -6969,7 +6986,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -6980,7 +6997,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>102</v>
       </c>
@@ -6991,7 +7008,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>105</v>
       </c>
@@ -7002,7 +7019,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>108</v>
       </c>
@@ -7013,7 +7030,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>111</v>
       </c>
@@ -7024,15 +7041,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="34" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C42" s="34" t="s">
         <v>1146</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>1147</v>
       </c>
     </row>
   </sheetData>
@@ -7044,14 +7061,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C90"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7062,7 +7079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -7070,7 +7087,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -7081,7 +7098,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>119</v>
       </c>
@@ -7092,7 +7109,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -7103,7 +7120,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>123</v>
       </c>
@@ -7114,23 +7131,23 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>1048</v>
       </c>
-      <c r="C8" s="24" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="7" t="s">
         <v>126</v>
       </c>
@@ -7141,7 +7158,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="7" t="s">
         <v>129</v>
       </c>
@@ -7152,7 +7169,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="7" t="s">
         <v>132</v>
       </c>
@@ -7163,7 +7180,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="7" t="s">
         <v>135</v>
       </c>
@@ -7174,7 +7191,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="8" t="s">
         <v>138</v>
       </c>
@@ -7185,7 +7202,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
         <v>141</v>
       </c>
@@ -7196,7 +7213,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
         <v>144</v>
       </c>
@@ -7207,7 +7224,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="8" t="s">
         <v>147</v>
       </c>
@@ -7218,7 +7235,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
         <v>150</v>
       </c>
@@ -7229,7 +7246,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
         <v>153</v>
       </c>
@@ -7240,7 +7257,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
         <v>156</v>
       </c>
@@ -7251,7 +7268,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
         <v>159</v>
       </c>
@@ -7262,7 +7279,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
         <v>162</v>
       </c>
@@ -7273,7 +7290,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="8" t="s">
         <v>165</v>
       </c>
@@ -7284,7 +7301,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="9" t="s">
         <v>168</v>
       </c>
@@ -7295,7 +7312,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="9" t="s">
         <v>171</v>
       </c>
@@ -7306,7 +7323,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="9" t="s">
         <v>174</v>
       </c>
@@ -7317,7 +7334,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="9" t="s">
         <v>176</v>
       </c>
@@ -7328,7 +7345,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="9" t="s">
         <v>179</v>
       </c>
@@ -7339,7 +7356,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="9" t="s">
         <v>182</v>
       </c>
@@ -7350,7 +7367,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="9" t="s">
         <v>185</v>
       </c>
@@ -7361,7 +7378,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
         <v>188</v>
       </c>
@@ -7372,7 +7389,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
         <v>191</v>
       </c>
@@ -7383,7 +7400,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
         <v>194</v>
       </c>
@@ -7394,7 +7411,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
         <v>197</v>
       </c>
@@ -7405,7 +7422,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" s="8" t="s">
         <v>200</v>
       </c>
@@ -7416,7 +7433,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="8" t="s">
         <v>203</v>
       </c>
@@ -7427,7 +7444,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" s="8" t="s">
         <v>206</v>
       </c>
@@ -7438,7 +7455,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" s="8" t="s">
         <v>209</v>
       </c>
@@ -7449,7 +7466,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" s="8" t="s">
         <v>212</v>
       </c>
@@ -7460,7 +7477,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" s="8" t="s">
         <v>215</v>
       </c>
@@ -7471,7 +7488,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" s="8" t="s">
         <v>218</v>
       </c>
@@ -7482,7 +7499,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" s="8" t="s">
         <v>221</v>
       </c>
@@ -7493,7 +7510,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" s="8" t="s">
         <v>224</v>
       </c>
@@ -7504,7 +7521,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" s="8" t="s">
         <v>227</v>
       </c>
@@ -7515,7 +7532,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" s="8" t="s">
         <v>229</v>
       </c>
@@ -7526,7 +7543,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
         <v>232</v>
       </c>
@@ -7537,7 +7554,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
         <v>235</v>
       </c>
@@ -7548,7 +7565,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
         <v>238</v>
       </c>
@@ -7559,7 +7576,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
         <v>241</v>
       </c>
@@ -7570,7 +7587,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
         <v>244</v>
       </c>
@@ -7581,7 +7598,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
         <v>247</v>
       </c>
@@ -7592,7 +7609,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" s="7" t="s">
         <v>250</v>
       </c>
@@ -7603,7 +7620,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
         <v>252</v>
       </c>
@@ -7614,7 +7631,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
         <v>254</v>
       </c>
@@ -7625,7 +7642,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
         <v>257</v>
       </c>
@@ -7636,7 +7653,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
         <v>259</v>
       </c>
@@ -7647,7 +7664,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
         <v>262</v>
       </c>
@@ -7658,7 +7675,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" s="10" t="s">
         <v>264</v>
       </c>
@@ -7669,7 +7686,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
         <v>266</v>
       </c>
@@ -7680,7 +7697,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" s="9" t="s">
         <v>269</v>
       </c>
@@ -7691,7 +7708,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" s="9" t="s">
         <v>271</v>
       </c>
@@ -7702,7 +7719,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" s="9" t="s">
         <v>273</v>
       </c>
@@ -7713,7 +7730,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" s="9" t="s">
         <v>276</v>
       </c>
@@ -7724,209 +7741,209 @@
         <v>277</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" s="33" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="33" t="s">
         <v>1092</v>
       </c>
-      <c r="B68" s="33" t="s">
+      <c r="B69" s="33" t="s">
         <v>1095</v>
       </c>
-      <c r="C68" s="33" t="s">
+      <c r="C69" s="33" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="33" t="s">
+    <row r="70" spans="1:3">
+      <c r="A70" s="33" t="s">
         <v>1093</v>
       </c>
-      <c r="B69" s="33" t="s">
+      <c r="B70" s="33" t="s">
         <v>1096</v>
       </c>
-      <c r="C69" s="33" t="s">
+      <c r="C70" s="33" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="33" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B70" s="33" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C70" s="33" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" s="33" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B71" s="33" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C71" s="33" t="s">
         <v>1109</v>
       </c>
-      <c r="C71" s="33" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="8" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="C73" s="8" t="s">
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="35" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="35" t="s">
+      <c r="B74" s="35" t="s">
         <v>1122</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="C74" s="35" t="s">
         <v>1123</v>
       </c>
-      <c r="C74" s="35" t="s">
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="8" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="B75" s="35" t="s">
         <v>1125</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="C75" s="35" t="s">
         <v>1126</v>
       </c>
-      <c r="C75" s="35" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="35" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="B76" s="35" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="B77" s="35" t="s">
         <v>1143</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>1144</v>
       </c>
-      <c r="C77" s="35" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B78" s="39" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C78" s="39" t="s">
         <v>1165</v>
       </c>
-      <c r="B78" s="43" t="s">
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="C78" s="43" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="B79" s="39" t="s">
         <v>1168</v>
       </c>
-      <c r="B79" s="43" t="s">
+      <c r="C79" s="39" t="s">
         <v>1169</v>
       </c>
-      <c r="C79" s="43" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="43" t="s">
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="39" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B80" s="39" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C80" s="39" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="39" t="s">
         <v>1178</v>
       </c>
-      <c r="B80" s="43" t="s">
+      <c r="B81" s="39" t="s">
         <v>1181</v>
       </c>
-      <c r="C80" s="43" t="s">
+      <c r="C81" s="39" t="s">
         <v>1184</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="43" t="s">
+    <row r="82" spans="1:3">
+      <c r="A82" s="40" t="s">
         <v>1179</v>
       </c>
-      <c r="B81" s="43" t="s">
+      <c r="B82" s="40" t="s">
         <v>1182</v>
       </c>
-      <c r="C81" s="43" t="s">
+      <c r="C82" s="39" t="s">
         <v>1185</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="44" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B82" s="44" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C82" s="43" t="s">
+    <row r="84" spans="1:3">
+      <c r="A84" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="9" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
+      <c r="B85" s="41" t="s">
         <v>1187</v>
       </c>
-      <c r="B85" s="45" t="s">
+      <c r="C85" s="41" t="s">
         <v>1188</v>
       </c>
-      <c r="C85" s="45" t="s">
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="41" t="s">
         <v>1189</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="45" t="s">
+      <c r="B86" s="41" t="s">
         <v>1190</v>
       </c>
-      <c r="B86" s="45" t="s">
+      <c r="C86" s="41" t="s">
         <v>1191</v>
       </c>
-      <c r="C86" s="45" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="9"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" s="9"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" s="9"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -7940,14 +7957,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7958,7 +7975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>278</v>
       </c>
@@ -7969,7 +7986,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -7980,7 +7997,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>284</v>
       </c>
@@ -7991,18 +8008,18 @@
         <v>286</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="265.2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="265.2">
       <c r="A5" t="s">
         <v>287</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>1058</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>288</v>
       </c>
@@ -8013,7 +8030,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>291</v>
       </c>
@@ -8024,7 +8041,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" ht="16.8">
       <c r="A8" t="s">
         <v>294</v>
       </c>
@@ -8035,7 +8052,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="195" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" ht="167.4">
       <c r="A9" t="s">
         <v>297</v>
       </c>
@@ -8047,7 +8064,7 @@
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" ht="16.8">
       <c r="A10" t="s">
         <v>300</v>
       </c>
@@ -8058,7 +8075,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="193.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="165.6">
       <c r="A11" t="s">
         <v>303</v>
       </c>
@@ -8069,7 +8086,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" ht="16.8">
       <c r="A12" t="s">
         <v>306</v>
       </c>
@@ -8080,43 +8097,43 @@
         <v>308</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="248.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="234.6">
       <c r="A13" t="s">
         <v>309</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" ht="16.8">
       <c r="A14" s="24" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="165.6">
+      <c r="A15" s="24" t="s">
         <v>1054</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="179.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>1055</v>
-      </c>
       <c r="B15" s="32" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>1062</v>
       </c>
-      <c r="C15" s="32" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5">
       <c r="C16" s="30"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3">
       <c r="C17" s="32"/>
     </row>
   </sheetData>
@@ -8128,14 +8145,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="21.88671875" customWidth="1"/>
     <col min="2" max="2" width="46.88671875" customWidth="1"/>
     <col min="3" max="3" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8146,18 +8163,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>311</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>313</v>
       </c>
@@ -8165,10 +8182,10 @@
         <v>314</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>315</v>
       </c>
@@ -8179,7 +8196,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>318</v>
       </c>
@@ -8190,7 +8207,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>321</v>
       </c>
@@ -8201,7 +8218,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>324</v>
       </c>
@@ -8212,114 +8229,114 @@
         <v>326</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>327</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="24" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>328</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="B9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="24" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>329</v>
-      </c>
-      <c r="B9" t="s">
-        <v>330</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="24" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A12" s="24" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="24" customFormat="1">
+      <c r="A13" s="24" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>332</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>333</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" t="s">
         <v>336</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="15.9" customHeight="1">
+      <c r="A17" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>338</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>339</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" t="s">
         <v>342</v>
-      </c>
-      <c r="C18" t="s">
-        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -8331,14 +8348,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
     <col min="2" max="2" width="10.88671875" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8349,20 +8366,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B2" t="s">
         <v>344</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>345</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>347</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -8371,202 +8388,202 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.35" customHeight="1">
       <c r="A4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B4" t="s">
         <v>348</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>349</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>351</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>352</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>354</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>355</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>357</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>358</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>360</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>361</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>363</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>364</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>366</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>367</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>369</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>370</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>372</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>373</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>375</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>376</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>378</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>379</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>381</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>382</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" s="24" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>384</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>385</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>386</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>388</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>389</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>391</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>392</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="27.6">
+      <c r="A23" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" t="s">
         <v>395</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="27.6">
+      <c r="A24" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" t="s">
         <v>398</v>
-      </c>
-      <c r="C24" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -8578,14 +8595,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D96"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
     <col min="2" max="2" width="76.77734375" customWidth="1"/>
     <col min="3" max="3" width="54.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8596,953 +8613,953 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B2" t="s">
         <v>400</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="31" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>401</v>
       </c>
-      <c r="C2" s="31" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>402</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>405</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>408</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>411</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>414</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>417</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>420</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>423</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>426</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="C11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>429</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>432</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>435</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>438</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C15" s="3" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" s="37" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B16" s="37" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C16" s="3" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>443</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C17" s="3" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>446</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C18" s="3" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>449</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>452</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>455</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>458</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C22" s="3" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>461</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C23" s="3" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>464</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="C24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>467</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>470</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>473</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>476</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="C28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>479</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>482</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C30" s="3" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>485</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C31" s="3" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>488</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C32" s="3" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>491</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C33" s="3" t="s">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>494</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C34" s="3" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>497</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C35" s="3" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>500</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="C36" s="3" t="s">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>503</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="C37" s="3" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>506</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C38" s="3" t="s">
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>509</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="C39" s="3" t="s">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>512</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C40" s="3" t="s">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>515</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="C41" s="3" t="s">
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>518</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C42" s="3" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>520</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>521</v>
       </c>
       <c r="B44">
         <v>111</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>522</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>523</v>
       </c>
       <c r="B45">
         <v>111</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>525</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="C47" s="3" t="s">
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>528</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="C48" s="3" t="s">
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>531</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="C49" s="3" t="s">
+    </row>
+    <row r="50" spans="1:3">
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C50" s="3"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>534</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C51" s="3" t="s">
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>537</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>538</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>540</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>541</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>543</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>544</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>546</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="C55" s="3" t="s">
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
         <v>549</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="C56" s="3" t="s">
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>552</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>553</v>
       </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>555</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>556</v>
       </c>
-      <c r="C58" t="s">
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>558</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>559</v>
       </c>
-      <c r="C60" t="s">
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>561</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>562</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>564</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>565</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>567</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>568</v>
       </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>570</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>571</v>
       </c>
-      <c r="C64" t="s">
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>573</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>574</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>576</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="C67" s="3" t="s">
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>579</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>580</v>
       </c>
-      <c r="C69" t="s">
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B70" t="s">
         <v>582</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>583</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B71" t="s">
         <v>585</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>586</v>
       </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B72" t="s">
         <v>588</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>589</v>
       </c>
-      <c r="C72" t="s">
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B73" t="s">
         <v>591</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>592</v>
       </c>
-      <c r="C73" t="s">
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B74" t="s">
         <v>594</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>595</v>
       </c>
-      <c r="C74" t="s">
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B76" t="s">
         <v>597</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>598</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
         <v>599</v>
       </c>
-      <c r="D76" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B77" t="s">
         <v>600</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>601</v>
       </c>
-      <c r="C77" t="s">
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B78" t="s">
         <v>603</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>604</v>
       </c>
-      <c r="C78" t="s">
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B79" t="s">
         <v>606</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>607</v>
       </c>
-      <c r="C79" t="s">
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B80" t="s">
         <v>609</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>610</v>
       </c>
-      <c r="C80" t="s">
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>612</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>613</v>
       </c>
-      <c r="C81" t="s">
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B82" t="s">
         <v>615</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>616</v>
       </c>
-      <c r="C82" t="s">
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B83" t="s">
         <v>618</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>619</v>
       </c>
-      <c r="C83" t="s">
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B84" t="s">
         <v>621</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>622</v>
       </c>
-      <c r="C84" t="s">
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B85" t="s">
         <v>624</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>625</v>
       </c>
-      <c r="C85" t="s">
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>627</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>628</v>
       </c>
-      <c r="C86" t="s">
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B87" t="s">
         <v>630</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>631</v>
       </c>
-      <c r="C87" t="s">
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B88" t="s">
         <v>633</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>634</v>
       </c>
-      <c r="C88" t="s">
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>636</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>637</v>
       </c>
-      <c r="C90" t="s">
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B91" t="s">
         <v>639</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>640</v>
       </c>
-      <c r="C91" t="s">
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>642</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>643</v>
       </c>
-      <c r="C92" t="s">
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="B93" t="s">
         <v>645</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>646</v>
       </c>
-      <c r="C93" t="s">
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B94" t="s">
         <v>648</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>649</v>
       </c>
-      <c r="C94" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C96" s="24" t="s">
         <v>1046</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -9555,13 +9572,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14.21875" customWidth="1"/>
     <col min="3" max="3" width="69.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9572,15 +9589,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B2" t="s">
         <v>651</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>652</v>
-      </c>
-      <c r="C2" t="s">
-        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -9592,13 +9609,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
     <col min="2" max="3" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9609,578 +9626,578 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2" t="s">
         <v>654</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>655</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>657</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>658</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>660</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>661</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>663</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>664</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>669</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>670</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>672</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>673</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>675</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>676</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="16.8">
+      <c r="A10" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>678</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="16.8">
+      <c r="A11" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>681</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="C11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="16.8">
+      <c r="A12" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>684</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>685</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="16.8">
+      <c r="A13" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>687</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>688</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>690</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>691</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" s="37" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C15" t="s">
         <v>693</v>
       </c>
-      <c r="B15" s="37" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>694</v>
+      </c>
+      <c r="B16" t="s">
+        <v>695</v>
+      </c>
+      <c r="C16" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>697</v>
+      </c>
+      <c r="B17" t="s">
+        <v>698</v>
+      </c>
+      <c r="C17" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.8">
+      <c r="A18" t="s">
+        <v>762</v>
+      </c>
+      <c r="B18" t="s">
+        <v>763</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>765</v>
+      </c>
+      <c r="B19" t="s">
+        <v>766</v>
+      </c>
+      <c r="C19" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>768</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>769</v>
+      </c>
+      <c r="B22" t="s">
+        <v>770</v>
+      </c>
+      <c r="C22" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>772</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E23" s="30"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E24" s="30"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>700</v>
+      </c>
+      <c r="B28" t="s">
+        <v>701</v>
+      </c>
+      <c r="C28" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>703</v>
+      </c>
+      <c r="B29" t="s">
+        <v>704</v>
+      </c>
+      <c r="C29" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>706</v>
+      </c>
+      <c r="B30" t="s">
+        <v>707</v>
+      </c>
+      <c r="C30" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>709</v>
+      </c>
+      <c r="B31" t="s">
+        <v>710</v>
+      </c>
+      <c r="C31" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>712</v>
+      </c>
+      <c r="B32" t="s">
+        <v>713</v>
+      </c>
+      <c r="C32" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>715</v>
+      </c>
+      <c r="B33" t="s">
+        <v>716</v>
+      </c>
+      <c r="C33" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>718</v>
+      </c>
+      <c r="B34" t="s">
+        <v>719</v>
+      </c>
+      <c r="C34" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>721</v>
+      </c>
+      <c r="B35" t="s">
+        <v>722</v>
+      </c>
+      <c r="C35" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>724</v>
+      </c>
+      <c r="B36" t="s">
+        <v>725</v>
+      </c>
+      <c r="C36" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="16.8">
+      <c r="A37" t="s">
+        <v>727</v>
+      </c>
+      <c r="B37" t="s">
+        <v>728</v>
+      </c>
+      <c r="C37" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>773</v>
+      </c>
+      <c r="B38" t="s">
+        <v>774</v>
+      </c>
+      <c r="C38" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>730</v>
+      </c>
+      <c r="B39" t="s">
+        <v>731</v>
+      </c>
+      <c r="C39" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>733</v>
+      </c>
+      <c r="B40" t="s">
+        <v>734</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>735</v>
+      </c>
+      <c r="B41" t="s">
+        <v>736</v>
+      </c>
+      <c r="C41" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>738</v>
+      </c>
+      <c r="B42" t="s">
+        <v>739</v>
+      </c>
+      <c r="C42" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>741</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>743</v>
+      </c>
+      <c r="B44" t="s">
+        <v>744</v>
+      </c>
+      <c r="C44" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="27.6">
+      <c r="A45" t="s">
+        <v>746</v>
+      </c>
+      <c r="B45" t="s">
+        <v>747</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>749</v>
+      </c>
+      <c r="B46" t="s">
+        <v>750</v>
+      </c>
+      <c r="C46" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>752</v>
+      </c>
+      <c r="B47" s="34" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>753</v>
+      </c>
+      <c r="B48" t="s">
+        <v>754</v>
+      </c>
+      <c r="C48" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>756</v>
+      </c>
+      <c r="B49" t="s">
+        <v>757</v>
+      </c>
+      <c r="C49" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>759</v>
+      </c>
+      <c r="B50" t="s">
+        <v>760</v>
+      </c>
+      <c r="C50" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="34" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="34" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="34" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B54" s="24" t="s">
         <v>1176</v>
       </c>
-      <c r="C15" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>695</v>
-      </c>
-      <c r="B16" t="s">
-        <v>696</v>
-      </c>
-      <c r="C16" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>698</v>
-      </c>
-      <c r="B17" t="s">
-        <v>699</v>
-      </c>
-      <c r="C17" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>763</v>
-      </c>
-      <c r="B18" t="s">
-        <v>764</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>766</v>
-      </c>
-      <c r="B19" t="s">
-        <v>767</v>
-      </c>
-      <c r="C19" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>769</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>770</v>
-      </c>
-      <c r="B22" t="s">
-        <v>771</v>
-      </c>
-      <c r="C22" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>773</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E23" s="30"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E24" s="30"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>701</v>
-      </c>
-      <c r="B28" t="s">
-        <v>702</v>
-      </c>
-      <c r="C28" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>704</v>
-      </c>
-      <c r="B29" t="s">
-        <v>705</v>
-      </c>
-      <c r="C29" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>707</v>
-      </c>
-      <c r="B30" t="s">
-        <v>708</v>
-      </c>
-      <c r="C30" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>710</v>
-      </c>
-      <c r="B31" t="s">
-        <v>711</v>
-      </c>
-      <c r="C31" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>713</v>
-      </c>
-      <c r="B32" t="s">
-        <v>714</v>
-      </c>
-      <c r="C32" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>716</v>
-      </c>
-      <c r="B33" t="s">
-        <v>717</v>
-      </c>
-      <c r="C33" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>719</v>
-      </c>
-      <c r="B34" t="s">
-        <v>720</v>
-      </c>
-      <c r="C34" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>722</v>
-      </c>
-      <c r="B35" t="s">
-        <v>723</v>
-      </c>
-      <c r="C35" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>725</v>
-      </c>
-      <c r="B36" t="s">
-        <v>726</v>
-      </c>
-      <c r="C36" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>728</v>
-      </c>
-      <c r="B37" t="s">
-        <v>729</v>
-      </c>
-      <c r="C37" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>774</v>
-      </c>
-      <c r="B38" t="s">
-        <v>775</v>
-      </c>
-      <c r="C38" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>731</v>
-      </c>
-      <c r="B39" t="s">
-        <v>732</v>
-      </c>
-      <c r="C39" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>734</v>
-      </c>
-      <c r="B40" t="s">
-        <v>735</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>736</v>
-      </c>
-      <c r="B41" t="s">
-        <v>737</v>
-      </c>
-      <c r="C41" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>739</v>
-      </c>
-      <c r="B42" t="s">
-        <v>740</v>
-      </c>
-      <c r="C42" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>742</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C43" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>744</v>
-      </c>
-      <c r="B44" t="s">
-        <v>745</v>
-      </c>
-      <c r="C44" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>747</v>
-      </c>
-      <c r="B45" t="s">
-        <v>748</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>750</v>
-      </c>
-      <c r="B46" t="s">
-        <v>751</v>
-      </c>
-      <c r="C46" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>753</v>
-      </c>
-      <c r="B47" s="34" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>754</v>
-      </c>
-      <c r="B48" t="s">
-        <v>755</v>
-      </c>
-      <c r="C48" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>757</v>
-      </c>
-      <c r="B49" t="s">
-        <v>758</v>
-      </c>
-      <c r="C49" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>760</v>
-      </c>
-      <c r="B50" t="s">
-        <v>761</v>
-      </c>
-      <c r="C50" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="34" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="34" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C53" s="24" t="s">
+      <c r="C54" s="24" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="34" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" s="37" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B56" s="37" t="s">
         <v>1162</v>
       </c>
-      <c r="B56" s="37" t="s">
+      <c r="C56" s="37" t="s">
         <v>1163</v>
-      </c>
-      <c r="C56" s="37" t="s">
-        <v>1164</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D23A3A-96EE-4368-AE1A-8013A53DAFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE507A95-A06C-4B04-A86B-16A464903837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="1209">
   <si>
     <t>#</t>
   </si>
@@ -2177,12 +2177,6 @@
     <t>Effect_Damage_Desc</t>
   </si>
   <si>
-    <t>Deal {0} damage.</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害</t>
-  </si>
-  <si>
     <t>Effect_Damage_Self_Desc</t>
   </si>
   <si>
@@ -2195,12 +2189,6 @@
     <t>Effect_Heal_Desc</t>
   </si>
   <si>
-    <t>Restore {0} HP.</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-  </si>
-  <si>
     <t>Effect_Draw_Desc</t>
   </si>
   <si>
@@ -2238,12 +2226,6 @@
   </si>
   <si>
     <t>Effect_Catalyze_Desc</t>
-  </si>
-  <si>
-    <t>[Card_Catalyze] {0}.</t>
-  </si>
-  <si>
-    <t>[Card_Catalyze]{0}</t>
   </si>
   <si>
     <t>Effect_Elemental_Fire_Desc</t>
@@ -2280,27 +2262,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔥</t>
-    </r>
-  </si>
-  <si>
     <t>Effect_Elemental_Water_Desc</t>
   </si>
   <si>
@@ -2335,27 +2296,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💦</t>
-    </r>
-  </si>
-  <si>
     <t>Effect_Elemental_Earth_Desc</t>
   </si>
   <si>
@@ -2414,58 +2354,6 @@
     <t>Effect_Elemental_Air_Desc</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Add {0} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-  </si>
-  <si>
     <t>Effect_Buff_Burn_Enemy_Desc</t>
   </si>
   <si>
@@ -3486,35 +3374,35 @@
   </si>
   <si>
     <t>UI_Button_Volume</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>UI_Button_CameraShakeSensitivity</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>CameraShakeSensitivity</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>镜头晃动</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Burn</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3530,7 +3418,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3546,15 +3434,15 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Lable_HighTemp_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3580,7 +3468,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3606,7 +3494,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3633,7 +3521,7 @@
       </rPr>
       <t>Sample</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3660,42 +3548,42 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Formal experiment</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>正式实验</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>在空白样本上尝试一下手头的药剂，或许会有新的收获。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>直面拥有特殊能力的造物，击败后即可进入下一阶段。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>休息一下。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Try the potionon the blank sample, maybe you will get something new.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Face the pureatures with special abilities, and defeat them to enter the next stage.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Take a break.</t>
   </si>
   <si>
     <t>Prototype_1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Prototype_2</t>
@@ -3762,21 +3650,21 @@
   </si>
   <si>
     <t>这部分是为了新教程准备的叙事大纲迭代</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tutorial_BranchTest_1</t>
   </si>
   <si>
     <t>卡牌分支测试</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
   </si>
   <si>
     <t>分支测试1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>分支测试2</t>
@@ -3786,19 +3674,19 @@
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3830,7 +3718,7 @@
       </rPr>
       <t>4</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3852,7 +3740,7 @@
       </rPr>
       <t>大地之子</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3934,7 +3822,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4015,7 +3903,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4046,100 +3934,100 @@
       </rPr>
       <t>Watcher</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
 Initial hand size: 4
 maximum hand size: 5
 Element meter capacity: 10</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 6</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>不动如山的守望者。灵魂来自大地，也将归于大地。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：6</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Sturdy</t>
@@ -4149,148 +4037,148 @@
   </si>
   <si>
     <t>坚固</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>反射</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Earth Element Bottle</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Basic Earth Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Earth Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Earth Core Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
   </si>
   <si>
     <t>Greater Earth Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
   </si>
   <si>
     <t>Vitality Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4303,120 +4191,120 @@
       </rPr>
       <t>健体药剂</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Ironbone Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
   </si>
   <si>
     <t>Shackle Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Reflection Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
   </si>
   <si>
     <t>Stoneskin Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>下一场实验：</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4424,26 +4312,28 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind</t>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>顺风</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4459,179 +4349,433 @@
       </rPr>
       <t>精炼或抽牌后顺风归零。</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Tailwind]不小于效果值时触发。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Gain tailwind by using cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>Triggers when [Card_Tailwind] is greater than or equal to the effect value.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
   </si>
   <si>
     <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Focus Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
   </si>
   <si>
     <t>Spike Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Earth Power Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Crust Potion</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Breath of Earth</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
   </si>
   <si>
     <t>Breath of the wild</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Roar of the Earth</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Calm</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Sturdy</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Reflect</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔥</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💦</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deal {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>damage.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>造成{0}点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>伤害</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Windborne_Desc</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Elemental_Air_Windborne_Desc</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Catalyze_Windborne_Desc</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Heal_Windborne_Desc</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：抓{0}张牌</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[Card_Windborne]：增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Catalyze]{0}</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Tailwind]不为0时触发。</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggers when [Card_Tailwind] is greater than 0.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]: Draw {0} cards.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Add {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Card_Windborne]: Add {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Catalyze] {0}.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore {0} HP.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]: Restore {0} HP.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4770,7 +4914,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4905,89 +5057,91 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5276,10 +5430,10 @@
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="43"/>
+      <c r="C1" s="44"/>
     </row>
     <row r="2" spans="1:3" ht="20.399999999999999">
       <c r="A2" s="12" t="s">
@@ -5352,17 +5506,17 @@
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="45"/>
+      <c r="C9" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5390,461 +5544,461 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="B2" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="C2" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="B3" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="C3" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="B4" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="C4" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="B5" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="C5" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="B6" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="C6" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="B7" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="C7" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="B9" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C9" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="B10" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="C10" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="B11" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="C11" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="B12" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="C12" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="B14" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="C14" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="B15" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="C15" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="B16" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="C16" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="B17" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="C17" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="B18" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="C18" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="B19" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="C19" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="B20" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C20" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="B21" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C21" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="B22" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C22" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="B23" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="C23" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="B24" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="C24" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="B25" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C25" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="B27" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C27" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="B28" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="C28" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="B29" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="C29" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="B30" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="C30" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="B31" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C31" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="B32" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="C32" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="B33" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="C33" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="B34" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C34" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="B35" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="C35" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="B36" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
       <c r="C36" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
       <c r="B37" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
       <c r="C37" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="B38" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="C38" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
       <c r="B39" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="C39" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="B40" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="C40" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="B41" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="C41" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1129</v>
+        <v>1119</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>1127</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="B43" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="C43" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="B44" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="C44" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="B45" t="s">
-        <v>889</v>
+        <v>879</v>
       </c>
       <c r="C45" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>1128</v>
+        <v>1118</v>
       </c>
       <c r="C46" t="s">
         <v>330</v>
@@ -5852,18 +6006,18 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="B47" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="C47" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="B48" t="s">
         <v>319</v>
@@ -5874,148 +6028,148 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="30" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
       <c r="G51" s="30"/>
       <c r="H51" s="30"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="30" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="G52" s="30"/>
       <c r="H52" s="30"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="30" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="30" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="30" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1102</v>
+        <v>1092</v>
       </c>
       <c r="G55" s="30"/>
       <c r="H55" s="30"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="30" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="36" t="s">
-        <v>1148</v>
+        <v>1138</v>
       </c>
       <c r="B57" s="36" t="s">
-        <v>1151</v>
+        <v>1141</v>
       </c>
       <c r="C57" s="36" t="s">
-        <v>1154</v>
+        <v>1144</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
     <row r="58" spans="1:8" ht="27.6">
       <c r="A58" s="36" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>1159</v>
+        <v>1148</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="36" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="36" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B60" s="36" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C60" s="37" t="s">
-        <v>1157</v>
+        <v>1143</v>
+      </c>
+      <c r="B60" s="47" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>1200</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -6024,32 +6178,32 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="B62" t="s">
-        <v>903</v>
+        <v>893</v>
       </c>
       <c r="C62" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="B63" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="C63" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B64" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="C64" t="s">
         <v>65</v>
@@ -6057,128 +6211,128 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="B65" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="C65" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
       <c r="B66" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="C66" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="B67" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="C67" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="B68" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="C68" t="s">
-        <v>921</v>
+        <v>911</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>922</v>
+        <v>912</v>
       </c>
       <c r="B69" t="s">
-        <v>923</v>
+        <v>913</v>
       </c>
       <c r="C69" t="s">
-        <v>924</v>
+        <v>914</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="B70" t="s">
-        <v>926</v>
+        <v>916</v>
       </c>
       <c r="C70" t="s">
-        <v>927</v>
+        <v>917</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>928</v>
+        <v>918</v>
       </c>
       <c r="B71" t="s">
-        <v>929</v>
+        <v>919</v>
       </c>
       <c r="C71" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="B73" t="s">
-        <v>932</v>
+        <v>922</v>
       </c>
       <c r="C73" t="s">
-        <v>927</v>
+        <v>917</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>933</v>
+        <v>923</v>
       </c>
       <c r="B74" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="C74" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
       <c r="B76" t="s">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="C76" t="s">
-        <v>938</v>
+        <v>928</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>939</v>
+        <v>929</v>
       </c>
       <c r="B77" t="s">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="C77" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>942</v>
+        <v>932</v>
       </c>
       <c r="B78" t="s">
         <v>52</v>
@@ -6189,65 +6343,65 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="B79" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="C79" t="s">
-        <v>945</v>
+        <v>935</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="B81" t="s">
-        <v>947</v>
+        <v>937</v>
       </c>
       <c r="C81" t="s">
-        <v>948</v>
+        <v>938</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>949</v>
+        <v>939</v>
       </c>
       <c r="B82" t="s">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="C82" t="s">
-        <v>951</v>
+        <v>941</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="B83" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="C83" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="B84" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="C84" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="B85" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
       <c r="C85" t="s">
         <v>39</v>
@@ -6255,109 +6409,109 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="B86" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="C86" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>963</v>
+        <v>953</v>
       </c>
       <c r="B88" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
       <c r="C88" t="s">
-        <v>965</v>
+        <v>955</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="B89" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="C89" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="B90" t="s">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="C90" t="s">
-        <v>971</v>
+        <v>961</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>972</v>
+        <v>962</v>
       </c>
       <c r="B91" t="s">
-        <v>973</v>
+        <v>963</v>
       </c>
       <c r="C91" t="s">
-        <v>974</v>
+        <v>964</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>975</v>
+        <v>965</v>
       </c>
       <c r="B92" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="C92" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="26" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="B93" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="C93" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="B94" t="s">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="C94" t="s">
-        <v>982</v>
+        <v>972</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="B95" t="s">
-        <v>984</v>
+        <v>974</v>
       </c>
       <c r="C95" t="s">
-        <v>985</v>
+        <v>975</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.6">
       <c r="A97" s="25" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
       <c r="C97" t="s">
         <v>395</v>
@@ -6365,43 +6519,43 @@
     </row>
     <row r="98" spans="1:3" ht="15.6">
       <c r="A98" s="25" t="s">
+        <v>999</v>
+      </c>
+      <c r="B98" s="26" t="s">
         <v>1009</v>
       </c>
-      <c r="B98" s="26" t="s">
-        <v>1019</v>
-      </c>
       <c r="C98" s="29" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.6">
       <c r="A99" s="26" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.6">
       <c r="A100" s="26" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B100" s="26" t="s">
         <v>1010</v>
       </c>
-      <c r="B100" s="26" t="s">
-        <v>1020</v>
-      </c>
       <c r="C100" s="28" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.6">
       <c r="A101" s="26" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="C101" t="s">
         <v>398</v>
@@ -6409,17 +6563,17 @@
     </row>
     <row r="102" spans="1:3" ht="15.6">
       <c r="A102" s="26" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B102" t="s">
         <v>1011</v>
       </c>
-      <c r="B102" t="s">
-        <v>1021</v>
-      </c>
       <c r="C102" s="28" t="s">
-        <v>1018</v>
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6447,50 +6601,50 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="B2" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
       <c r="C2" t="s">
-        <v>988</v>
+        <v>978</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
       <c r="B3" t="s">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="C3" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="B4" t="s">
-        <v>993</v>
+        <v>983</v>
       </c>
       <c r="C4" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
       <c r="B5" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="C5" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6518,119 +6672,119 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="24" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="24" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="24" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="24" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="24" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="24" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="24" t="s">
-        <v>1032</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24" t="s">
-        <v>1033</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="24" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="24" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="24" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="24" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="24" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="24" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="24" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="24" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6790,7 +6944,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -6801,13 +6955,13 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7043,17 +7197,17 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="34" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1147</v>
+        <v>1137</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>1146</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7133,18 +7287,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>1047</v>
+        <v>1037</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7743,189 +7897,189 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="33" t="s">
-        <v>1091</v>
+        <v>1081</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="33" t="s">
-        <v>1092</v>
+        <v>1082</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="33" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="33" t="s">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>1109</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="8" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>1120</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="35" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="B74" s="35" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="8" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="B75" s="35" t="s">
-        <v>1125</v>
+        <v>1115</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>1126</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="35" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
       <c r="B76" s="35" t="s">
-        <v>1133</v>
+        <v>1123</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>1134</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="8" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>1143</v>
+        <v>1133</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="8" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
       <c r="B78" s="39" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
       <c r="C78" s="39" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="8" t="s">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="B79" s="39" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="C79" s="39" t="s">
-        <v>1169</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="39" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="B80" s="39" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="39" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
       <c r="B81" s="39" t="s">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="C81" s="39" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="40" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="9" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>1116</v>
+        <v>1106</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="9" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
       <c r="B85" s="41" t="s">
-        <v>1187</v>
+        <v>1175</v>
       </c>
       <c r="C85" s="41" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="41" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="B86" s="41" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
       <c r="C86" s="41" t="s">
-        <v>1191</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7949,7 +8103,7 @@
       <c r="C90" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8013,10 +8167,10 @@
         <v>287</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8102,7 +8256,7 @@
         <v>309</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>310</v>
@@ -8110,24 +8264,24 @@
     </row>
     <row r="14" spans="1:5" ht="16.8">
       <c r="A14" s="24" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="165.6">
       <c r="A15" s="24" t="s">
-        <v>1054</v>
+        <v>1044</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>1061</v>
+        <v>1051</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8137,7 +8291,7 @@
       <c r="C17" s="32"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8168,7 +8322,7 @@
         <v>311</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="C2" t="s">
         <v>312</v>
@@ -8182,7 +8336,7 @@
         <v>314</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8234,10 +8388,10 @@
         <v>327</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8253,46 +8407,46 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>1072</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>1003</v>
+        <v>993</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="24" customFormat="1">
       <c r="A13" s="24" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8340,7 +8494,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8525,10 +8679,10 @@
         <v>383</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1051</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8587,7 +8741,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8621,7 +8775,7 @@
         <v>400</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>1055</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8772,7 +8926,7 @@
         <v>440</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1158</v>
+        <v>1147</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>441</v>
@@ -9556,14 +9710,14 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>1045</v>
+        <v>1035</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait"/>
 </worksheet>
@@ -9601,14 +9755,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -9626,582 +9780,626 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
         <v>653</v>
       </c>
-      <c r="B2" t="s">
-        <v>654</v>
-      </c>
-      <c r="C2" t="s">
-        <v>655</v>
+      <c r="B2" s="24" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>1188</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C3" t="s">
         <v>656</v>
-      </c>
-      <c r="B3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>659</v>
-      </c>
-      <c r="B4" t="s">
-        <v>660</v>
-      </c>
-      <c r="C4" t="s">
-        <v>661</v>
+        <v>657</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B5" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C5" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B7" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C7" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B8" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C8" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>674</v>
-      </c>
-      <c r="B9" t="s">
-        <v>675</v>
-      </c>
-      <c r="C9" t="s">
-        <v>676</v>
+        <v>670</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>1196</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.8">
       <c r="A10" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B10" t="s">
-        <v>678</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>679</v>
+        <v>672</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>1185</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.8">
       <c r="A11" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B11" t="s">
-        <v>681</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>682</v>
+        <v>674</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>1186</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.8">
       <c r="A12" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B12" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C12" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.8">
       <c r="A13" t="s">
-        <v>686</v>
-      </c>
-      <c r="B13" t="s">
-        <v>687</v>
-      </c>
-      <c r="C13" t="s">
-        <v>688</v>
+        <v>678</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="B14" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C14" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="C15" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="B16" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C16" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B17" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="C17" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.8">
       <c r="A18" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="B18" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="B19" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C19" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>1066</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="B22" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="C22" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1068</v>
+        <v>1058</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
       <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1064</v>
+        <v>1054</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>1113</v>
+        <v>1103</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1065</v>
+        <v>1055</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>1090</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="B28" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C28" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="B29" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="C29" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="B30" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="C30" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="B31" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="C31" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="B32" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="C32" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="B33" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C33" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="B34" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="C34" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="B35" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="C35" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="B36" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="C36" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16.8">
       <c r="A37" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="B37" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="C37" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="B38" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="C38" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="B39" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C39" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="B40" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>1111</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="B41" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="C41" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="B42" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="C42" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="C43" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="B44" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C44" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="27.6">
       <c r="A45" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="B45" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="B46" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C46" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1138</v>
+        <v>1128</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>1136</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="B48" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C48" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="B49" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="C49" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="B50" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="C50" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>1106</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="34" t="s">
-        <v>1135</v>
+        <v>1125</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="34" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="34" t="s">
-        <v>1171</v>
+        <v>1159</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>1173</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="37" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B56" s="37" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C56" s="37" t="s">
-        <v>1163</v>
+        <v>1149</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="37" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="16.8">
+      <c r="A58" s="37" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="37" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="37" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>1199</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE507A95-A06C-4B04-A86B-16A464903837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F098117E-BDBD-4334-BFD0-B5DD40458F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1244">
   <si>
     <t>#</t>
   </si>
@@ -1140,12 +1140,6 @@
     <t>Character_Scientist_Desc</t>
   </si>
   <si>
-    <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
-初始手牌数：4
-初始手牌上限：5
-元素槽容量：8</t>
-  </si>
-  <si>
     <t>Buff_Burning</t>
   </si>
   <si>
@@ -1216,12 +1210,6 @@
   </si>
   <si>
     <t>Buff_Rusted_Desc</t>
-  </si>
-  <si>
-    <t>Whenever you use a potion, you take {buffStack} damage.</t>
-  </si>
-  <si>
-    <t>你每次使用药剂时，会受到{buffStack}点伤害。</t>
   </si>
   <si>
     <t>Buff_HighReactivity</t>
@@ -3214,9 +3202,6 @@
     <t>A fast way to play cards using mouse buttons instead of drag-and-drop.</t>
   </si>
   <si>
-    <t>开启后，可以使用鼠标左键使用卡牌，鼠标右键精炼卡牌</t>
-  </si>
-  <si>
     <t>Tip_Battle_InitialDeck</t>
   </si>
   <si>
@@ -3247,12 +3232,6 @@
     <t>Tip_Battle_Discard_Desc</t>
   </si>
   <si>
-    <t>The potions you use will temporarily go here.</t>
-  </si>
-  <si>
-    <t>你使用过的药剂会暂时进入这里。</t>
-  </si>
-  <si>
     <t>Tip_Battle_Draw</t>
   </si>
   <si>
@@ -3374,35 +3353,35 @@
   </si>
   <si>
     <t>UI_Button_Volume</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>UI_Button_CameraShakeSensitivity</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>CameraShakeSensitivity</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>镜头晃动</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Burn</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3418,7 +3397,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3434,15 +3413,15 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Lable_HighTemp_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3468,7 +3447,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3494,7 +3473,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3521,7 +3500,7 @@
       </rPr>
       <t>Sample</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3548,42 +3527,42 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Formal experiment</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>正式实验</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>在空白样本上尝试一下手头的药剂，或许会有新的收获。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>直面拥有特殊能力的造物，击败后即可进入下一阶段。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>休息一下。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Try the potionon the blank sample, maybe you will get something new.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Face the pureatures with special abilities, and defeat them to enter the next stage.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Take a break.</t>
   </si>
   <si>
     <t>Prototype_1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Prototype_2</t>
@@ -3650,21 +3629,21 @@
   </si>
   <si>
     <t>这部分是为了新教程准备的叙事大纲迭代</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tutorial_BranchTest_1</t>
   </si>
   <si>
     <t>卡牌分支测试</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
   </si>
   <si>
     <t>分支测试1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>分支测试2</t>
@@ -3673,20 +3652,12 @@
     <t>Branch_Test2</t>
   </si>
   <si>
-    <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>Character_EarthMage</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3718,7 +3689,7 @@
       </rPr>
       <t>4</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3740,7 +3711,7 @@
       </rPr>
       <t>大地之子</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3822,7 +3793,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3903,7 +3874,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3934,100 +3905,100 @@
       </rPr>
       <t>Watcher</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
 Initial hand size: 4
 maximum hand size: 5
 Element meter capacity: 10</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 6</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>不动如山的守望者。灵魂来自大地，也将归于大地。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：6</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Sturdy</t>
@@ -4037,148 +4008,148 @@
   </si>
   <si>
     <t>坚固</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>反射</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Earth Element Bottle</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Basic Earth Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Earth Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Earth Core Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
   </si>
   <si>
     <t>Greater Earth Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
   </si>
   <si>
     <t>Vitality Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4191,120 +4162,120 @@
       </rPr>
       <t>健体药剂</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Ironbone Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
   </si>
   <si>
     <t>Shackle Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Reflection Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
   </si>
   <si>
     <t>Stoneskin Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>下一场实验：</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4318,190 +4289,170 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind</t>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>顺风</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>连续使用卡牌会积累顺风，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>精炼或抽牌后顺风归零。</t>
-    </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gain tailwind by using cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
   </si>
   <si>
     <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Focus Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
   </si>
   <si>
     <t>Spike Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Earth Power Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Crust Potion</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Breath of Earth</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
   </si>
   <si>
     <t>Breath of the wild</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Roar of the Earth</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Calm</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Sturdy</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Reflect</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4523,7 +4474,7 @@
       </rPr>
       <t>🔥</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4545,7 +4496,7 @@
       </rPr>
       <t>💦</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4571,7 +4522,7 @@
       </rPr>
       <t>damage.</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4597,27 +4548,27 @@
       </rPr>
       <t>伤害</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Windborne_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Elemental_Air_Windborne_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Catalyze_Windborne_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Heal_Windborne_Desc</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：抓{0}张牌</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4639,7 +4590,7 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4654,35 +4605,27 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Tailwind]不为0时触发。</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>Triggers when [Card_Tailwind] is greater than 0.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Draw {0} cards.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4714,7 +4657,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4740,35 +4683,284 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Restore {0} HP.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Restore {0} HP.</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirElementBottle</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAirPotion</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirPotion</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>TailwindPotion</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air Element Bottle</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Air Potion</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air Potion</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tailwind Potion</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>气元素瓶</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础气流药剂</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>气流药剂</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺风药剂</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Airbender</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Airbender_Desc</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Airbender</t>
+    </r>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>驭气者</t>
+    </r>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
+初始手牌数：4
+初始手牌上限：5
+元素槽容量：8</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>能驾驭气流，掌控天空。善于使用连续且优雅的招式。
+初始手牌数：5
+初始手牌上限：5
+元素槽容量：3</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Master of wind, casting in flowing, unbroken sequences.
+Initial hand size: 5
+maximum hand size: 5
+Element meter capacity: 3</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Use_Desc</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Use</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用药剂指消耗元素使用其效果，精炼药剂不属于使用。</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consuming elements to utilize its effect; refining a potion isn't regarded as using.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>上一个行动是[Player_Use]药剂时触发。</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggers when the last move is [Player_Use] a potion.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>你使用或精炼过的药剂会暂时进入这里。</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>The potions you [Player_Use] or refine will temporarily go here.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启后，可以使用鼠标左键[Player_Use]卡牌，鼠标右键精炼卡牌</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>连续[Player_Use]卡牌会积累顺风，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>精炼或抽牌后顺风归零。</t>
+    </r>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain tailwind by [Player_Use] cards consecutively. Refining or drawing resets tailwind.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledFissure</t>
+  </si>
+  <si>
+    <t>Bottled Fissure</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沟壑</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledSandstorm</t>
+  </si>
+  <si>
+    <t>Bottled Sandstorm</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沙暴</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bedrock</t>
+  </si>
+  <si>
+    <t>基岩</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScorchingSandsPotion</t>
+  </si>
+  <si>
+    <t>Scorching Sands</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>热砂药剂</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>你每次[Player_Use]药剂时，会受到{buffStack}点伤害。</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whenever you [Player_Use] a potion, you take {buffStack} damage.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4924,6 +5116,19 @@
       <name val="Segoe UI Symbol"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -5057,94 +5262,98 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5418,22 +5627,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="11"/>
+    <col min="1" max="1" width="12.8984375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="25.69921875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="30.296875" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="8.69921875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="87" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="44"/>
+      <c r="C1" s="47"/>
     </row>
     <row r="2" spans="1:3" ht="20.399999999999999">
       <c r="A2" s="12" t="s">
@@ -5506,29 +5715,29 @@
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="46"/>
+      <c r="C9" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" customWidth="1"/>
-    <col min="2" max="2" width="53.6640625" customWidth="1"/>
-    <col min="3" max="3" width="58.21875" customWidth="1"/>
+    <col min="1" max="1" width="29.296875" customWidth="1"/>
+    <col min="2" max="2" width="53.69921875" customWidth="1"/>
+    <col min="3" max="3" width="58.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5544,1036 +5753,1058 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B3" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C3" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B4" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B5" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C5" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B6" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C6" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B7" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C7" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B9" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C9" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B10" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C10" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B11" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C11" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B12" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C12" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B14" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C14" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B15" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B16" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C16" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B17" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C17" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B18" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C18" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B19" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C19" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B20" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C20" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B21" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C21" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B22" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C22" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B23" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C23" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B24" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C24" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B25" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C25" t="s">
-        <v>825</v>
+        <v>822</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="44" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>1219</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>826</v>
-      </c>
-      <c r="B27" t="s">
-        <v>827</v>
-      </c>
-      <c r="C27" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>829</v>
-      </c>
-      <c r="B28" t="s">
-        <v>830</v>
-      </c>
-      <c r="C28" t="s">
-        <v>831</v>
+      <c r="A27" s="44" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="B29" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="C29" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="B30" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="C30" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="B31" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="C31" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="B32" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C32" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="B33" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="C33" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="B34" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="C34" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="B35" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="C35" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="B36" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="C36" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="B37" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="C37" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="B38" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="C38" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="B39" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="C39" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="B40" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="C40" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="B41" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="C41" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>871</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>1117</v>
+        <v>862</v>
+      </c>
+      <c r="B42" t="s">
+        <v>863</v>
+      </c>
+      <c r="C42" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="B43" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C43" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>875</v>
-      </c>
-      <c r="B44" t="s">
-        <v>876</v>
-      </c>
-      <c r="C44" t="s">
-        <v>877</v>
+        <v>868</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B45" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C45" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>881</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>1118</v>
+        <v>872</v>
+      </c>
+      <c r="B46" t="s">
+        <v>873</v>
       </c>
       <c r="C46" t="s">
-        <v>330</v>
+        <v>874</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="B47" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="C47" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>878</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C48" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>879</v>
+      </c>
+      <c r="B49" t="s">
+        <v>880</v>
+      </c>
+      <c r="C49" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>882</v>
+      </c>
+      <c r="B50" t="s">
+        <v>318</v>
+      </c>
+      <c r="C50" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="B48" t="s">
-        <v>319</v>
-      </c>
-      <c r="C48" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="1" t="s">
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="30" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="30" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="30" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>1074</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="30" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="30" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>1093</v>
+        <v>1061</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1064</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
+        <v>1066</v>
+      </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="30" t="s">
-        <v>1091</v>
+        <v>1062</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1094</v>
+        <v>1068</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="36" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B57" s="36" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C57" s="36" t="s">
-        <v>1144</v>
+      <c r="A57" s="30" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>1084</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
-    <row r="58" spans="1:8" ht="27.6">
-      <c r="A58" s="36" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B58" s="38" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C58" s="37" t="s">
-        <v>1145</v>
+    <row r="58" spans="1:8">
+      <c r="A58" s="30" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>1086</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="36" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>1136</v>
+      </c>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+    </row>
+    <row r="60" spans="1:8" ht="27.6">
       <c r="A60" s="36" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B60" s="47" t="s">
-        <v>1201</v>
+        <v>1131</v>
+      </c>
+      <c r="B60" s="45" t="s">
+        <v>1228</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1200</v>
-      </c>
+        <v>1227</v>
+      </c>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="36"/>
-      <c r="B61" s="36"/>
+      <c r="A61" s="36" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C61" s="36" t="s">
+        <v>1132</v>
+      </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" t="s">
-        <v>892</v>
-      </c>
-      <c r="B62" t="s">
-        <v>893</v>
-      </c>
-      <c r="C62" t="s">
-        <v>894</v>
+      <c r="A62" s="36" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B62" s="44" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" t="s">
-        <v>895</v>
-      </c>
-      <c r="B63" t="s">
-        <v>896</v>
-      </c>
-      <c r="C63" t="s">
-        <v>897</v>
-      </c>
+      <c r="A63" s="36"/>
+      <c r="B63" s="36"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="B64" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>891</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="B65" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="C65" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="B66" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="C66" t="s">
-        <v>905</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B67" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="C67" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="B68" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="C68" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B69" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="C69" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="B70" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="C70" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B71" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C71" t="s">
-        <v>920</v>
+        <v>911</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>912</v>
+      </c>
+      <c r="B72" t="s">
+        <v>913</v>
+      </c>
+      <c r="C72" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="B73" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="C73" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>923</v>
-      </c>
-      <c r="B74" t="s">
-        <v>924</v>
-      </c>
-      <c r="C74" t="s">
-        <v>925</v>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>918</v>
+      </c>
+      <c r="B75" t="s">
+        <v>919</v>
+      </c>
+      <c r="C75" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="B76" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="C76" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>929</v>
-      </c>
-      <c r="B77" t="s">
-        <v>930</v>
-      </c>
-      <c r="C77" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="B78" t="s">
-        <v>52</v>
+        <v>924</v>
       </c>
       <c r="C78" t="s">
-        <v>53</v>
+        <v>925</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="B79" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="C79" t="s">
-        <v>935</v>
+        <v>928</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>929</v>
+      </c>
+      <c r="B80" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="B81" t="s">
-        <v>937</v>
-      </c>
-      <c r="C81" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
-        <v>939</v>
-      </c>
-      <c r="B82" t="s">
-        <v>940</v>
-      </c>
-      <c r="C82" t="s">
-        <v>941</v>
+        <v>931</v>
+      </c>
+      <c r="C81" s="44" t="s">
+        <v>1226</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>942</v>
+        <v>932</v>
       </c>
       <c r="B83" t="s">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="C83" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>945</v>
+        <v>935</v>
       </c>
       <c r="B84" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="C84" t="s">
-        <v>947</v>
+        <v>937</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>948</v>
+        <v>938</v>
       </c>
       <c r="B85" t="s">
-        <v>949</v>
+        <v>939</v>
       </c>
       <c r="C85" t="s">
-        <v>39</v>
+        <v>940</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>950</v>
-      </c>
-      <c r="B86" t="s">
-        <v>951</v>
-      </c>
-      <c r="C86" t="s">
-        <v>952</v>
+        <v>941</v>
+      </c>
+      <c r="B86" s="44" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C86" s="44" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>942</v>
+      </c>
+      <c r="B87" t="s">
+        <v>943</v>
+      </c>
+      <c r="C87" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B88" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="C88" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
-        <v>956</v>
-      </c>
-      <c r="B89" t="s">
-        <v>957</v>
-      </c>
-      <c r="C89" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B90" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="C90" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="B91" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="C91" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="B92" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="C92" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="26" t="s">
-        <v>998</v>
+      <c r="A93" t="s">
+        <v>956</v>
       </c>
       <c r="B93" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="C93" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="B94" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="C94" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" t="s">
-        <v>973</v>
+      <c r="A95" s="26" t="s">
+        <v>992</v>
       </c>
       <c r="B95" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
       <c r="C95" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="15.6">
-      <c r="A97" s="25" t="s">
-        <v>995</v>
-      </c>
-      <c r="B97" s="27" t="s">
-        <v>1002</v>
+        <v>963</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>964</v>
+      </c>
+      <c r="B96" t="s">
+        <v>965</v>
+      </c>
+      <c r="C96" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>967</v>
+      </c>
+      <c r="B97" t="s">
+        <v>968</v>
       </c>
       <c r="C97" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.6">
-      <c r="A98" s="25" t="s">
-        <v>999</v>
-      </c>
-      <c r="B98" s="26" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C98" s="29" t="s">
-        <v>1006</v>
+        <v>969</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.6">
-      <c r="A99" s="26" t="s">
+      <c r="A99" s="25" t="s">
+        <v>989</v>
+      </c>
+      <c r="B99" s="27" t="s">
         <v>996</v>
       </c>
-      <c r="B99" s="26" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>1005</v>
+      <c r="C99" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.6">
-      <c r="A100" s="26" t="s">
+      <c r="A100" s="25" t="s">
+        <v>993</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C100" s="29" t="s">
         <v>1000</v>
-      </c>
-      <c r="B100" s="26" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C100" s="28" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.6">
       <c r="A101" s="26" t="s">
-        <v>997</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C101" t="s">
-        <v>398</v>
+        <v>990</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>998</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.6">
       <c r="A102" s="26" t="s">
+        <v>994</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C102" s="28" t="s">
         <v>1001</v>
       </c>
-      <c r="B102" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>1008</v>
+    </row>
+    <row r="103" spans="1:3" ht="15.6">
+      <c r="A103" s="26" t="s">
+        <v>991</v>
+      </c>
+      <c r="B103" s="27" t="s">
+        <v>997</v>
+      </c>
+      <c r="C103" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15.6">
+      <c r="A104" s="26" t="s">
+        <v>995</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>1002</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6581,10 +6812,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="1" max="1" width="29.296875" customWidth="1"/>
+    <col min="2" max="2" width="31.796875" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6601,50 +6832,50 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B2" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C2" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="B3" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="C3" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="B4" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="C4" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B5" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="C5" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6654,9 +6885,9 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.69921875" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="67.77734375" customWidth="1"/>
+    <col min="3" max="3" width="67.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6672,119 +6903,119 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="24" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="24" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="24" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="24" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="24" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="24" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="24" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="24" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="24" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="24" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="24" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="24" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="24" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="24" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="24" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6795,8 +7026,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.296875" customWidth="1"/>
+    <col min="3" max="3" width="15.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6944,7 +7175,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -6955,13 +7186,13 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7096,7 +7327,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="151.80000000000001">
+    <row r="32" spans="1:3" ht="138">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -7197,29 +7428,29 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="34" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
       <c r="C42" s="34" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.09765625" customWidth="1"/>
+    <col min="2" max="2" width="16.296875" customWidth="1"/>
+    <col min="3" max="3" width="15.296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7287,18 +7518,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7897,213 +8128,366 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="33" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="33" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="33" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="33" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="8" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="35" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="B74" s="35" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="8" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
       <c r="B75" s="35" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="35" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
       <c r="B76" s="35" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="8" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="8" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B78" s="39" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C78" s="39" t="s">
-        <v>1153</v>
+        <v>1142</v>
+      </c>
+      <c r="B78" s="38" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C78" s="38" t="s">
+        <v>1143</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="8" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B79" s="38" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C79" s="38" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="38" t="s">
         <v>1155</v>
       </c>
-      <c r="B79" s="39" t="s">
+      <c r="B80" s="38" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C80" s="38" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="38" t="s">
         <v>1156</v>
       </c>
-      <c r="C79" s="39" t="s">
+      <c r="B81" s="38" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C81" s="38" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="39" t="s">
         <v>1157</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="39" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B80" s="39" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C80" s="39" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="39" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B81" s="39" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C81" s="39" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="40" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B82" s="40" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C82" s="39" t="s">
-        <v>1173</v>
+      <c r="B82" s="39" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C82" s="38" t="s">
+        <v>1163</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="9" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="9" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B85" s="41" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C85" s="41" t="s">
-        <v>1176</v>
+        <v>1164</v>
+      </c>
+      <c r="B85" s="40" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C85" s="40" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="41" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B86" s="41" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C86" s="41" t="s">
-        <v>1179</v>
+      <c r="A86" s="40" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B86" s="40" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C86" s="40" t="s">
+        <v>1169</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
+      <c r="A87" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B87" s="50" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C87" s="50" t="s">
+        <v>1231</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
+      <c r="A88" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B88" s="50" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C88" s="50" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
+      <c r="A89" s="9" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B89" s="50" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C89" s="50" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
+      <c r="A90" s="9" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C90" s="50" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="33" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B92" s="33" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C92" s="33" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="33" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C93" s="33" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="33" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B94" s="33" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C94" s="33" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="33" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B95" s="33" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C95" s="33" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="35"/>
+      <c r="B98" s="35"/>
+      <c r="C98" s="35"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="8"/>
+      <c r="B99" s="35"/>
+      <c r="C99" s="35"/>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="35"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="35"/>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="8"/>
+      <c r="B101" s="35"/>
+      <c r="C101" s="35"/>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="8"/>
+      <c r="B102" s="38"/>
+      <c r="C102" s="38"/>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="8"/>
+      <c r="B103" s="38"/>
+      <c r="C103" s="38"/>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="38"/>
+      <c r="B104" s="38"/>
+      <c r="C104" s="38"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="38"/>
+      <c r="B105" s="38"/>
+      <c r="C105" s="38"/>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="39"/>
+      <c r="B106" s="39"/>
+      <c r="C106" s="38"/>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="9"/>
+      <c r="B109" s="40"/>
+      <c r="C109" s="40"/>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="40"/>
+      <c r="B110" s="40"/>
+      <c r="C110" s="40"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="9"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="9"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8113,9 +8497,9 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="16.796875" customWidth="1"/>
+    <col min="2" max="2" width="16.296875" customWidth="1"/>
+    <col min="3" max="3" width="17.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8167,10 +8551,10 @@
         <v>287</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8206,7 +8590,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="167.4">
+    <row r="9" spans="1:5" ht="153.6">
       <c r="A9" t="s">
         <v>297</v>
       </c>
@@ -8229,7 +8613,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="165.6">
+    <row r="11" spans="1:5" ht="151.80000000000001">
       <c r="A11" t="s">
         <v>303</v>
       </c>
@@ -8251,47 +8635,63 @@
         <v>308</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="234.6">
+    <row r="13" spans="1:5" ht="207">
       <c r="A13" t="s">
         <v>309</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>310</v>
+        <v>1042</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>1213</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.8">
       <c r="A14" s="24" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="151.80000000000001">
+      <c r="A15" s="24" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B15" s="45" t="s">
         <v>1043</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="165.6">
-      <c r="A15" s="24" t="s">
+      <c r="C15" s="32" t="s">
         <v>1044</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="C16" s="30"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="32"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.6">
+      <c r="A16" s="24" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="124.2">
+      <c r="A17" s="24" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>1214</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8301,9 +8701,9 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.8984375" customWidth="1"/>
+    <col min="2" max="2" width="46.8984375" customWidth="1"/>
+    <col min="3" max="3" width="41.296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8319,182 +8719,182 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>988</v>
+      </c>
+      <c r="C2" t="s">
         <v>311</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>994</v>
-      </c>
-      <c r="C2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C3" s="24" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4" t="s">
         <v>315</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>316</v>
-      </c>
-      <c r="C4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5" t="s">
         <v>318</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>319</v>
-      </c>
-      <c r="C5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B6" t="s">
         <v>321</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>322</v>
-      </c>
-      <c r="C6" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" t="s">
         <v>324</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>325</v>
-      </c>
-      <c r="C7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" t="s">
         <v>328</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>329</v>
-      </c>
-      <c r="C9" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="24" customFormat="1">
       <c r="A13" s="24" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" t="s">
         <v>331</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>332</v>
-      </c>
-      <c r="C15" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>334</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C16" t="s">
-        <v>336</v>
+        <v>333</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.9" customHeight="1">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B17" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C18" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8504,9 +8904,9 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="11.796875" customWidth="1"/>
+    <col min="2" max="2" width="10.8984375" customWidth="1"/>
+    <col min="3" max="3" width="9.296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8522,18 +8922,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -8544,204 +8944,204 @@
     </row>
     <row r="4" spans="1:3" ht="13.35" customHeight="1">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B9" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C11" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B12" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C12" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B13" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C13" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B15" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C15" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B16" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C16" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1042</v>
+        <v>1243</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1041</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B19" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C19" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B20" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C20" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="27.6">
       <c r="A23" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C23" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="27.6">
       <c r="A24" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C24" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8751,9 +9151,9 @@
   <dimension ref="A1:D96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="32.33203125" customWidth="1"/>
-    <col min="2" max="2" width="76.77734375" customWidth="1"/>
-    <col min="3" max="3" width="54.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.296875" customWidth="1"/>
+    <col min="2" max="2" width="76.796875" customWidth="1"/>
+    <col min="3" max="3" width="54.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8769,508 +9169,508 @@
     </row>
     <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B10" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B11" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B12" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B15" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1147</v>
+        <v>1138</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B17" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B18" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B19" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B20" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B21" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B22" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B23" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B24" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B26" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B27" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B28" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B29" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B30" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B31" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B32" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B33" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B34" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B36" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B37" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B38" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B39" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B40" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B41" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B42" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B44">
         <v>111</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B45">
         <v>111</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B47" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B48" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B49" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9278,446 +9678,446 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B51" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B52" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C52" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B53" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C53" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B54" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C54" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B55" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B56" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B57" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C57" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B58" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C58" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B60" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C60" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B61" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C61" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B62" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C62" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B63" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C63" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B64" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C64" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B65" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C65" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B67" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B69" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C69" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B70" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C70" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B71" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C71" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B72" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C72" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B73" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C73" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B74" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C74" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B76" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C76" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D76" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B77" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C77" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B78" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C78" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B79" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C79" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B80" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C80" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B81" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C81" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B82" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C82" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C83" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B84" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C84" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B85" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C85" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B86" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C86" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B87" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C87" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B88" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C88" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B90" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C90" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B91" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C91" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B92" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C92" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B93" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C93" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B94" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C94" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait"/>
 </worksheet>
@@ -9728,8 +10128,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="3" max="3" width="69.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.19921875" customWidth="1"/>
+    <col min="3" max="3" width="69.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9745,17 +10145,17 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9765,8 +10165,8 @@
   <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" customWidth="1"/>
-    <col min="2" max="3" width="53.6640625" customWidth="1"/>
+    <col min="1" max="1" width="32.69921875" customWidth="1"/>
+    <col min="2" max="3" width="53.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9782,624 +10182,624 @@
     </row>
     <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B3" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B5" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B8" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C8" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1205</v>
+        <v>1193</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.8">
       <c r="A10" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B10" t="s">
-        <v>672</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>1185</v>
+        <v>669</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.8">
       <c r="A11" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B11" t="s">
-        <v>674</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>1186</v>
+        <v>671</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>1176</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.8">
       <c r="A12" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B12" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C12" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.8">
       <c r="A13" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B14" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C14" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="C15" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B16" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C16" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B17" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C17" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.8">
       <c r="A18" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B18" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B19" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C19" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B22" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C22" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
       <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B28" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C28" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B29" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C29" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B30" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C30" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B31" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C31" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B32" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C32" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B33" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C33" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B34" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C34" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B35" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C35" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B36" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C36" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16.8">
       <c r="A37" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B37" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C37" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B38" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C38" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B39" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C39" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B40" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B41" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C41" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B42" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C42" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
       <c r="C43" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B44" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C44" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="27.6">
       <c r="A45" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B45" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B46" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C46" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B48" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C48" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B49" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C49" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B50" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C50" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="34" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="34" t="s">
-        <v>1158</v>
+        <v>1148</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>1160</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="34" t="s">
-        <v>1159</v>
+        <v>1149</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="37" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>1151</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="37" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.8">
       <c r="A58" s="37" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>1204</v>
+        <v>1192</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="37" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="37" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F098117E-BDBD-4334-BFD0-B5DD40458F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC9D6A3-D3D7-478F-99BE-84EC1DAA17B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -819,9 +819,6 @@
     <t>Bottled Swirl</t>
   </si>
   <si>
-    <t>瓶装漩涡</t>
-  </si>
-  <si>
     <t>BottledOasis</t>
   </si>
   <si>
@@ -3353,35 +3350,35 @@
   </si>
   <si>
     <t>UI_Button_Volume</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>UI_Button_CameraShakeSensitivity</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>CameraShakeSensitivity</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>镜头晃动</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Burn</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3397,7 +3394,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3413,15 +3410,15 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Lable_HighTemp_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3447,7 +3444,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3473,7 +3470,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3500,7 +3497,7 @@
       </rPr>
       <t>Sample</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3527,42 +3524,42 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Formal experiment</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>正式实验</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>在空白样本上尝试一下手头的药剂，或许会有新的收获。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>直面拥有特殊能力的造物，击败后即可进入下一阶段。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>休息一下。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Try the potionon the blank sample, maybe you will get something new.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Face the pureatures with special abilities, and defeat them to enter the next stage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Take a break.</t>
   </si>
   <si>
     <t>Prototype_1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Prototype_2</t>
@@ -3629,21 +3626,21 @@
   </si>
   <si>
     <t>这部分是为了新教程准备的叙事大纲迭代</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tutorial_BranchTest_1</t>
   </si>
   <si>
     <t>卡牌分支测试</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
   </si>
   <si>
     <t>分支测试1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>分支测试2</t>
@@ -3653,11 +3650,11 @@
   </si>
   <si>
     <t>Character_EarthMage</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3689,7 +3686,7 @@
       </rPr>
       <t>4</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3711,7 +3708,7 @@
       </rPr>
       <t>大地之子</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3793,7 +3790,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3874,7 +3871,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3905,100 +3902,100 @@
       </rPr>
       <t>Watcher</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
 Initial hand size: 4
 maximum hand size: 5
 Element meter capacity: 10</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 6</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>不动如山的守望者。灵魂来自大地，也将归于大地。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：6</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Sturdy</t>
@@ -4008,148 +4005,148 @@
   </si>
   <si>
     <t>坚固</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>反射</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Earth Element Bottle</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Basic Earth Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Earth Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Earth Core Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
   </si>
   <si>
     <t>Greater Earth Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
   </si>
   <si>
     <t>Vitality Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4162,120 +4159,120 @@
       </rPr>
       <t>健体药剂</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Ironbone Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
   </si>
   <si>
     <t>Shackle Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Reflection Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
   </si>
   <si>
     <t>Stoneskin Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>下一场实验：</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4289,170 +4286,170 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind</t>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>顺风</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
   </si>
   <si>
     <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Focus Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
   </si>
   <si>
     <t>Spike Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Earth Power Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Crust Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Breath of Earth</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
   </si>
   <si>
     <t>Breath of the wild</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Roar of the Earth</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Calm</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Sturdy</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Reflect</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4474,7 +4471,7 @@
       </rPr>
       <t>🔥</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4496,7 +4493,7 @@
       </rPr>
       <t>💦</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4522,7 +4519,7 @@
       </rPr>
       <t>damage.</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4548,27 +4545,27 @@
       </rPr>
       <t>伤害</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Windborne_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Elemental_Air_Windborne_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Catalyze_Windborne_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Heal_Windborne_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：抓{0}张牌</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4590,7 +4587,7 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4605,27 +4602,27 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Draw {0} cards.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4657,7 +4654,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4683,79 +4680,79 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Restore {0} HP.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Restore {0} HP.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>AirElementBottle</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>BasicAirPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>AirPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>TailwindPotion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Air Element Bottle</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Basic Air Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Air Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind Potion</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>气元素瓶</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>基础气流药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>气流药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>顺风药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Character_Airbender</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Character_Airbender_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4776,7 +4773,7 @@
       </rPr>
       <t>Airbender</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4793,72 +4790,72 @@
       </rPr>
       <t>驭气者</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
 初始手牌数：4
 初始手牌上限：5
 元素槽容量：8</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>能驾驭气流，掌控天空。善于使用连续且优雅的招式。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：3</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Master of wind, casting in flowing, unbroken sequences.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 3</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use_Desc</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>使用药剂指消耗元素使用其效果，精炼药剂不属于使用。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>使用</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Use</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Consuming elements to utilize its effect; refining a potion isn't regarded as using.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>上一个行动是[Player_Use]药剂时触发。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Triggers when the last move is [Player_Use] a potion.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>你使用或精炼过的药剂会暂时进入这里。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>The potions you [Player_Use] or refine will temporarily go here.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>开启后，可以使用鼠标左键[Player_Use]卡牌，鼠标右键精炼卡牌</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4874,79 +4871,90 @@
       </rPr>
       <t>精炼或抽牌后顺风归零。</t>
     </r>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Gain tailwind by [Player_Use] cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>BottledFissure</t>
   </si>
   <si>
     <t>Bottled Fissure</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沟壑</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>BottledSandstorm</t>
   </si>
   <si>
     <t>Bottled Sandstorm</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沙暴</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Bedrock</t>
   </si>
   <si>
     <t>基岩</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>ScorchingSandsPotion</t>
   </si>
   <si>
     <t>Scorching Sands</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>热砂药剂</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>你每次[Player_Use]药剂时，会受到{buffStack}点伤害。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Whenever you [Player_Use] a potion, you take {buffStack} damage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装涡旋</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5262,95 +5270,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5639,10 +5648,10 @@
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="2" spans="1:3" ht="20.399999999999999">
       <c r="A2" s="12" t="s">
@@ -5715,17 +5724,17 @@
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="49"/>
+      <c r="C9" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5753,654 +5762,654 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B2" t="s">
         <v>763</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>764</v>
-      </c>
-      <c r="C2" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B3" t="s">
         <v>766</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>767</v>
-      </c>
-      <c r="C3" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>768</v>
+      </c>
+      <c r="B4" t="s">
         <v>769</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>770</v>
-      </c>
-      <c r="C4" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B5" t="s">
         <v>772</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>773</v>
-      </c>
-      <c r="C5" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B6" t="s">
         <v>775</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>776</v>
-      </c>
-      <c r="C6" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>777</v>
+      </c>
+      <c r="B7" t="s">
         <v>778</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>779</v>
-      </c>
-      <c r="C7" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>780</v>
+      </c>
+      <c r="B9" t="s">
         <v>781</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>782</v>
-      </c>
-      <c r="C9" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>783</v>
+      </c>
+      <c r="B10" t="s">
         <v>784</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>785</v>
-      </c>
-      <c r="C10" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>786</v>
+      </c>
+      <c r="B11" t="s">
         <v>787</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>788</v>
-      </c>
-      <c r="C11" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B12" t="s">
         <v>790</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>791</v>
-      </c>
-      <c r="C12" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>792</v>
+      </c>
+      <c r="B14" t="s">
         <v>793</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>794</v>
-      </c>
-      <c r="C14" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>795</v>
+      </c>
+      <c r="B15" t="s">
         <v>796</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>797</v>
-      </c>
-      <c r="C15" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>798</v>
+      </c>
+      <c r="B16" t="s">
         <v>799</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>800</v>
-      </c>
-      <c r="C16" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>801</v>
+      </c>
+      <c r="B17" t="s">
         <v>802</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>803</v>
-      </c>
-      <c r="C17" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>804</v>
+      </c>
+      <c r="B18" t="s">
         <v>805</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>806</v>
-      </c>
-      <c r="C18" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>807</v>
+      </c>
+      <c r="B19" t="s">
         <v>808</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>809</v>
-      </c>
-      <c r="C19" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>810</v>
+      </c>
+      <c r="B20" t="s">
         <v>811</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>812</v>
-      </c>
-      <c r="C20" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B21" t="s">
+        <v>811</v>
+      </c>
+      <c r="C21" t="s">
         <v>812</v>
-      </c>
-      <c r="C21" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B22" t="s">
+        <v>811</v>
+      </c>
+      <c r="C22" t="s">
         <v>812</v>
-      </c>
-      <c r="C22" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B23" t="s">
+        <v>811</v>
+      </c>
+      <c r="C23" t="s">
         <v>812</v>
-      </c>
-      <c r="C23" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>816</v>
+      </c>
+      <c r="B24" t="s">
         <v>817</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>818</v>
-      </c>
-      <c r="C24" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>819</v>
+      </c>
+      <c r="B25" t="s">
         <v>820</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>821</v>
-      </c>
-      <c r="C25" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="44" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="44" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>822</v>
+      </c>
+      <c r="B29" t="s">
         <v>823</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>824</v>
-      </c>
-      <c r="C29" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>825</v>
+      </c>
+      <c r="B30" t="s">
         <v>826</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>827</v>
-      </c>
-      <c r="C30" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>828</v>
+      </c>
+      <c r="B31" t="s">
         <v>829</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>830</v>
-      </c>
-      <c r="C31" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>831</v>
+      </c>
+      <c r="B32" t="s">
         <v>832</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>833</v>
-      </c>
-      <c r="C32" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>834</v>
+      </c>
+      <c r="B33" t="s">
         <v>835</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>836</v>
-      </c>
-      <c r="C33" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>837</v>
+      </c>
+      <c r="B34" t="s">
         <v>838</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>839</v>
-      </c>
-      <c r="C34" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>840</v>
+      </c>
+      <c r="B35" t="s">
         <v>841</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>842</v>
-      </c>
-      <c r="C35" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>843</v>
+      </c>
+      <c r="B36" t="s">
         <v>844</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>845</v>
-      </c>
-      <c r="C36" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>846</v>
+      </c>
+      <c r="B37" t="s">
         <v>847</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>848</v>
-      </c>
-      <c r="C37" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>849</v>
+      </c>
+      <c r="B38" t="s">
         <v>850</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>851</v>
-      </c>
-      <c r="C38" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>852</v>
+      </c>
+      <c r="B39" t="s">
         <v>853</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>854</v>
-      </c>
-      <c r="C39" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>855</v>
+      </c>
+      <c r="B40" t="s">
         <v>856</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>857</v>
-      </c>
-      <c r="C40" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>858</v>
+      </c>
+      <c r="B41" t="s">
         <v>859</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>860</v>
-      </c>
-      <c r="C41" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>861</v>
+      </c>
+      <c r="B42" t="s">
         <v>862</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>863</v>
-      </c>
-      <c r="C42" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>864</v>
+      </c>
+      <c r="B43" t="s">
         <v>865</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>866</v>
-      </c>
-      <c r="C43" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>868</v>
+      </c>
+      <c r="B45" t="s">
         <v>869</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>870</v>
-      </c>
-      <c r="C45" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>871</v>
+      </c>
+      <c r="B46" t="s">
         <v>872</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>873</v>
-      </c>
-      <c r="C46" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>874</v>
+      </c>
+      <c r="B47" t="s">
         <v>875</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>876</v>
-      </c>
-      <c r="C47" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
+        <v>878</v>
+      </c>
+      <c r="B49" t="s">
         <v>879</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>880</v>
-      </c>
-      <c r="C49" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B50" t="s">
+        <v>317</v>
+      </c>
+      <c r="C50" t="s">
         <v>318</v>
-      </c>
-      <c r="C50" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="30" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G53" s="30"/>
       <c r="H53" s="30"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="30" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="30" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="30" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="30" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="36" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="30"/>
     </row>
     <row r="60" spans="1:8" ht="27.6">
       <c r="A60" s="36" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G60" s="30"/>
       <c r="H60" s="30"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="36" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="36" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -6409,32 +6418,32 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
+        <v>888</v>
+      </c>
+      <c r="B64" t="s">
         <v>889</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>890</v>
-      </c>
-      <c r="C64" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>891</v>
+      </c>
+      <c r="B65" t="s">
         <v>892</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>893</v>
-      </c>
-      <c r="C65" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
+        <v>894</v>
+      </c>
+      <c r="B66" t="s">
         <v>895</v>
-      </c>
-      <c r="B66" t="s">
-        <v>896</v>
       </c>
       <c r="C66" t="s">
         <v>65</v>
@@ -6442,128 +6451,128 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>896</v>
+      </c>
+      <c r="B67" t="s">
         <v>897</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>898</v>
-      </c>
-      <c r="C67" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>899</v>
+      </c>
+      <c r="B68" t="s">
         <v>900</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>901</v>
-      </c>
-      <c r="C68" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>902</v>
+      </c>
+      <c r="B69" t="s">
         <v>903</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>904</v>
-      </c>
-      <c r="C69" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>905</v>
+      </c>
+      <c r="B70" t="s">
         <v>906</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>907</v>
-      </c>
-      <c r="C70" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>908</v>
+      </c>
+      <c r="B71" t="s">
         <v>909</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>910</v>
-      </c>
-      <c r="C71" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>911</v>
+      </c>
+      <c r="B72" t="s">
         <v>912</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>913</v>
-      </c>
-      <c r="C72" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>914</v>
+      </c>
+      <c r="B73" t="s">
         <v>915</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>916</v>
-      </c>
-      <c r="C73" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
+        <v>917</v>
+      </c>
+      <c r="B75" t="s">
         <v>918</v>
       </c>
-      <c r="B75" t="s">
-        <v>919</v>
-      </c>
       <c r="C75" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>919</v>
+      </c>
+      <c r="B76" t="s">
         <v>920</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>921</v>
-      </c>
-      <c r="C76" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
+        <v>922</v>
+      </c>
+      <c r="B78" t="s">
         <v>923</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>924</v>
-      </c>
-      <c r="C78" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
+        <v>925</v>
+      </c>
+      <c r="B79" t="s">
         <v>926</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>927</v>
-      </c>
-      <c r="C79" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B80" t="s">
         <v>52</v>
@@ -6574,65 +6583,65 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
+        <v>929</v>
+      </c>
+      <c r="B81" t="s">
         <v>930</v>
       </c>
-      <c r="B81" t="s">
-        <v>931</v>
-      </c>
       <c r="C81" s="44" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
+        <v>931</v>
+      </c>
+      <c r="B83" t="s">
         <v>932</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>933</v>
-      </c>
-      <c r="C83" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
+        <v>934</v>
+      </c>
+      <c r="B84" t="s">
         <v>935</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>936</v>
-      </c>
-      <c r="C84" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>937</v>
+      </c>
+      <c r="B85" t="s">
         <v>938</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>939</v>
-      </c>
-      <c r="C85" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B86" s="44" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C86" s="44" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
+        <v>941</v>
+      </c>
+      <c r="B87" t="s">
         <v>942</v>
-      </c>
-      <c r="B87" t="s">
-        <v>943</v>
       </c>
       <c r="C87" t="s">
         <v>39</v>
@@ -6640,171 +6649,171 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
+        <v>943</v>
+      </c>
+      <c r="B88" t="s">
         <v>944</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>945</v>
-      </c>
-      <c r="C88" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
+        <v>946</v>
+      </c>
+      <c r="B90" t="s">
         <v>947</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>948</v>
-      </c>
-      <c r="C90" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
+        <v>949</v>
+      </c>
+      <c r="B91" t="s">
         <v>950</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>951</v>
-      </c>
-      <c r="C91" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
+        <v>952</v>
+      </c>
+      <c r="B92" t="s">
         <v>953</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>954</v>
-      </c>
-      <c r="C92" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
+        <v>955</v>
+      </c>
+      <c r="B93" t="s">
         <v>956</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>957</v>
-      </c>
-      <c r="C93" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>958</v>
+      </c>
+      <c r="B94" t="s">
         <v>959</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>960</v>
-      </c>
-      <c r="C94" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="26" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B95" t="s">
+        <v>961</v>
+      </c>
+      <c r="C95" t="s">
         <v>962</v>
-      </c>
-      <c r="C95" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
+        <v>963</v>
+      </c>
+      <c r="B96" t="s">
         <v>964</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>965</v>
-      </c>
-      <c r="C96" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
+        <v>966</v>
+      </c>
+      <c r="B97" t="s">
         <v>967</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>968</v>
-      </c>
-      <c r="C97" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.6">
       <c r="A99" s="25" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C99" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.6">
       <c r="A100" s="25" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B100" s="26" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C100" s="29" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.6">
       <c r="A101" s="26" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B101" s="26" t="s">
+        <v>997</v>
+      </c>
+      <c r="C101" s="28" t="s">
         <v>998</v>
-      </c>
-      <c r="C101" s="28" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.6">
       <c r="A102" s="26" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B102" s="26" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.6">
       <c r="A103" s="26" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C103" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.6">
       <c r="A104" s="26" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B104" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6832,50 +6841,50 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B2" t="s">
         <v>970</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>971</v>
-      </c>
-      <c r="C2" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>972</v>
+      </c>
+      <c r="B3" t="s">
         <v>973</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>974</v>
-      </c>
-      <c r="C3" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>975</v>
+      </c>
+      <c r="B4" t="s">
         <v>976</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>977</v>
-      </c>
-      <c r="C4" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>978</v>
+      </c>
+      <c r="B5" t="s">
         <v>979</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>980</v>
       </c>
-      <c r="C5" t="s">
-        <v>981</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6903,119 +6912,119 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="24" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="24" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="24" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="24" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="24" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="24" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="24" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="24" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="24" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="24" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="24" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="24" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7175,7 +7184,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -7186,13 +7195,13 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
+        <v>982</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>983</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="C15" s="24" t="s">
         <v>984</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7428,17 +7437,17 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="34" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C42" s="34" t="s">
         <v>1127</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>1128</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7518,18 +7527,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>1031</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7968,437 +7977,437 @@
       <c r="B51" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>243</v>
+      <c r="C51" s="52" t="s">
+        <v>1243</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="C52" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="C57" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>257</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B62" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="C62" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C63" s="9" t="s">
         <v>269</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C64" s="9" t="s">
         <v>271</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B65" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="C65" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C66" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="33" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="33" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="33" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B71" s="33" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C71" s="33" t="s">
         <v>1090</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="8" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>1101</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="35" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B74" s="35" t="s">
         <v>1103</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="C74" s="35" t="s">
         <v>1104</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B75" s="35" t="s">
         <v>1106</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="C75" s="35" t="s">
         <v>1107</v>
-      </c>
-      <c r="C75" s="35" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="35" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B76" s="35" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C76" s="35" t="s">
         <v>1115</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B77" s="35" t="s">
         <v>1124</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>1125</v>
-      </c>
-      <c r="C77" s="35" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B78" s="38" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C78" s="38" t="s">
         <v>1142</v>
-      </c>
-      <c r="B78" s="38" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C78" s="38" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="8" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B79" s="38" t="s">
         <v>1145</v>
       </c>
-      <c r="B79" s="38" t="s">
+      <c r="C79" s="38" t="s">
         <v>1146</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="38" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="38" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="39" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="9" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>1097</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>1098</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="9" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B85" s="40" t="s">
         <v>1164</v>
       </c>
-      <c r="B85" s="40" t="s">
+      <c r="C85" s="40" t="s">
         <v>1165</v>
-      </c>
-      <c r="C85" s="40" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="40" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B86" s="40" t="s">
         <v>1167</v>
       </c>
-      <c r="B86" s="40" t="s">
+      <c r="C86" s="40" t="s">
         <v>1168</v>
-      </c>
-      <c r="C86" s="40" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B87" s="46" t="s">
         <v>1229</v>
       </c>
-      <c r="B87" s="50" t="s">
+      <c r="C87" s="46" t="s">
         <v>1230</v>
-      </c>
-      <c r="C87" s="50" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B88" s="46" t="s">
         <v>1232</v>
       </c>
-      <c r="B88" s="50" t="s">
+      <c r="C88" s="46" t="s">
         <v>1233</v>
-      </c>
-      <c r="C88" s="50" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="9" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B89" s="46" t="s">
         <v>1237</v>
       </c>
-      <c r="B89" s="50" t="s">
+      <c r="C89" s="46" t="s">
         <v>1238</v>
-      </c>
-      <c r="C89" s="50" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C90" s="46" t="s">
         <v>1235</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C90" s="50" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="33" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="33" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="33" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="33" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C95" s="33" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -8487,7 +8496,7 @@
       <c r="C114" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8515,183 +8524,183 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B2" t="s">
         <v>278</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>279</v>
-      </c>
-      <c r="C2" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B3" t="s">
         <v>281</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>282</v>
-      </c>
-      <c r="C3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" t="s">
         <v>284</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>285</v>
-      </c>
-      <c r="C4" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="265.2">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>1039</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
         <v>288</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>289</v>
-      </c>
-      <c r="C6" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B7" t="s">
         <v>291</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>292</v>
-      </c>
-      <c r="C7" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.8">
       <c r="A8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="153.6">
       <c r="A9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" ht="16.8">
       <c r="A10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>301</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="151.80000000000001">
       <c r="A11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.8">
       <c r="A12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="207">
       <c r="A13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.8">
       <c r="A14" s="24" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="151.80000000000001">
       <c r="A15" s="24" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B15" s="45" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>1043</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="24" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B16" s="43" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C16" s="44" t="s">
         <v>1211</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="124.2">
       <c r="A17" s="24" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8719,182 +8728,182 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>987</v>
+      </c>
+      <c r="C2" t="s">
         <v>310</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>988</v>
-      </c>
-      <c r="C2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C3" s="24" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
         <v>314</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>315</v>
-      </c>
-      <c r="C4" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B5" t="s">
         <v>317</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>318</v>
-      </c>
-      <c r="C5" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" t="s">
         <v>320</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>321</v>
-      </c>
-      <c r="C6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7" t="s">
         <v>323</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>324</v>
-      </c>
-      <c r="C7" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B9" t="s">
         <v>327</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>328</v>
-      </c>
-      <c r="C9" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="24" customFormat="1">
       <c r="A13" s="24" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B15" t="s">
         <v>330</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>331</v>
-      </c>
-      <c r="C15" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>333</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C16" s="51" t="s">
+        <v>332</v>
+      </c>
+      <c r="B16" s="47" t="s">
         <v>1240</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.9" customHeight="1">
       <c r="A17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B17" t="s">
         <v>334</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>335</v>
-      </c>
-      <c r="C17" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" t="s">
         <v>338</v>
       </c>
-      <c r="C18" t="s">
-        <v>339</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8922,18 +8931,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" t="s">
         <v>340</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>341</v>
-      </c>
-      <c r="C2" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -8944,204 +8953,204 @@
     </row>
     <row r="4" spans="1:3" ht="13.35" customHeight="1">
       <c r="A4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B4" t="s">
         <v>344</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>345</v>
-      </c>
-      <c r="C4" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" t="s">
         <v>347</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>348</v>
-      </c>
-      <c r="C5" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B6" t="s">
         <v>350</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>351</v>
-      </c>
-      <c r="C6" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" t="s">
         <v>353</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>354</v>
-      </c>
-      <c r="C7" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" t="s">
         <v>356</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>357</v>
-      </c>
-      <c r="C8" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" t="s">
         <v>359</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>360</v>
-      </c>
-      <c r="C9" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B10" t="s">
         <v>362</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>363</v>
-      </c>
-      <c r="C10" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" t="s">
         <v>365</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>366</v>
-      </c>
-      <c r="C11" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" t="s">
         <v>368</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>369</v>
-      </c>
-      <c r="C12" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>370</v>
+      </c>
+      <c r="B13" t="s">
         <v>371</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>372</v>
-      </c>
-      <c r="C13" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>373</v>
+      </c>
+      <c r="B15" t="s">
         <v>374</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>375</v>
-      </c>
-      <c r="C15" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B16" t="s">
         <v>377</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>378</v>
-      </c>
-      <c r="C16" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B19" t="s">
         <v>381</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>382</v>
-      </c>
-      <c r="C19" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" t="s">
         <v>384</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>385</v>
-      </c>
-      <c r="C20" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>386</v>
+      </c>
+      <c r="B21" t="s">
         <v>387</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>388</v>
-      </c>
-      <c r="C21" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="27.6">
       <c r="A23" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" t="s">
         <v>391</v>
-      </c>
-      <c r="C23" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="27.6">
       <c r="A24" t="s">
+        <v>392</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" t="s">
         <v>394</v>
       </c>
-      <c r="C24" t="s">
-        <v>395</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9169,508 +9178,508 @@
     </row>
     <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B2" t="s">
         <v>396</v>
       </c>
-      <c r="B2" t="s">
-        <v>397</v>
-      </c>
       <c r="C2" s="31" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" t="s">
         <v>398</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" t="s">
         <v>401</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B5" t="s">
         <v>404</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B6" t="s">
         <v>407</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B7" t="s">
         <v>410</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" t="s">
         <v>413</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
         <v>416</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B10" t="s">
         <v>419</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>421</v>
+      </c>
+      <c r="B11" t="s">
         <v>422</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" t="s">
         <v>425</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" t="s">
         <v>428</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>430</v>
+      </c>
+      <c r="B14" t="s">
         <v>431</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>433</v>
+      </c>
+      <c r="B15" t="s">
         <v>434</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>436</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>438</v>
+      </c>
+      <c r="B17" t="s">
         <v>439</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>441</v>
+      </c>
+      <c r="B18" t="s">
         <v>442</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>444</v>
+      </c>
+      <c r="B19" t="s">
         <v>445</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>447</v>
+      </c>
+      <c r="B20" t="s">
         <v>448</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>450</v>
+      </c>
+      <c r="B21" t="s">
         <v>451</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>453</v>
+      </c>
+      <c r="B22" t="s">
         <v>454</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" t="s">
         <v>457</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>459</v>
+      </c>
+      <c r="B24" t="s">
         <v>460</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>462</v>
+      </c>
+      <c r="B25" t="s">
         <v>463</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>465</v>
+      </c>
+      <c r="B26" t="s">
         <v>466</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>468</v>
+      </c>
+      <c r="B27" t="s">
         <v>469</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>471</v>
+      </c>
+      <c r="B28" t="s">
         <v>472</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>474</v>
+      </c>
+      <c r="B29" t="s">
         <v>475</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>477</v>
+      </c>
+      <c r="B30" t="s">
         <v>478</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>480</v>
+      </c>
+      <c r="B31" t="s">
         <v>481</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>483</v>
+      </c>
+      <c r="B32" t="s">
         <v>484</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>486</v>
+      </c>
+      <c r="B33" t="s">
         <v>487</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" s="3" t="s">
         <v>488</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>489</v>
+      </c>
+      <c r="B34" t="s">
         <v>490</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>492</v>
+      </c>
+      <c r="B35" t="s">
         <v>493</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" t="s">
         <v>496</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>498</v>
+      </c>
+      <c r="B37" t="s">
         <v>499</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38" t="s">
         <v>502</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>504</v>
+      </c>
+      <c r="B39" t="s">
         <v>505</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>507</v>
+      </c>
+      <c r="B40" t="s">
         <v>508</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>510</v>
+      </c>
+      <c r="B41" t="s">
         <v>511</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>513</v>
+      </c>
+      <c r="B42" t="s">
         <v>514</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B44">
         <v>111</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B45">
         <v>111</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>520</v>
+      </c>
+      <c r="B47" t="s">
         <v>521</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>523</v>
+      </c>
+      <c r="B48" t="s">
         <v>524</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>526</v>
+      </c>
+      <c r="B49" t="s">
         <v>527</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9678,446 +9687,446 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>529</v>
+      </c>
+      <c r="B51" t="s">
         <v>530</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>532</v>
+      </c>
+      <c r="B52" t="s">
         <v>533</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>534</v>
-      </c>
-      <c r="C52" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>535</v>
+      </c>
+      <c r="B53" t="s">
         <v>536</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>537</v>
-      </c>
-      <c r="C53" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>538</v>
+      </c>
+      <c r="B54" t="s">
         <v>539</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>540</v>
-      </c>
-      <c r="C54" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>541</v>
+      </c>
+      <c r="B55" t="s">
         <v>542</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>544</v>
+      </c>
+      <c r="B56" t="s">
         <v>545</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>547</v>
+      </c>
+      <c r="B57" t="s">
         <v>548</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>549</v>
-      </c>
-      <c r="C57" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>550</v>
+      </c>
+      <c r="B58" t="s">
         <v>551</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>552</v>
-      </c>
-      <c r="C58" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>553</v>
+      </c>
+      <c r="B60" t="s">
         <v>554</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>555</v>
-      </c>
-      <c r="C60" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>556</v>
+      </c>
+      <c r="B61" t="s">
         <v>557</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>558</v>
-      </c>
-      <c r="C61" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>559</v>
+      </c>
+      <c r="B62" t="s">
         <v>560</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>561</v>
-      </c>
-      <c r="C62" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>562</v>
+      </c>
+      <c r="B63" t="s">
         <v>563</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>564</v>
-      </c>
-      <c r="C63" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>565</v>
+      </c>
+      <c r="B64" t="s">
         <v>566</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>567</v>
-      </c>
-      <c r="C64" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
+        <v>568</v>
+      </c>
+      <c r="B65" t="s">
         <v>569</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>570</v>
-      </c>
-      <c r="C65" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
+        <v>571</v>
+      </c>
+      <c r="B67" t="s">
         <v>572</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
+        <v>574</v>
+      </c>
+      <c r="B69" t="s">
         <v>575</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>576</v>
-      </c>
-      <c r="C69" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
+        <v>577</v>
+      </c>
+      <c r="B70" t="s">
         <v>578</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>579</v>
-      </c>
-      <c r="C70" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
+        <v>580</v>
+      </c>
+      <c r="B71" t="s">
         <v>581</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>582</v>
-      </c>
-      <c r="C71" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
+        <v>583</v>
+      </c>
+      <c r="B72" t="s">
         <v>584</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>585</v>
-      </c>
-      <c r="C72" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>586</v>
+      </c>
+      <c r="B73" t="s">
         <v>587</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>588</v>
-      </c>
-      <c r="C73" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
+        <v>589</v>
+      </c>
+      <c r="B74" t="s">
         <v>590</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>591</v>
-      </c>
-      <c r="C74" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
+        <v>592</v>
+      </c>
+      <c r="B76" t="s">
         <v>593</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>594</v>
       </c>
-      <c r="C76" t="s">
-        <v>595</v>
-      </c>
       <c r="D76" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
+        <v>595</v>
+      </c>
+      <c r="B77" t="s">
         <v>596</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>597</v>
-      </c>
-      <c r="C77" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>598</v>
+      </c>
+      <c r="B78" t="s">
         <v>599</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>600</v>
-      </c>
-      <c r="C78" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
+        <v>601</v>
+      </c>
+      <c r="B79" t="s">
         <v>602</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>603</v>
-      </c>
-      <c r="C79" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
+        <v>604</v>
+      </c>
+      <c r="B80" t="s">
         <v>605</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>606</v>
-      </c>
-      <c r="C80" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
+        <v>607</v>
+      </c>
+      <c r="B81" t="s">
         <v>608</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>609</v>
-      </c>
-      <c r="C81" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>610</v>
+      </c>
+      <c r="B82" t="s">
         <v>611</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>612</v>
-      </c>
-      <c r="C82" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
+        <v>613</v>
+      </c>
+      <c r="B83" t="s">
         <v>614</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>615</v>
-      </c>
-      <c r="C83" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
+        <v>616</v>
+      </c>
+      <c r="B84" t="s">
         <v>617</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>618</v>
-      </c>
-      <c r="C84" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>619</v>
+      </c>
+      <c r="B85" t="s">
         <v>620</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>621</v>
-      </c>
-      <c r="C85" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
+        <v>622</v>
+      </c>
+      <c r="B86" t="s">
         <v>623</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>624</v>
-      </c>
-      <c r="C86" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
+        <v>625</v>
+      </c>
+      <c r="B87" t="s">
         <v>626</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>627</v>
-      </c>
-      <c r="C87" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
+        <v>628</v>
+      </c>
+      <c r="B88" t="s">
         <v>629</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>630</v>
-      </c>
-      <c r="C88" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
+        <v>631</v>
+      </c>
+      <c r="B90" t="s">
         <v>632</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>633</v>
-      </c>
-      <c r="C90" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
+        <v>634</v>
+      </c>
+      <c r="B91" t="s">
         <v>635</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>636</v>
-      </c>
-      <c r="C91" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
+        <v>637</v>
+      </c>
+      <c r="B92" t="s">
         <v>638</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>639</v>
-      </c>
-      <c r="C92" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
+        <v>640</v>
+      </c>
+      <c r="B93" t="s">
         <v>641</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>642</v>
-      </c>
-      <c r="C93" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>643</v>
+      </c>
+      <c r="B94" t="s">
         <v>644</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>645</v>
-      </c>
-      <c r="C94" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C96" s="24" t="s">
         <v>1029</v>
       </c>
-      <c r="C96" s="24" t="s">
-        <v>1030</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait"/>
 </worksheet>
@@ -10145,17 +10154,17 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B2" t="s">
         <v>647</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>648</v>
       </c>
-      <c r="C2" t="s">
-        <v>649</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10182,624 +10191,624 @@
     </row>
     <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>1177</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B3" t="s">
         <v>651</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>652</v>
-      </c>
-      <c r="C3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B5" t="s">
         <v>655</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>656</v>
-      </c>
-      <c r="C5" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>660</v>
+      </c>
+      <c r="B7" t="s">
         <v>661</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>662</v>
-      </c>
-      <c r="C7" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>663</v>
+      </c>
+      <c r="B8" t="s">
         <v>664</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>665</v>
-      </c>
-      <c r="C8" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.8">
       <c r="A10" t="s">
+        <v>667</v>
+      </c>
+      <c r="B10" t="s">
         <v>668</v>
       </c>
-      <c r="B10" t="s">
-        <v>669</v>
-      </c>
       <c r="C10" s="41" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.8">
       <c r="A11" t="s">
+        <v>669</v>
+      </c>
+      <c r="B11" t="s">
         <v>670</v>
       </c>
-      <c r="B11" t="s">
-        <v>671</v>
-      </c>
       <c r="C11" s="42" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.8">
       <c r="A12" t="s">
+        <v>671</v>
+      </c>
+      <c r="B12" t="s">
         <v>672</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>673</v>
-      </c>
-      <c r="C12" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.8">
       <c r="A13" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>675</v>
+      </c>
+      <c r="B14" t="s">
         <v>676</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>677</v>
-      </c>
-      <c r="C14" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>678</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C15" t="s">
         <v>679</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>680</v>
+      </c>
+      <c r="B16" t="s">
         <v>681</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>682</v>
-      </c>
-      <c r="C16" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>683</v>
+      </c>
+      <c r="B17" t="s">
         <v>684</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>685</v>
-      </c>
-      <c r="C17" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.8">
       <c r="A18" t="s">
+        <v>748</v>
+      </c>
+      <c r="B18" t="s">
         <v>749</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>751</v>
+      </c>
+      <c r="B19" t="s">
         <v>752</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>753</v>
-      </c>
-      <c r="C19" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>755</v>
+      </c>
+      <c r="B22" t="s">
         <v>756</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>757</v>
-      </c>
-      <c r="C22" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
+        <v>686</v>
+      </c>
+      <c r="B28" t="s">
         <v>687</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>688</v>
-      </c>
-      <c r="C28" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
+        <v>689</v>
+      </c>
+      <c r="B29" t="s">
         <v>690</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>691</v>
-      </c>
-      <c r="C29" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>692</v>
+      </c>
+      <c r="B30" t="s">
         <v>693</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>694</v>
-      </c>
-      <c r="C30" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>695</v>
+      </c>
+      <c r="B31" t="s">
         <v>696</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>697</v>
-      </c>
-      <c r="C31" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
+        <v>698</v>
+      </c>
+      <c r="B32" t="s">
         <v>699</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>700</v>
-      </c>
-      <c r="C32" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>701</v>
+      </c>
+      <c r="B33" t="s">
         <v>702</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>703</v>
-      </c>
-      <c r="C33" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>704</v>
+      </c>
+      <c r="B34" t="s">
         <v>705</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>706</v>
-      </c>
-      <c r="C34" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>707</v>
+      </c>
+      <c r="B35" t="s">
         <v>708</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>709</v>
-      </c>
-      <c r="C35" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>710</v>
+      </c>
+      <c r="B36" t="s">
         <v>711</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>712</v>
-      </c>
-      <c r="C36" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16.8">
       <c r="A37" t="s">
+        <v>713</v>
+      </c>
+      <c r="B37" t="s">
         <v>714</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>715</v>
-      </c>
-      <c r="C37" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>759</v>
+      </c>
+      <c r="B38" t="s">
         <v>760</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>761</v>
-      </c>
-      <c r="C38" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>716</v>
+      </c>
+      <c r="B39" t="s">
         <v>717</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>718</v>
-      </c>
-      <c r="C39" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>719</v>
+      </c>
+      <c r="B40" t="s">
         <v>720</v>
       </c>
-      <c r="B40" t="s">
-        <v>721</v>
-      </c>
       <c r="C40" s="34" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>721</v>
+      </c>
+      <c r="B41" t="s">
         <v>722</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>723</v>
-      </c>
-      <c r="C41" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>724</v>
+      </c>
+      <c r="B42" t="s">
         <v>725</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>726</v>
-      </c>
-      <c r="C42" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>727</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C43" t="s">
         <v>728</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C43" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>729</v>
+      </c>
+      <c r="B44" t="s">
         <v>730</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>731</v>
-      </c>
-      <c r="C44" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="27.6">
       <c r="A45" t="s">
+        <v>732</v>
+      </c>
+      <c r="B45" t="s">
         <v>733</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>735</v>
+      </c>
+      <c r="B46" t="s">
         <v>736</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>737</v>
-      </c>
-      <c r="C46" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>739</v>
+      </c>
+      <c r="B48" t="s">
         <v>740</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>741</v>
-      </c>
-      <c r="C48" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>742</v>
+      </c>
+      <c r="B49" t="s">
         <v>743</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>744</v>
-      </c>
-      <c r="C49" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>745</v>
+      </c>
+      <c r="B50" t="s">
         <v>746</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>747</v>
-      </c>
-      <c r="C50" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C51" s="24" t="s">
         <v>1087</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="34" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="34" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="34" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="37" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B56" s="24" t="s">
         <v>1139</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="C56" s="24" t="s">
         <v>1140</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="37" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.8">
       <c r="A58" s="37" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="37" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="37" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC9D6A3-D3D7-478F-99BE-84EC1DAA17B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBB48F7-53BC-434E-9370-60C220904368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3588" yWindow="2316" windowWidth="17280" windowHeight="9744" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="1250">
   <si>
     <t>#</t>
   </si>
@@ -3350,35 +3350,35 @@
   </si>
   <si>
     <t>UI_Button_Volume</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>UI_Button_CameraShakeSensitivity</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>CameraShakeSensitivity</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>镜头晃动</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Burn</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3394,7 +3394,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3410,15 +3410,15 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Lable_HighTemp_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3444,7 +3444,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3470,7 +3470,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3497,7 +3497,7 @@
       </rPr>
       <t>Sample</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3524,42 +3524,42 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Formal experiment</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>正式实验</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>在空白样本上尝试一下手头的药剂，或许会有新的收获。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>直面拥有特殊能力的造物，击败后即可进入下一阶段。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>休息一下。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Try the potionon the blank sample, maybe you will get something new.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Face the pureatures with special abilities, and defeat them to enter the next stage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Take a break.</t>
   </si>
   <si>
     <t>Prototype_1</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Prototype_2</t>
@@ -3626,21 +3626,21 @@
   </si>
   <si>
     <t>这部分是为了新教程准备的叙事大纲迭代</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tutorial_BranchTest_1</t>
   </si>
   <si>
     <t>卡牌分支测试</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
   </si>
   <si>
     <t>分支测试1</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>分支测试2</t>
@@ -3650,11 +3650,11 @@
   </si>
   <si>
     <t>Character_EarthMage</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3686,7 +3686,7 @@
       </rPr>
       <t>4</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3708,7 +3708,7 @@
       </rPr>
       <t>大地之子</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3790,7 +3790,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3871,7 +3871,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3902,100 +3902,100 @@
       </rPr>
       <t>Watcher</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
 Initial hand size: 4
 maximum hand size: 5
 Element meter capacity: 10</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 6</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>不动如山的守望者。灵魂来自大地，也将归于大地。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：6</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Sturdy</t>
@@ -4005,148 +4005,148 @@
   </si>
   <si>
     <t>坚固</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>反射</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Earth Element Bottle</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Basic Earth Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Earth Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Earth Core Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
   </si>
   <si>
     <t>Greater Earth Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
   </si>
   <si>
     <t>Vitality Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4159,120 +4159,120 @@
       </rPr>
       <t>健体药剂</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Ironbone Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
   </si>
   <si>
     <t>Shackle Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Reflection Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
   </si>
   <si>
     <t>Stoneskin Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>下一场实验：</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4286,170 +4286,170 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind</t>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>顺风</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
   </si>
   <si>
     <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Focus Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
   </si>
   <si>
     <t>Spike Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Earth Power Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Crust Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Breath of Earth</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
   </si>
   <si>
     <t>Breath of the wild</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Roar of the Earth</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Calm</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Sturdy</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Reflect</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4471,7 +4471,7 @@
       </rPr>
       <t>🔥</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4493,7 +4493,7 @@
       </rPr>
       <t>💦</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4519,7 +4519,7 @@
       </rPr>
       <t>damage.</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4545,27 +4545,27 @@
       </rPr>
       <t>伤害</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Windborne_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Elemental_Air_Windborne_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Catalyze_Windborne_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Heal_Windborne_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：抓{0}张牌</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4587,7 +4587,7 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4602,27 +4602,27 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Draw {0} cards.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4654,7 +4654,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4680,79 +4680,79 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Restore {0} HP.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Restore {0} HP.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>AirElementBottle</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>BasicAirPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>AirPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>TailwindPotion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Air Element Bottle</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Basic Air Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Air Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind Potion</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>气元素瓶</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>基础气流药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>气流药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>顺风药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Character_Airbender</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Character_Airbender_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4773,7 +4773,7 @@
       </rPr>
       <t>Airbender</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4790,72 +4790,72 @@
       </rPr>
       <t>驭气者</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
 初始手牌数：4
 初始手牌上限：5
 元素槽容量：8</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>能驾驭气流，掌控天空。善于使用连续且优雅的招式。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：3</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Master of wind, casting in flowing, unbroken sequences.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 3</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use_Desc</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>使用药剂指消耗元素使用其效果，精炼药剂不属于使用。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>使用</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Use</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Consuming elements to utilize its effect; refining a potion isn't regarded as using.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>上一个行动是[Player_Use]药剂时触发。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Triggers when the last move is [Player_Use] a potion.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>你使用或精炼过的药剂会暂时进入这里。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>The potions you [Player_Use] or refine will temporarily go here.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>开启后，可以使用鼠标左键[Player_Use]卡牌，鼠标右键精炼卡牌</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4871,83 +4871,114 @@
       </rPr>
       <t>精炼或抽牌后顺风归零。</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Gain tailwind by [Player_Use] cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>BottledFissure</t>
   </si>
   <si>
     <t>Bottled Fissure</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓶装沟壑</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>BottledSandstorm</t>
   </si>
   <si>
     <t>Bottled Sandstorm</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沙暴</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Bedrock</t>
   </si>
   <si>
     <t>基岩</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>ScorchingSandsPotion</t>
   </si>
   <si>
     <t>Scorching Sands</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>热砂药剂</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>你每次[Player_Use]药剂时，会受到{buffStack}点伤害。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>Whenever you [Player_Use] a potion, you take {buffStack} damage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>瓶装涡旋</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreezePotion</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrongWindPotion</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breeze Potion</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong Wind Potion</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>和风药剂</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>强风药剂</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装裂隙</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5270,99 +5301,101 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5636,22 +5669,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="12.8984375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="25.69921875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="30.296875" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="11"/>
+    <col min="1" max="1" width="12.88671875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="87" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49"/>
+      <c r="C1" s="50"/>
     </row>
     <row r="2" spans="1:3" ht="20.399999999999999">
       <c r="A2" s="12" t="s">
@@ -5724,17 +5757,17 @@
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5744,9 +5777,9 @@
   <dimension ref="A1:H104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="29.296875" customWidth="1"/>
-    <col min="2" max="2" width="53.69921875" customWidth="1"/>
-    <col min="3" max="3" width="58.19921875" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="53.6640625" customWidth="1"/>
+    <col min="3" max="3" width="58.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6813,7 +6846,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6821,10 +6854,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="29.296875" customWidth="1"/>
-    <col min="2" max="2" width="31.796875" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6884,7 +6917,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6894,9 +6927,9 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.69921875" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="67.796875" customWidth="1"/>
+    <col min="3" max="3" width="67.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7024,7 +7057,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7035,8 +7068,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="22.296875" customWidth="1"/>
-    <col min="3" max="3" width="15.69921875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7336,7 +7369,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="138">
+    <row r="32" spans="1:3" ht="151.80000000000001">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -7447,7 +7480,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7457,9 +7490,9 @@
   <dimension ref="A1:C114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="15.09765625" customWidth="1"/>
-    <col min="2" max="2" width="16.296875" customWidth="1"/>
-    <col min="3" max="3" width="15.296875" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7977,8 +8010,8 @@
       <c r="B51" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="C51" s="52" t="s">
-        <v>1243</v>
+      <c r="C51" s="48" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8329,41 +8362,41 @@
       <c r="B87" s="46" t="s">
         <v>1229</v>
       </c>
-      <c r="C87" s="46" t="s">
-        <v>1230</v>
+      <c r="C87" s="54" t="s">
+        <v>1249</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B88" s="46" t="s">
         <v>1231</v>
       </c>
-      <c r="B88" s="46" t="s">
+      <c r="C88" s="46" t="s">
         <v>1232</v>
-      </c>
-      <c r="C88" s="46" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="9" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B89" s="46" t="s">
         <v>1236</v>
       </c>
-      <c r="B89" s="46" t="s">
+      <c r="C89" s="46" t="s">
         <v>1237</v>
-      </c>
-      <c r="C89" s="46" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C90" s="46" t="s">
         <v>1234</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C90" s="46" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -8411,14 +8444,26 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
+      <c r="A97" s="53" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B97" s="53" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C97" s="39" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="35"/>
-      <c r="B98" s="35"/>
-      <c r="C98" s="35"/>
+      <c r="A98" s="39" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B98" s="39" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C98" s="53" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="8"/>
@@ -8496,7 +8541,7 @@
       <c r="C114" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8506,9 +8551,9 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16.796875" customWidth="1"/>
-    <col min="2" max="2" width="16.296875" customWidth="1"/>
-    <col min="3" max="3" width="17.09765625" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8599,7 +8644,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="153.6">
+    <row r="9" spans="1:5" ht="167.4">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -8622,7 +8667,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="151.80000000000001">
+    <row r="11" spans="1:5" ht="165.6">
       <c r="A11" t="s">
         <v>302</v>
       </c>
@@ -8644,7 +8689,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="207">
+    <row r="13" spans="1:5" ht="234.6">
       <c r="A13" t="s">
         <v>308</v>
       </c>
@@ -8666,7 +8711,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="151.80000000000001">
+    <row r="15" spans="1:5" ht="165.6">
       <c r="A15" s="24" t="s">
         <v>1035</v>
       </c>
@@ -8700,7 +8745,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8710,9 +8755,9 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.8984375" customWidth="1"/>
-    <col min="2" max="2" width="46.8984375" customWidth="1"/>
-    <col min="3" max="3" width="41.296875" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8874,10 +8919,10 @@
         <v>332</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.9" customHeight="1">
@@ -8903,7 +8948,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8913,9 +8958,9 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.796875" customWidth="1"/>
-    <col min="2" max="2" width="10.8984375" customWidth="1"/>
-    <col min="3" max="3" width="9.296875" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9088,10 +9133,10 @@
         <v>379</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9150,7 +9195,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9160,9 +9205,9 @@
   <dimension ref="A1:D96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="32.296875" customWidth="1"/>
-    <col min="2" max="2" width="76.796875" customWidth="1"/>
-    <col min="3" max="3" width="54.19921875" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="76.77734375" customWidth="1"/>
+    <col min="3" max="3" width="54.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10126,7 +10171,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait"/>
 </worksheet>
@@ -10137,8 +10182,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" customWidth="1"/>
-    <col min="3" max="3" width="69.796875" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="3" max="3" width="69.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10164,7 +10209,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10174,8 +10219,8 @@
   <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="32.69921875" customWidth="1"/>
-    <col min="2" max="3" width="53.69921875" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="3" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -10808,7 +10853,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBB48F7-53BC-434E-9370-60C220904368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C775D9D-1A69-4586-9224-AEDF16BF52EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3588" yWindow="2316" windowWidth="17280" windowHeight="9744" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="1286">
   <si>
     <t>#</t>
   </si>
@@ -1496,9 +1496,6 @@
     <t>Tutorial_Message_11</t>
   </si>
   <si>
-    <t>The way to obtain elements is by refine your potions, and then you can obtain a corresponding element.</t>
-  </si>
-  <si>
     <t>而获得元素的方式是精炼你的药剂，然后你就可以获得对应的一个元素。</t>
   </si>
   <si>
@@ -3350,35 +3347,35 @@
   </si>
   <si>
     <t>UI_Button_Volume</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>UI_Button_CameraShakeSensitivity</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>CameraShakeSensitivity</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>镜头晃动</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Burn</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3394,7 +3391,7 @@
       </rPr>
       <t>Boss</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3410,15 +3407,15 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Lable_HighTemp_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_ChooseLevel_Sample_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3444,7 +3441,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3470,7 +3467,7 @@
       </rPr>
       <t>_Desc</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3497,7 +3494,7 @@
       </rPr>
       <t>Sample</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3524,42 +3521,42 @@
       </rPr>
       <t>Tavern</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Formal experiment</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>正式实验</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>在空白样本上尝试一下手头的药剂，或许会有新的收获。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>直面拥有特殊能力的造物，击败后即可进入下一阶段。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>休息一下。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Try the potionon the blank sample, maybe you will get something new.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Face the pureatures with special abilities, and defeat them to enter the next stage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Take a break.</t>
   </si>
   <si>
     <t>Prototype_1</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Prototype_2</t>
@@ -3626,21 +3623,21 @@
   </si>
   <si>
     <t>这部分是为了新教程准备的叙事大纲迭代</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tutorial_BranchTest_1</t>
   </si>
   <si>
     <t>卡牌分支测试</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Branch_Test1</t>
   </si>
   <si>
     <t>分支测试1</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>分支测试2</t>
@@ -3650,11 +3647,11 @@
   </si>
   <si>
     <t>Character_EarthMage</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Character_EarthMage_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3686,7 +3683,7 @@
       </rPr>
       <t>4</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3708,7 +3705,7 @@
       </rPr>
       <t>大地之子</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3790,7 +3787,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3871,7 +3868,7 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3902,100 +3899,100 @@
       </rPr>
       <t>Watcher</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
 Initial hand size: 4
 maximum hand size: 5
 Element meter capacity: 10</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 6</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>不动如山的守望者。灵魂来自大地，也将归于大地。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：6</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Sturdy</t>
@@ -4005,148 +4002,148 @@
   </si>
   <si>
     <t>坚固</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>反射</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>EarthElementBottle</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BasicEarthPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>EarthPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Earth Element Bottle</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Basic Earth Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Earth Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>土元素瓶</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>基础大地药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>大地药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Earth Core Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>地核药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>EarthCorePotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>GreaterEarthPotion</t>
   </si>
   <si>
     <t>Greater Earth Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>高等大地药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>VitalityPotion</t>
   </si>
   <si>
     <t>Vitality Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4159,120 +4156,120 @@
       </rPr>
       <t>健体药剂</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>IronbonePotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Ironbone Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>铁骨药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>ShacklePotion</t>
   </si>
   <si>
     <t>Shackle Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>束缚药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Reflection Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>反射药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
   </si>
   <si>
     <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>ReflectionPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>StoneskinPotion</t>
   </si>
   <si>
     <t>Stoneskin Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>石肤药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>下一场实验：</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4286,170 +4283,170 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind</t>
   </si>
   <si>
     <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>顺风</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
   </si>
   <si>
     <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>FocusPotion</t>
   </si>
   <si>
     <t>集中药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Focus Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>SpikePotion</t>
   </si>
   <si>
     <t>Spike Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>地刺药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>EarthPowerPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>CrustPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfEarth</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Earth Power Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Crust Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Breath of Earth</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>地能药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>地壳药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>息壤</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BreathOfTheWild</t>
   </si>
   <si>
     <t>Breath of the wild</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>荒野之息</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Roar of the Earth</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>土石咆哮</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff] Calm</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Sturdy</t>
-    <phoneticPr fontId="19" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>[Intro_Buff]Reflect</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4471,7 +4468,7 @@
       </rPr>
       <t>🔥</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4493,7 +4490,7 @@
       </rPr>
       <t>💦</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4519,7 +4516,7 @@
       </rPr>
       <t>damage.</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4545,27 +4542,27 @@
       </rPr>
       <t>伤害</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Windborne_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Elemental_Air_Windborne_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Catalyze_Windborne_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Heal_Windborne_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：抓{0}张牌</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4587,7 +4584,7 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4602,27 +4599,27 @@
       </rPr>
       <t>💨</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Draw {0} cards.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4654,7 +4651,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4680,79 +4677,79 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Restore {0} HP.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>[Card_Windborne]: Restore {0} HP.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>AirElementBottle</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BasicAirPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>AirPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>TailwindPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Air Element Bottle</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Basic Air Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Air Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tailwind Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>气元素瓶</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>基础气流药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>气流药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>顺风药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Character_Airbender</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Character_Airbender_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4773,7 +4770,7 @@
       </rPr>
       <t>Airbender</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4790,72 +4787,72 @@
       </rPr>
       <t>驭气者</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
 初始手牌数：4
 初始手牌上限：5
 元素槽容量：8</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>能驾驭气流，掌控天空。善于使用连续且优雅的招式。
 初始手牌数：5
 初始手牌上限：5
 元素槽容量：3</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Master of wind, casting in flowing, unbroken sequences.
 Initial hand size: 5
 maximum hand size: 5
 Element meter capacity: 3</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use_Desc</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Tip_Player_Use</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>使用药剂指消耗元素使用其效果，精炼药剂不属于使用。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>使用</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Use</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Consuming elements to utilize its effect; refining a potion isn't regarded as using.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>上一个行动是[Player_Use]药剂时触发。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Triggers when the last move is [Player_Use] a potion.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>你使用或精炼过的药剂会暂时进入这里。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>The potions you [Player_Use] or refine will temporarily go here.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>开启后，可以使用鼠标左键[Player_Use]卡牌，鼠标右键精炼卡牌</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4871,107 +4868,263 @@
       </rPr>
       <t>精炼或抽牌后顺风归零。</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Gain tailwind by [Player_Use] cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BottledFissure</t>
   </si>
   <si>
     <t>Bottled Fissure</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BottledSandstorm</t>
   </si>
   <si>
     <t>Bottled Sandstorm</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>瓶装沙暴</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Bedrock</t>
   </si>
   <si>
     <t>基岩</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>ScorchingSandsPotion</t>
   </si>
   <si>
     <t>Scorching Sands</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>热砂药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>你每次[Player_Use]药剂时，会受到{buffStack}点伤害。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Whenever you [Player_Use] a potion, you take {buffStack} damage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>瓶装涡旋</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>BreezePotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>StrongWindPotion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Breeze Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Strong Wind Potion</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>和风药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>强风药剂</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>瓶装裂隙</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>GustPotion</t>
+  </si>
+  <si>
+    <t>Gust Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>TornadoPotion</t>
+  </si>
+  <si>
+    <t>Tornado Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>The way to obtain elements is by refining your potions, and then you can obtain a corresponding element.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreaterAirPotion</t>
+  </si>
+  <si>
+    <t>Greater Air Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等气流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConvectionPotion</t>
+  </si>
+  <si>
+    <t>Convection Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>对流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>SevereConvectionPotion</t>
+  </si>
+  <si>
+    <t>Severe Convection</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>强对流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>HurricanePotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hurricane Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>飓风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Aftermath</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Aftermath_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>余响</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅在被转化时触发。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aftermath</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggers when being transmuted.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]: Deal {0} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Aftermath_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Heal_Aftermath_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Damage_Aftermath_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]：造成{0}点伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]：抓{0}张牌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]: Restore {0} HP.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]: Draw {0} cards.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>FairyWind</t>
+  </si>
+  <si>
+    <t>Fairy Wind</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖精之风</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5301,98 +5454,102 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5681,10 +5838,10 @@
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50"/>
+      <c r="C1" s="53"/>
     </row>
     <row r="2" spans="1:3" ht="20.399999999999999">
       <c r="A2" s="12" t="s">
@@ -5757,24 +5914,24 @@
       <c r="A9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="52"/>
+      <c r="C9" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="29.33203125" customWidth="1"/>
@@ -5795,483 +5952,483 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>761</v>
+      </c>
+      <c r="B2" t="s">
         <v>762</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>763</v>
-      </c>
-      <c r="C2" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B3" t="s">
         <v>765</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>766</v>
-      </c>
-      <c r="C3" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B4" t="s">
         <v>768</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>769</v>
-      </c>
-      <c r="C4" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>770</v>
+      </c>
+      <c r="B5" t="s">
         <v>771</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>772</v>
-      </c>
-      <c r="C5" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>773</v>
+      </c>
+      <c r="B6" t="s">
         <v>774</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>775</v>
-      </c>
-      <c r="C6" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>776</v>
+      </c>
+      <c r="B7" t="s">
         <v>777</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>778</v>
-      </c>
-      <c r="C7" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B9" t="s">
         <v>780</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>781</v>
-      </c>
-      <c r="C9" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>782</v>
+      </c>
+      <c r="B10" t="s">
         <v>783</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>784</v>
-      </c>
-      <c r="C10" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>785</v>
+      </c>
+      <c r="B11" t="s">
         <v>786</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>787</v>
-      </c>
-      <c r="C11" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>788</v>
+      </c>
+      <c r="B12" t="s">
         <v>789</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>790</v>
-      </c>
-      <c r="C12" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>791</v>
+      </c>
+      <c r="B14" t="s">
         <v>792</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>793</v>
-      </c>
-      <c r="C14" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>794</v>
+      </c>
+      <c r="B15" t="s">
         <v>795</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>796</v>
-      </c>
-      <c r="C15" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>797</v>
+      </c>
+      <c r="B16" t="s">
         <v>798</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>799</v>
-      </c>
-      <c r="C16" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>800</v>
+      </c>
+      <c r="B17" t="s">
         <v>801</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>802</v>
-      </c>
-      <c r="C17" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>803</v>
+      </c>
+      <c r="B18" t="s">
         <v>804</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>805</v>
-      </c>
-      <c r="C18" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>806</v>
+      </c>
+      <c r="B19" t="s">
         <v>807</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>808</v>
-      </c>
-      <c r="C19" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>809</v>
+      </c>
+      <c r="B20" t="s">
         <v>810</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>811</v>
-      </c>
-      <c r="C20" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B21" t="s">
+        <v>810</v>
+      </c>
+      <c r="C21" t="s">
         <v>811</v>
-      </c>
-      <c r="C21" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B22" t="s">
+        <v>810</v>
+      </c>
+      <c r="C22" t="s">
         <v>811</v>
-      </c>
-      <c r="C22" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B23" t="s">
+        <v>810</v>
+      </c>
+      <c r="C23" t="s">
         <v>811</v>
-      </c>
-      <c r="C23" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>815</v>
+      </c>
+      <c r="B24" t="s">
         <v>816</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>817</v>
-      </c>
-      <c r="C24" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>818</v>
+      </c>
+      <c r="B25" t="s">
         <v>819</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>820</v>
-      </c>
-      <c r="C25" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="44" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="44" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>821</v>
+      </c>
+      <c r="B29" t="s">
         <v>822</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>823</v>
-      </c>
-      <c r="C29" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>824</v>
+      </c>
+      <c r="B30" t="s">
         <v>825</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>826</v>
-      </c>
-      <c r="C30" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>827</v>
+      </c>
+      <c r="B31" t="s">
         <v>828</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>829</v>
-      </c>
-      <c r="C31" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>830</v>
+      </c>
+      <c r="B32" t="s">
         <v>831</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>832</v>
-      </c>
-      <c r="C32" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>833</v>
+      </c>
+      <c r="B33" t="s">
         <v>834</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>835</v>
-      </c>
-      <c r="C33" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>836</v>
+      </c>
+      <c r="B34" t="s">
         <v>837</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>838</v>
-      </c>
-      <c r="C34" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>839</v>
+      </c>
+      <c r="B35" t="s">
         <v>840</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>841</v>
-      </c>
-      <c r="C35" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>842</v>
+      </c>
+      <c r="B36" t="s">
         <v>843</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>844</v>
-      </c>
-      <c r="C36" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>845</v>
+      </c>
+      <c r="B37" t="s">
         <v>846</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>847</v>
-      </c>
-      <c r="C37" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>848</v>
+      </c>
+      <c r="B38" t="s">
         <v>849</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>850</v>
-      </c>
-      <c r="C38" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>851</v>
+      </c>
+      <c r="B39" t="s">
         <v>852</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>853</v>
-      </c>
-      <c r="C39" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>854</v>
+      </c>
+      <c r="B40" t="s">
         <v>855</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>856</v>
-      </c>
-      <c r="C40" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>857</v>
+      </c>
+      <c r="B41" t="s">
         <v>858</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>859</v>
-      </c>
-      <c r="C41" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>860</v>
+      </c>
+      <c r="B42" t="s">
         <v>861</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>862</v>
-      </c>
-      <c r="C42" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>863</v>
+      </c>
+      <c r="B43" t="s">
         <v>864</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>865</v>
-      </c>
-      <c r="C43" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>867</v>
+      </c>
+      <c r="B45" t="s">
         <v>868</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>869</v>
-      </c>
-      <c r="C45" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>870</v>
+      </c>
+      <c r="B46" t="s">
         <v>871</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>872</v>
-      </c>
-      <c r="C46" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>873</v>
+      </c>
+      <c r="B47" t="s">
         <v>874</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>875</v>
-      </c>
-      <c r="C47" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C48" t="s">
         <v>328</v>
@@ -6279,18 +6436,18 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
+        <v>877</v>
+      </c>
+      <c r="B49" t="s">
         <v>878</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>879</v>
-      </c>
-      <c r="C49" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B50" t="s">
         <v>317</v>
@@ -6301,552 +6458,575 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="30" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G53" s="30"/>
       <c r="H53" s="30"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="30" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="30" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="30" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="30" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="36" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="30"/>
     </row>
     <row r="60" spans="1:8" ht="27.6">
       <c r="A60" s="36" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G60" s="30"/>
       <c r="H60" s="30"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="36" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="36" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="36"/>
-      <c r="B63" s="36"/>
+      <c r="A63" s="58" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B63" s="58" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>1270</v>
+      </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" t="s">
-        <v>888</v>
-      </c>
-      <c r="B64" t="s">
-        <v>889</v>
-      </c>
-      <c r="C64" t="s">
-        <v>890</v>
+      <c r="A64" s="58" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B64" s="58" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>1271</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>891</v>
-      </c>
-      <c r="B65" t="s">
-        <v>892</v>
-      </c>
-      <c r="C65" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>894</v>
-      </c>
-      <c r="B66" t="s">
-        <v>895</v>
-      </c>
-      <c r="C66" t="s">
-        <v>65</v>
-      </c>
+      <c r="A65" s="36"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="24"/>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="B67" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="C67" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B68" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="C68" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="B69" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="C69" t="s">
-        <v>904</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="B70" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="C70" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B71" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="C71" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="B72" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="C72" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="B73" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
       <c r="C73" t="s">
-        <v>916</v>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>907</v>
+      </c>
+      <c r="B74" t="s">
+        <v>908</v>
+      </c>
+      <c r="C74" t="s">
+        <v>909</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B75" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="C75" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="B76" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C76" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="B78" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="C78" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="B79" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="C79" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>928</v>
-      </c>
-      <c r="B80" t="s">
-        <v>52</v>
-      </c>
-      <c r="C80" t="s">
-        <v>53</v>
+        <v>920</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="B81" t="s">
-        <v>930</v>
-      </c>
-      <c r="C81" s="44" t="s">
-        <v>1225</v>
+        <v>922</v>
+      </c>
+      <c r="C81" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>924</v>
+      </c>
+      <c r="B82" t="s">
+        <v>925</v>
+      </c>
+      <c r="C82" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B83" t="s">
-        <v>932</v>
+        <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>933</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B84" t="s">
-        <v>935</v>
-      </c>
-      <c r="C84" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
-        <v>937</v>
-      </c>
-      <c r="B85" t="s">
-        <v>938</v>
-      </c>
-      <c r="C85" t="s">
-        <v>939</v>
+        <v>929</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>1224</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>940</v>
-      </c>
-      <c r="B86" s="44" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C86" s="44" t="s">
-        <v>1223</v>
+        <v>930</v>
+      </c>
+      <c r="B86" t="s">
+        <v>931</v>
+      </c>
+      <c r="C86" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="B87" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>935</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="B88" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="C88" t="s">
-        <v>945</v>
+        <v>938</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>939</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B90" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="C90" t="s">
-        <v>948</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="B91" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="C91" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>952</v>
-      </c>
-      <c r="B92" t="s">
-        <v>953</v>
-      </c>
-      <c r="C92" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="B93" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="C93" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="B94" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
       <c r="C94" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="26" t="s">
-        <v>991</v>
+      <c r="A95" t="s">
+        <v>951</v>
       </c>
       <c r="B95" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="C95" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B96" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="C96" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
+        <v>957</v>
+      </c>
+      <c r="B97" t="s">
+        <v>958</v>
+      </c>
+      <c r="C97" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="26" t="s">
+        <v>990</v>
+      </c>
+      <c r="B98" t="s">
+        <v>960</v>
+      </c>
+      <c r="C98" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>962</v>
+      </c>
+      <c r="B99" t="s">
+        <v>963</v>
+      </c>
+      <c r="C99" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>965</v>
+      </c>
+      <c r="B100" t="s">
         <v>966</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C100" t="s">
         <v>967</v>
       </c>
-      <c r="C97" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.6">
-      <c r="A99" s="25" t="s">
-        <v>988</v>
-      </c>
-      <c r="B99" s="27" t="s">
-        <v>995</v>
-      </c>
-      <c r="C99" t="s">
+    </row>
+    <row r="102" spans="1:3" ht="15.6">
+      <c r="A102" s="25" t="s">
+        <v>987</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>994</v>
+      </c>
+      <c r="C102" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.6">
-      <c r="A100" s="25" t="s">
-        <v>992</v>
-      </c>
-      <c r="B100" s="26" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C100" s="29" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="15.6">
-      <c r="A101" s="26" t="s">
-        <v>989</v>
-      </c>
-      <c r="B101" s="26" t="s">
-        <v>997</v>
-      </c>
-      <c r="C101" s="28" t="s">
+    <row r="103" spans="1:3" ht="15.6">
+      <c r="A103" s="25" t="s">
+        <v>991</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C103" s="29" t="s">
         <v>998</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="15.6">
-      <c r="A102" s="26" t="s">
-        <v>993</v>
-      </c>
-      <c r="B102" s="26" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="15.6">
-      <c r="A103" s="26" t="s">
-        <v>990</v>
-      </c>
-      <c r="B103" s="27" t="s">
-        <v>996</v>
-      </c>
-      <c r="C103" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.6">
       <c r="A104" s="26" t="s">
-        <v>994</v>
-      </c>
-      <c r="B104" t="s">
-        <v>1004</v>
+        <v>988</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>996</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>1001</v>
+        <v>997</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15.6">
+      <c r="A105" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C105" s="28" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="15.6">
+      <c r="A106" s="26" t="s">
+        <v>989</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>995</v>
+      </c>
+      <c r="C106" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15.6">
+      <c r="A107" s="26" t="s">
+        <v>993</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6874,50 +7054,50 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B2" t="s">
         <v>969</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>970</v>
-      </c>
-      <c r="C2" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B3" t="s">
         <v>972</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>973</v>
-      </c>
-      <c r="C3" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>974</v>
+      </c>
+      <c r="B4" t="s">
         <v>975</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>976</v>
-      </c>
-      <c r="C4" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>977</v>
+      </c>
+      <c r="B5" t="s">
         <v>978</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>979</v>
       </c>
-      <c r="C5" t="s">
-        <v>980</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6945,119 +7125,119 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="24" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="24" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="24" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="24" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="24" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="24" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="24" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="24" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="24" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="24" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="24" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="24" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="24" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="24" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="24" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7217,7 +7397,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -7228,13 +7408,13 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="24" t="s">
+        <v>981</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>982</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="C15" s="24" t="s">
         <v>983</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7470,24 +7650,24 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="34" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C42" s="34" t="s">
         <v>1126</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>1127</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -7560,18 +7740,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>1030</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8011,7 +8191,7 @@
         <v>242</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8170,362 +8350,405 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="33" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="33" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="33" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B71" s="33" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C71" s="33" t="s">
         <v>1089</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="8" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1099</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>1100</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="35" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B74" s="35" t="s">
         <v>1102</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="C74" s="35" t="s">
         <v>1103</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B75" s="35" t="s">
         <v>1105</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="C75" s="35" t="s">
         <v>1106</v>
-      </c>
-      <c r="C75" s="35" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="35" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B76" s="35" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C76" s="35" t="s">
         <v>1114</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B77" s="35" t="s">
         <v>1123</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>1124</v>
-      </c>
-      <c r="C77" s="35" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="8" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B78" s="38" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C78" s="38" t="s">
         <v>1141</v>
-      </c>
-      <c r="B78" s="38" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C78" s="38" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B79" s="38" t="s">
         <v>1144</v>
       </c>
-      <c r="B79" s="38" t="s">
+      <c r="C79" s="38" t="s">
         <v>1145</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="38" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="38" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="39" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>1096</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>1097</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="9" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B85" s="40" t="s">
         <v>1163</v>
       </c>
-      <c r="B85" s="40" t="s">
+      <c r="C85" s="40" t="s">
         <v>1164</v>
-      </c>
-      <c r="C85" s="40" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="40" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B86" s="40" t="s">
         <v>1166</v>
       </c>
-      <c r="B86" s="40" t="s">
+      <c r="C86" s="40" t="s">
         <v>1167</v>
-      </c>
-      <c r="C86" s="40" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B87" s="46" t="s">
         <v>1228</v>
       </c>
-      <c r="B87" s="46" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C87" s="54" t="s">
-        <v>1249</v>
+      <c r="C87" s="50" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B88" s="46" t="s">
         <v>1230</v>
       </c>
-      <c r="B88" s="46" t="s">
+      <c r="C88" s="46" t="s">
         <v>1231</v>
-      </c>
-      <c r="C88" s="46" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B89" s="46" t="s">
         <v>1235</v>
       </c>
-      <c r="B89" s="46" t="s">
+      <c r="C89" s="46" t="s">
         <v>1236</v>
-      </c>
-      <c r="C89" s="46" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C90" s="46" t="s">
         <v>1233</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C90" s="46" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="33" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="33" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="33" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="33" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C95" s="33" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="53" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="49" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B97" s="49" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C97" s="39" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="39" t="s">
         <v>1243</v>
       </c>
-      <c r="B97" s="53" t="s">
+      <c r="B98" s="39" t="s">
         <v>1245</v>
       </c>
-      <c r="C97" s="39" t="s">
+      <c r="C98" s="49" t="s">
         <v>1247</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="39" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B98" s="39" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C98" s="53" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="8"/>
-      <c r="B99" s="35"/>
-      <c r="C99" s="35"/>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="35"/>
-      <c r="B100" s="35"/>
-      <c r="C100" s="35"/>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="8"/>
-      <c r="B101" s="35"/>
-      <c r="C101" s="35"/>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="8"/>
-      <c r="B102" s="38"/>
-      <c r="C102" s="38"/>
-    </row>
-    <row r="103" spans="1:3">
+    <row r="99" spans="1:4">
+      <c r="A99" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B99" s="51" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C99" s="51" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="35" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B100" s="51" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C100" s="51" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="39" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B101" s="57" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C101" s="57" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="8" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B102" s="57" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C102" s="57" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D102" s="24"/>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" s="8"/>
       <c r="B103" s="38"/>
       <c r="C103" s="38"/>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:4">
       <c r="A104" s="38"/>
       <c r="B104" s="38"/>
       <c r="C104" s="38"/>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:4">
       <c r="A105" s="38"/>
       <c r="B105" s="38"/>
       <c r="C105" s="38"/>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:4">
       <c r="A106" s="39"/>
       <c r="B106" s="39"/>
       <c r="C106" s="38"/>
     </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="9"/>
-      <c r="B109" s="40"/>
-      <c r="C109" s="40"/>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="40"/>
-      <c r="B110" s="40"/>
-      <c r="C110" s="40"/>
-    </row>
-    <row r="111" spans="1:3">
+    <row r="108" spans="1:4">
+      <c r="A108" s="9" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B108" s="56" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C108" s="56" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="9" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B109" s="56" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C109" s="56" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="40" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B110" s="56" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C110" s="56" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" s="9"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:4">
       <c r="A112" s="9"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
@@ -8541,7 +8764,7 @@
       <c r="C114" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8605,10 +8828,10 @@
         <v>286</v>
       </c>
       <c r="B5" s="32" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>1038</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8694,58 +8917,58 @@
         <v>308</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.8">
       <c r="A14" s="24" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="165.6">
       <c r="A15" s="24" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B15" s="45" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>1042</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="24" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B16" s="43" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C16" s="44" t="s">
         <v>1210</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="124.2">
       <c r="A17" s="24" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8776,7 +8999,7 @@
         <v>309</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C2" t="s">
         <v>310</v>
@@ -8790,7 +9013,7 @@
         <v>312</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -8842,10 +9065,10 @@
         <v>325</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8861,46 +9084,46 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="24" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="24" customFormat="1">
       <c r="A13" s="24" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -8919,10 +9142,10 @@
         <v>332</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.9" customHeight="1">
@@ -8948,7 +9171,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9133,10 +9356,10 @@
         <v>379</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9195,7 +9418,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9229,7 +9452,7 @@
         <v>396</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9346,385 +9569,385 @@
       <c r="A13" t="s">
         <v>427</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="24" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B14" t="s">
         <v>430</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>432</v>
+      </c>
+      <c r="B15" t="s">
         <v>433</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>437</v>
+      </c>
+      <c r="B17" t="s">
         <v>438</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>440</v>
+      </c>
+      <c r="B18" t="s">
         <v>441</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>443</v>
+      </c>
+      <c r="B19" t="s">
         <v>444</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>446</v>
+      </c>
+      <c r="B20" t="s">
         <v>447</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>449</v>
+      </c>
+      <c r="B21" t="s">
         <v>450</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>452</v>
+      </c>
+      <c r="B22" t="s">
         <v>453</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>455</v>
+      </c>
+      <c r="B23" t="s">
         <v>456</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>458</v>
+      </c>
+      <c r="B24" t="s">
         <v>459</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>461</v>
+      </c>
+      <c r="B25" t="s">
         <v>462</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>464</v>
+      </c>
+      <c r="B26" t="s">
         <v>465</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>467</v>
+      </c>
+      <c r="B27" t="s">
         <v>468</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>470</v>
+      </c>
+      <c r="B28" t="s">
         <v>471</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>473</v>
+      </c>
+      <c r="B29" t="s">
         <v>474</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>476</v>
+      </c>
+      <c r="B30" t="s">
         <v>477</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>479</v>
+      </c>
+      <c r="B31" t="s">
         <v>480</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>482</v>
+      </c>
+      <c r="B32" t="s">
         <v>483</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>485</v>
+      </c>
+      <c r="B33" t="s">
         <v>486</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>488</v>
+      </c>
+      <c r="B34" t="s">
         <v>489</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>491</v>
+      </c>
+      <c r="B35" t="s">
         <v>492</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>494</v>
+      </c>
+      <c r="B36" t="s">
         <v>495</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>497</v>
+      </c>
+      <c r="B37" t="s">
         <v>498</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>500</v>
+      </c>
+      <c r="B38" t="s">
         <v>501</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>503</v>
+      </c>
+      <c r="B39" t="s">
         <v>504</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>506</v>
+      </c>
+      <c r="B40" t="s">
         <v>507</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>509</v>
+      </c>
+      <c r="B41" t="s">
         <v>510</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>512</v>
+      </c>
+      <c r="B42" t="s">
         <v>513</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" s="3" t="s">
         <v>514</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B44">
         <v>111</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B45">
         <v>111</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>519</v>
+      </c>
+      <c r="B47" t="s">
         <v>520</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>522</v>
+      </c>
+      <c r="B48" t="s">
         <v>523</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>525</v>
+      </c>
+      <c r="B49" t="s">
         <v>526</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -9732,446 +9955,446 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>528</v>
+      </c>
+      <c r="B51" t="s">
         <v>529</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>531</v>
+      </c>
+      <c r="B52" t="s">
         <v>532</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>533</v>
-      </c>
-      <c r="C52" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>534</v>
+      </c>
+      <c r="B53" t="s">
         <v>535</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>536</v>
-      </c>
-      <c r="C53" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>537</v>
+      </c>
+      <c r="B54" t="s">
         <v>538</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>539</v>
-      </c>
-      <c r="C54" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>540</v>
+      </c>
+      <c r="B55" t="s">
         <v>541</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>543</v>
+      </c>
+      <c r="B56" t="s">
         <v>544</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>546</v>
+      </c>
+      <c r="B57" t="s">
         <v>547</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>548</v>
-      </c>
-      <c r="C57" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>549</v>
+      </c>
+      <c r="B58" t="s">
         <v>550</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>551</v>
-      </c>
-      <c r="C58" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>552</v>
+      </c>
+      <c r="B60" t="s">
         <v>553</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>554</v>
-      </c>
-      <c r="C60" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>555</v>
+      </c>
+      <c r="B61" t="s">
         <v>556</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>557</v>
-      </c>
-      <c r="C61" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>558</v>
+      </c>
+      <c r="B62" t="s">
         <v>559</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>560</v>
-      </c>
-      <c r="C62" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>561</v>
+      </c>
+      <c r="B63" t="s">
         <v>562</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>563</v>
-      </c>
-      <c r="C63" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>564</v>
+      </c>
+      <c r="B64" t="s">
         <v>565</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>566</v>
-      </c>
-      <c r="C64" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
+        <v>567</v>
+      </c>
+      <c r="B65" t="s">
         <v>568</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>569</v>
-      </c>
-      <c r="C65" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
+        <v>570</v>
+      </c>
+      <c r="B67" t="s">
         <v>571</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
+        <v>573</v>
+      </c>
+      <c r="B69" t="s">
         <v>574</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>575</v>
-      </c>
-      <c r="C69" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
+        <v>576</v>
+      </c>
+      <c r="B70" t="s">
         <v>577</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>578</v>
-      </c>
-      <c r="C70" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
+        <v>579</v>
+      </c>
+      <c r="B71" t="s">
         <v>580</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>581</v>
-      </c>
-      <c r="C71" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
+        <v>582</v>
+      </c>
+      <c r="B72" t="s">
         <v>583</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>584</v>
-      </c>
-      <c r="C72" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>585</v>
+      </c>
+      <c r="B73" t="s">
         <v>586</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>587</v>
-      </c>
-      <c r="C73" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
+        <v>588</v>
+      </c>
+      <c r="B74" t="s">
         <v>589</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>590</v>
-      </c>
-      <c r="C74" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
+        <v>591</v>
+      </c>
+      <c r="B76" t="s">
         <v>592</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>593</v>
       </c>
-      <c r="C76" t="s">
-        <v>594</v>
-      </c>
       <c r="D76" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
+        <v>594</v>
+      </c>
+      <c r="B77" t="s">
         <v>595</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>596</v>
-      </c>
-      <c r="C77" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>597</v>
+      </c>
+      <c r="B78" t="s">
         <v>598</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>599</v>
-      </c>
-      <c r="C78" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
+        <v>600</v>
+      </c>
+      <c r="B79" t="s">
         <v>601</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>602</v>
-      </c>
-      <c r="C79" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
+        <v>603</v>
+      </c>
+      <c r="B80" t="s">
         <v>604</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>605</v>
-      </c>
-      <c r="C80" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
+        <v>606</v>
+      </c>
+      <c r="B81" t="s">
         <v>607</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>608</v>
-      </c>
-      <c r="C81" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>609</v>
+      </c>
+      <c r="B82" t="s">
         <v>610</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>611</v>
-      </c>
-      <c r="C82" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
+        <v>612</v>
+      </c>
+      <c r="B83" t="s">
         <v>613</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>614</v>
-      </c>
-      <c r="C83" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
+        <v>615</v>
+      </c>
+      <c r="B84" t="s">
         <v>616</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>617</v>
-      </c>
-      <c r="C84" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>618</v>
+      </c>
+      <c r="B85" t="s">
         <v>619</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>620</v>
-      </c>
-      <c r="C85" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
+        <v>621</v>
+      </c>
+      <c r="B86" t="s">
         <v>622</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>623</v>
-      </c>
-      <c r="C86" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
+        <v>624</v>
+      </c>
+      <c r="B87" t="s">
         <v>625</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>626</v>
-      </c>
-      <c r="C87" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
+        <v>627</v>
+      </c>
+      <c r="B88" t="s">
         <v>628</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>629</v>
-      </c>
-      <c r="C88" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
+        <v>630</v>
+      </c>
+      <c r="B90" t="s">
         <v>631</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>632</v>
-      </c>
-      <c r="C90" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
+        <v>633</v>
+      </c>
+      <c r="B91" t="s">
         <v>634</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>635</v>
-      </c>
-      <c r="C91" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
+        <v>636</v>
+      </c>
+      <c r="B92" t="s">
         <v>637</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>638</v>
-      </c>
-      <c r="C92" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
+        <v>639</v>
+      </c>
+      <c r="B93" t="s">
         <v>640</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>641</v>
-      </c>
-      <c r="C93" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>642</v>
+      </c>
+      <c r="B94" t="s">
         <v>643</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>644</v>
-      </c>
-      <c r="C94" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C96" s="24" t="s">
         <v>1028</v>
       </c>
-      <c r="C96" s="24" t="s">
-        <v>1029</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait"/>
 </worksheet>
@@ -10199,24 +10422,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B2" t="s">
         <v>646</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>647</v>
       </c>
-      <c r="C2" t="s">
-        <v>648</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
@@ -10236,624 +10459,657 @@
     </row>
     <row r="2" spans="1:3" ht="16.8">
       <c r="A2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>1176</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B3" t="s">
         <v>650</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>651</v>
-      </c>
-      <c r="C3" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B5" t="s">
         <v>654</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>655</v>
-      </c>
-      <c r="C5" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>656</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>659</v>
+      </c>
+      <c r="B7" t="s">
         <v>660</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>661</v>
-      </c>
-      <c r="C7" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>662</v>
+      </c>
+      <c r="B8" t="s">
         <v>663</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>664</v>
-      </c>
-      <c r="C8" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.8">
       <c r="A10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B10" t="s">
         <v>667</v>
       </c>
-      <c r="B10" t="s">
-        <v>668</v>
-      </c>
       <c r="C10" s="41" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.8">
       <c r="A11" t="s">
+        <v>668</v>
+      </c>
+      <c r="B11" t="s">
         <v>669</v>
       </c>
-      <c r="B11" t="s">
-        <v>670</v>
-      </c>
       <c r="C11" s="42" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.8">
       <c r="A12" t="s">
+        <v>670</v>
+      </c>
+      <c r="B12" t="s">
         <v>671</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>672</v>
-      </c>
-      <c r="C12" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.8">
       <c r="A13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>674</v>
+      </c>
+      <c r="B14" t="s">
         <v>675</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>676</v>
-      </c>
-      <c r="C14" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>677</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C15" t="s">
         <v>678</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C15" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>679</v>
+      </c>
+      <c r="B16" t="s">
         <v>680</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>681</v>
-      </c>
-      <c r="C16" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>682</v>
+      </c>
+      <c r="B17" t="s">
         <v>683</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>684</v>
-      </c>
-      <c r="C17" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.8">
       <c r="A18" t="s">
+        <v>747</v>
+      </c>
+      <c r="B18" t="s">
         <v>748</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>750</v>
+      </c>
+      <c r="B19" t="s">
         <v>751</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>752</v>
-      </c>
-      <c r="C19" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>754</v>
+      </c>
+      <c r="B22" t="s">
         <v>755</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>756</v>
-      </c>
-      <c r="C22" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
+        <v>685</v>
+      </c>
+      <c r="B28" t="s">
         <v>686</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>687</v>
-      </c>
-      <c r="C28" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
+        <v>688</v>
+      </c>
+      <c r="B29" t="s">
         <v>689</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>690</v>
-      </c>
-      <c r="C29" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>691</v>
+      </c>
+      <c r="B30" t="s">
         <v>692</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>693</v>
-      </c>
-      <c r="C30" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>694</v>
+      </c>
+      <c r="B31" t="s">
         <v>695</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>696</v>
-      </c>
-      <c r="C31" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
+        <v>697</v>
+      </c>
+      <c r="B32" t="s">
         <v>698</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>699</v>
-      </c>
-      <c r="C32" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>700</v>
+      </c>
+      <c r="B33" t="s">
         <v>701</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>702</v>
-      </c>
-      <c r="C33" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>703</v>
+      </c>
+      <c r="B34" t="s">
         <v>704</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>705</v>
-      </c>
-      <c r="C34" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>706</v>
+      </c>
+      <c r="B35" t="s">
         <v>707</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>708</v>
-      </c>
-      <c r="C35" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>709</v>
+      </c>
+      <c r="B36" t="s">
         <v>710</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>711</v>
-      </c>
-      <c r="C36" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16.8">
       <c r="A37" t="s">
+        <v>712</v>
+      </c>
+      <c r="B37" t="s">
         <v>713</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>714</v>
-      </c>
-      <c r="C37" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>758</v>
+      </c>
+      <c r="B38" t="s">
         <v>759</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>760</v>
-      </c>
-      <c r="C38" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>715</v>
+      </c>
+      <c r="B39" t="s">
         <v>716</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>717</v>
-      </c>
-      <c r="C39" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>718</v>
+      </c>
+      <c r="B40" t="s">
         <v>719</v>
       </c>
-      <c r="B40" t="s">
-        <v>720</v>
-      </c>
       <c r="C40" s="34" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>720</v>
+      </c>
+      <c r="B41" t="s">
         <v>721</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>722</v>
-      </c>
-      <c r="C41" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>723</v>
+      </c>
+      <c r="B42" t="s">
         <v>724</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>725</v>
-      </c>
-      <c r="C42" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>726</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C43" t="s">
         <v>727</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C43" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>728</v>
+      </c>
+      <c r="B44" t="s">
         <v>729</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>730</v>
-      </c>
-      <c r="C44" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="27.6">
       <c r="A45" t="s">
+        <v>731</v>
+      </c>
+      <c r="B45" t="s">
         <v>732</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>734</v>
+      </c>
+      <c r="B46" t="s">
         <v>735</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>736</v>
-      </c>
-      <c r="C46" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>738</v>
+      </c>
+      <c r="B48" t="s">
         <v>739</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>740</v>
-      </c>
-      <c r="C48" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>741</v>
+      </c>
+      <c r="B49" t="s">
         <v>742</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>743</v>
-      </c>
-      <c r="C49" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>744</v>
+      </c>
+      <c r="B50" t="s">
         <v>745</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>746</v>
-      </c>
-      <c r="C50" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C51" s="24" t="s">
         <v>1086</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="34" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="34" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="34" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="37" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B56" s="24" t="s">
         <v>1138</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="C56" s="24" t="s">
         <v>1139</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="37" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.8">
       <c r="A58" s="37" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="37" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="37" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1188</v>
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="37" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B62" s="24" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="37" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="37" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>1280</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/Game/Content/Data/LocalizeTable.xlsx
+++ b/Assets/Game/Content/Data/LocalizeTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C775D9D-1A69-4586-9224-AEDF16BF52EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC9D306-942C-42E6-96E0-D9D1F361942E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="1286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="1289">
   <si>
     <t>#</t>
   </si>
@@ -3794,10 +3794,1244 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⛰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">Earth </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Watcher</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
+Initial hand size: 4
+maximum hand size: 5
+Element meter capacity: 10</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
+Initial hand size: 5
+maximum hand size: 5
+Element meter capacity: 6</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动如山的守望者。灵魂来自大地，也将归于大地。
+初始手牌数：5
+初始手牌上限：5
+元素槽容量：6</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy_Self_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Self_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Enemy_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]冷静</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]坚固</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次行动受到{buffStack}伤害。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]反射</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Sturdy</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Sturdy_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Reflect</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Reflect_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sturdy</t>
+  </si>
+  <si>
+    <t>Reflect</t>
+  </si>
+  <si>
+    <t>坚固</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>反射</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据层数减少受到的伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害时，根据层数反弹伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthElementBottle</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicEarthPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth Element Bottle</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Earth Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>土元素瓶</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础大地药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Focus</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Focus_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Focus</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果上一次行动后未受到伤害则触发。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Focus_Desc</t>
+  </si>
+  <si>
+    <t>[Card_Focus]：抓{0}张牌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]: Draw {0} cards.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth Core Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>地核药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthCorePotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Unstable]：失去{0}点生命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreaterEarthPotion</t>
+  </si>
+  <si>
+    <t>Greater Earth Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等大地药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>VitalityPotion</t>
+  </si>
+  <si>
+    <t>Vitality Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>健体药剂</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>IronbonePotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ironbone Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁骨药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShacklePotion</t>
+  </si>
+  <si>
+    <t>Shackle Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>束缚药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>有层数时，敌人无法攻击（上限为1）</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>When there are stacks (maxmium 1) , cannot attack.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduces incoming damage based on stacks.</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reflects damage equal to stacks when hit.</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggers if you took no damage since your last action.</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reflection Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>反射药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Damage_Focus_Desc</t>
+  </si>
+  <si>
+    <t>[Card_Peace]：造成{0}点伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]：造成{0}点伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Peace]: Deal {0} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]: Deal {0} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Cooldown]: Deal {0} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReflectionPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>StoneskinPotion</t>
+  </si>
+  <si>
+    <t>Stoneskin Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>石肤药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Shop_NextExp</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一场实验：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Next experienment: </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Tailwind</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Tailwind_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>乘风</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tailwind</t>
+  </si>
+  <si>
+    <t>Tip_Card_Windborne</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Windborne_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺风</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windborne</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Damage_Windborne_Desc</t>
+  </si>
+  <si>
+    <t>[Card_Windborne]: Deal {0} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：造成{0}点伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>FocusPotion</t>
+  </si>
+  <si>
+    <t>集中药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Focus Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpikePotion</t>
+  </si>
+  <si>
+    <t>Spike Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>地刺药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy_Self_Focus_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Self_Focus_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>EarthPowerPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>CrustPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfEarth</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth Power Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crust Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breath of Earth</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>地能药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>地壳药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>息壤</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreathOfTheWild</t>
+  </si>
+  <si>
+    <t>Breath of the wild</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>荒野之息</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoarOfTheEarth</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Roar of the Earth</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>土石咆哮</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff] Calm</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]Sturdy</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Intro_Buff]Reflect</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔥</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💦</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deal {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>damage.</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>造成{0}点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>伤害</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Windborne_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Elemental_Air_Windborne_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Catalyze_Windborne_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Heal_Windborne_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：抓{0}张牌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[Card_Windborne]：增加{0}个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Catalyze]{0}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]: Draw {0} cards.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Add {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Card_Windborne]: Add {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Catalyze] {0}.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore {0} HP.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Windborne]: Restore {0} HP.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirElementBottle</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicAirPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>TailwindPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air Element Bottle</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Air Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tailwind Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>气元素瓶</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础气流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>气流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Airbender</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character_Airbender_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Airbender</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>💨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>驭气者</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
+初始手牌数：4
+初始手牌上限：5
+元素槽容量：8</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>能驾驭气流，掌控天空。善于使用连续且优雅的招式。
+初始手牌数：5
+初始手牌上限：5
+元素槽容量：3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Master of wind, casting in flowing, unbroken sequences.
+Initial hand size: 5
+maximum hand size: 5
+Element meter capacity: 3</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Use_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Player_Use</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用药剂指消耗元素使用其效果，精炼药剂不属于使用。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consuming elements to utilize its effect; refining a potion isn't regarded as using.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>上一个行动是[Player_Use]药剂时触发。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggers when the last move is [Player_Use] a potion.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>你使用或精炼过的药剂会暂时进入这里。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>The potions you [Player_Use] or refine will temporarily go here.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启后，可以使用鼠标左键[Player_Use]卡牌，鼠标右键精炼卡牌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>连续[Player_Use]卡牌会积累顺风，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>精炼或抽牌后顺风归零。</t>
+    </r>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain tailwind by [Player_Use] cards consecutively. Refining or drawing resets tailwind.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledFissure</t>
+  </si>
+  <si>
+    <t>Bottled Fissure</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BottledSandstorm</t>
+  </si>
+  <si>
+    <t>Bottled Sandstorm</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装沙暴</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bedrock</t>
+  </si>
+  <si>
+    <t>基岩</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScorchingSandsPotion</t>
+  </si>
+  <si>
+    <t>Scorching Sands</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>热砂药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>你每次[Player_Use]药剂时，会受到{buffStack}点伤害。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whenever you [Player_Use] a potion, you take {buffStack} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装涡旋</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreezePotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrongWindPotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breeze Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong Wind Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>和风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>强风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶装裂隙</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>GustPotion</t>
+  </si>
+  <si>
+    <t>Gust Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>TornadoPotion</t>
+  </si>
+  <si>
+    <t>Tornado Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙卷药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>The way to obtain elements is by refining your potions, and then you can obtain a corresponding element.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreaterAirPotion</t>
+  </si>
+  <si>
+    <t>Greater Air Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>高等气流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConvectionPotion</t>
+  </si>
+  <si>
+    <t>Convection Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>对流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>SevereConvectionPotion</t>
+  </si>
+  <si>
+    <t>Severe Convection</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>强对流药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>HurricanePotion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hurricane Potion</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>飓风药剂</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Aftermath</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tip_Card_Aftermath_Desc</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>余响</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅在被转化时触发。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aftermath</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triggers when being transmuted.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]: Deal {0} damage.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Aftermath_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Heal_Aftermath_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Damage_Aftermath_Desc</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]：造成{0}点伤害</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]：抓{0}张牌</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]: Restore {0} HP.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Card_Aftermath]: Draw {0} cards.</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>FairyWind</t>
+  </si>
+  <si>
+    <t>Fairy Wind</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>妖精之风</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reactive Gas</t>
+  </si>
+  <si>
+    <t>ReactiveGas</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>活性气体</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">元素组合的不同将会让你扮演不同的"角色"。在实验成功的奖励和精华商店中，你只会获得所选择元素的药剂。
 当前版本可用组合： 
 </t>
@@ -3868,1236 +5102,6 @@
       </rPr>
       <t>🔥💦</t>
     </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>⛰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Earth </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Watcher</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scientists believe that alchemy requires a calmer mind and scientific guidance. They found some potions from somewhere that seemed to be out of this era and might be useful.
-Initial hand size: 4
-maximum hand size: 5
-Element meter capacity: 10</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>A watcher as immovable as a mountain. The soul comes from the earth and will return to the earth.
-Initial hand size: 5
-maximum hand size: 5
-Element meter capacity: 6</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>不动如山的守望者。灵魂来自大地，也将归于大地。
-初始手牌数：5
-初始手牌上限：5
-元素槽容量：6</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Calm]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Calm].</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Stun].</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Intro_Buff]冷静</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Intro_Buff]坚固</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次行动受到{buffStack}伤害。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到伤害时，将其减少{buffStack}，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Intro_Buff]反射</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到伤害时，对敌方造成{buffStack}伤害，然后层数减半（向下取整）。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Sturdy</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Sturdy_Desc</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Reflect</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Reflect_Desc</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sturdy</t>
-  </si>
-  <si>
-    <t>Reflect</t>
-  </si>
-  <si>
-    <t>坚固</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>反射</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据层数减少受到的伤害</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到伤害时，根据层数反弹伤害</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Stun]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;施加&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthElementBottle</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicEarthPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earth Element Bottle</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Earth Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earth Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>土元素瓶</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础大地药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>大地药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Focus</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Focus_Desc</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>集中</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Focus</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果上一次行动后未受到伤害则触发。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Draw_Focus_Desc</t>
-  </si>
-  <si>
-    <t>[Card_Focus]：抓{0}张牌</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]: Draw {0} cards.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earth Core Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>地核药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthCorePotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Unstable]：失去{0}点生命</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;Add&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreaterEarthPotion</t>
-  </si>
-  <si>
-    <t>Greater Earth Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等大地药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>VitalityPotion</t>
-  </si>
-  <si>
-    <t>Vitality Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>健体药剂</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>IronbonePotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ironbone Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>铁骨药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShacklePotion</t>
-  </si>
-  <si>
-    <t>Shackle Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>束缚药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>有层数时，敌人无法攻击（上限为1）</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>When there are stacks, cards with [Card_Unstable] will 100% trigger.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>When there are stacks (maxmium 1) , cannot attack.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reduces incoming damage based on stacks.</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reflects damage equal to stacks when hit.</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Triggers if you took no damage since your last action.</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reflection Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>反射药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Damage_Focus_Desc</t>
-  </si>
-  <si>
-    <t>[Card_Peace]：造成{0}点伤害</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]：造成{0}点伤害</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Peace]: Deal {0} damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]: Deal {0} damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Cooldown]: Deal {0} damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReflectionPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>StoneskinPotion</t>
-  </si>
-  <si>
-    <t>Stoneskin Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>石肤药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_Shop_NextExp</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一场实验：</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Next experienment: </t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Tailwind</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Tailwind_Desc</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>乘风</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tailwind</t>
-  </si>
-  <si>
-    <t>Tip_Card_Windborne</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Windborne_Desc</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>顺风</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Windborne</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>For example, if you refine this &lt;color=#E80011&gt;&lt;b&gt;Basic Fire Potion&lt;/color&gt;&lt;/b&gt;, you will get a &lt;color=#E80011&gt;&lt;b&gt;fire element&lt;/color&gt;&lt;/b&gt;.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Damage_Windborne_Desc</t>
-  </si>
-  <si>
-    <t>[Card_Windborne]: Deal {0} damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]：造成{0}点伤害</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>FocusPotion</t>
-  </si>
-  <si>
-    <t>集中药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Focus Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpikePotion</t>
-  </si>
-  <si>
-    <t>Spike Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>地刺药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Sturdy]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]：&lt;b&gt;获得&lt;/b&gt;{0}[Card_Reflect]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Sturdy]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;Gain&lt;/b&gt; {0} [Card_Burn].</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Focus]: &lt;b&gt;Gain&lt;/b&gt; {0} [Card_Reflect]</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarthPowerPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>CrustPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreathOfEarth</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earth Power Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crust Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Breath of Earth</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>地能药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>地壳药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>息壤</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreathOfTheWild</t>
-  </si>
-  <si>
-    <t>Breath of the wild</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>荒野之息</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoarOfTheEarth</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Roar of the Earth</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>土石咆哮</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>When damaged, reduce by {buffStack}, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>When damaged, deal {buffStack} damage, then halve the number of stacks(rounded down).</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Intro_Buff] Calm</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Intro_Buff]Sturdy</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Intro_Buff]Reflect</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔥</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💦</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Deal {0} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>💥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>damage.</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>造成{0}点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>💥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>伤害</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Draw_Windborne_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Elemental_Air_Windborne_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Catalyze_Windborne_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Heal_Windborne_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]：抓{0}张牌</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[Card_Windborne]：增加{0}个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]：[Card_Catalyze]{0}</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]: Draw {0} cards.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Add {0} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[Card_Windborne]: Add {0} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="3"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]: [Card_Catalyze] {0}.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Restore {0} HP.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Windborne]: Restore {0} HP.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>AirElementBottle</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicAirPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>AirPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>TailwindPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Air Element Bottle</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Air Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Air Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tailwind Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>气元素瓶</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础气流药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>气流药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>顺风药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character_Airbender</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character_Airbender_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Airbender</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>💨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>驭气者</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>科学家们相信炼金需要更冷静的头脑，也需要科学的引导。他们从某个地方发现了一些似乎不属于这个时代的药水，或许可以派上用场。
-初始手牌数：4
-初始手牌上限：5
-元素槽容量：8</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>能驾驭气流，掌控天空。善于使用连续且优雅的招式。
-初始手牌数：5
-初始手牌上限：5
-元素槽容量：3</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Master of wind, casting in flowing, unbroken sequences.
-Initial hand size: 5
-maximum hand size: 5
-Element meter capacity: 3</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Player_Use_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Player_Use</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用药剂指消耗元素使用其效果，精炼药剂不属于使用。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consuming elements to utilize its effect; refining a potion isn't regarded as using.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>上一个行动是[Player_Use]药剂时触发。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Triggers when the last move is [Player_Use] a potion.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>你使用或精炼过的药剂会暂时进入这里。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>The potions you [Player_Use] or refine will temporarily go here.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>开启后，可以使用鼠标左键[Player_Use]卡牌，鼠标右键精炼卡牌</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>连续[Player_Use]卡牌会积累顺风，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>精炼或抽牌后顺风归零。</t>
-    </r>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gain tailwind by [Player_Use] cards consecutively. Refining or drawing resets tailwind.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledFissure</t>
-  </si>
-  <si>
-    <t>Bottled Fissure</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BottledSandstorm</t>
-  </si>
-  <si>
-    <t>Bottled Sandstorm</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓶装沙暴</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bedrock</t>
-  </si>
-  <si>
-    <t>基岩</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScorchingSandsPotion</t>
-  </si>
-  <si>
-    <t>Scorching Sands</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>热砂药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>你每次[Player_Use]药剂时，会受到{buffStack}点伤害。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Whenever you [Player_Use] a potion, you take {buffStack} damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#844A4A&gt;&lt;b&gt;锈蚀之器：&lt;/color&gt;&lt;/b&gt;你每次&lt;color=#1A5A54&gt;&lt;b&gt;使用卡牌&lt;/color&gt;&lt;/b&gt;时，会受到5点伤害。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#844A4A&gt;&lt;b&gt;Rusted Vessel:&lt;/color&gt;&lt;/b&gt; Each time you &lt;color=#1A5A54&gt;&lt;b&gt;use a potion&lt;/color&gt;&lt;/b&gt;, you will take 5 damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓶装涡旋</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreezePotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>StrongWindPotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Breeze Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strong Wind Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>和风药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>强风药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓶装裂隙</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>GustPotion</t>
-  </si>
-  <si>
-    <t>Gust Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>阵风药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>TornadoPotion</t>
-  </si>
-  <si>
-    <t>Tornado Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>龙卷药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>The way to obtain elements is by refining your potions, and then you can obtain a corresponding element.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreaterAirPotion</t>
-  </si>
-  <si>
-    <t>Greater Air Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>高等气流药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConvectionPotion</t>
-  </si>
-  <si>
-    <t>Convection Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>对流药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>SevereConvectionPotion</t>
-  </si>
-  <si>
-    <t>Severe Convection</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>强对流药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>HurricanePotion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hurricane Potion</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>飓风药剂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Aftermath</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tip_Card_Aftermath_Desc</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>余响</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅在被转化时触发。</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aftermath</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Triggers when being transmuted.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Aftermath]: Deal {0} damage.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Draw_Aftermath_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Heal_Aftermath_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect_Damage_Aftermath_Desc</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Aftermath]：造成{0}点伤害</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Aftermath]：抓{0}张牌</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Aftermath]：&lt;b&gt;获得&lt;/b&gt;{0}点生命</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Aftermath]: Restore {0} HP.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>[Card_Aftermath]: Draw {0} cards.</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>FairyWind</t>
-  </si>
-  <si>
-    <t>Fairy Wind</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>妖精之风</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -5454,7 +5458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5550,6 +5554,9 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6194,24 +6201,24 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="44" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="44" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6384,10 +6391,10 @@
         <v>866</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6428,7 +6435,7 @@
         <v>876</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C48" t="s">
         <v>328</v>
@@ -6480,148 +6487,148 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="30" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G53" s="30"/>
       <c r="H53" s="30"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="30" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G54" s="30"/>
       <c r="H54" s="30"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="30" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="30" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C56" s="34" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G56" s="30"/>
       <c r="H56" s="30"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="30" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G57" s="30"/>
       <c r="H57" s="30"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="30" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C58" s="34" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="36" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C59" s="36" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="30"/>
     </row>
     <row r="60" spans="1:8" ht="27.6">
       <c r="A60" s="36" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G60" s="30"/>
       <c r="H60" s="30"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="36" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C61" s="36" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="36" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B62" s="44" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="58" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B63" s="58" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="58" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B64" s="58" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -6802,7 +6809,7 @@
         <v>929</v>
       </c>
       <c r="C84" s="44" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -6843,10 +6850,10 @@
         <v>939</v>
       </c>
       <c r="B89" s="44" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C89" s="44" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7650,13 +7657,13 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="34" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C42" s="34" t="s">
         <v>1125</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -8191,7 +8198,7 @@
         <v>242</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8350,350 +8357,356 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="33" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="33" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="33" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B71" s="33" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C71" s="33" t="s">
         <v>1088</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="8" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>1098</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>1099</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="35" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B74" s="35" t="s">
         <v>1101</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="C74" s="35" t="s">
         <v>1102</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B75" s="35" t="s">
         <v>1104</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="C75" s="35" t="s">
         <v>1105</v>
-      </c>
-      <c r="C75" s="35" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="35" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B76" s="35" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C76" s="35" t="s">
         <v>1113</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B77" s="35" t="s">
         <v>1122</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>1123</v>
-      </c>
-      <c r="C77" s="35" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="8" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B78" s="38" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C78" s="38" t="s">
         <v>1140</v>
-      </c>
-      <c r="B78" s="38" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C78" s="38" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B79" s="38" t="s">
         <v>1143</v>
       </c>
-      <c r="B79" s="38" t="s">
+      <c r="C79" s="38" t="s">
         <v>1144</v>
-      </c>
-      <c r="C79" s="38" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="38" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="38" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="39" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="9" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>1095</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="C84" s="9" t="s">
         <v>1096</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B85" s="40" t="s">
         <v>1162</v>
       </c>
-      <c r="B85" s="40" t="s">
+      <c r="C85" s="40" t="s">
         <v>1163</v>
-      </c>
-      <c r="C85" s="40" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="40" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B86" s="40" t="s">
         <v>1165</v>
       </c>
-      <c r="B86" s="40" t="s">
+      <c r="C86" s="40" t="s">
         <v>1166</v>
-      </c>
-      <c r="C86" s="40" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B87" s="46" t="s">
         <v>1227</v>
       </c>
-      <c r="B87" s="46" t="s">
-        <v>1228</v>
-      </c>
       <c r="C87" s="50" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B88" s="46" t="s">
         <v>1229</v>
       </c>
-      <c r="B88" s="46" t="s">
+      <c r="C88" s="46" t="s">
         <v>1230</v>
-      </c>
-      <c r="C88" s="46" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B89" s="46" t="s">
         <v>1234</v>
       </c>
-      <c r="B89" s="46" t="s">
+      <c r="C89" s="46" t="s">
         <v>1235</v>
-      </c>
-      <c r="C89" s="46" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C90" s="46" t="s">
         <v>1232</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C90" s="46" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="33" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="33" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="33" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="33" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C95" s="33" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="49" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B97" s="49" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C97" s="39" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="39" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B98" s="39" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C98" s="49" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B99" s="51" t="s">
         <v>1249</v>
       </c>
-      <c r="B99" s="51" t="s">
+      <c r="C99" s="51" t="s">
         <v>1250</v>
-      </c>
-      <c r="C99" s="51" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="35" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B100" s="51" t="s">
         <v>1252</v>
       </c>
-      <c r="B100" s="51" t="s">
+      <c r="C100" s="51" t="s">
         <v>1253</v>
-      </c>
-      <c r="C100" s="51" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="39" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B101" s="57" t="s">
         <v>1265</v>
       </c>
-      <c r="B101" s="57" t="s">
+      <c r="C101" s="57" t="s">
         <v>1266</v>
-      </c>
-      <c r="C101" s="57" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B102" s="57" t="s">
         <v>1259</v>
       </c>
-      <c r="B102" s="57" t="s">
+      <c r="C102" s="57" t="s">
         <v>1260</v>
       </c>
-      <c r="C102" s="57" t="s">
-        <v>1261</v>
-      </c>
       <c r="D102" s="24"/>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="8"/>
-      <c r="B103" s="38"/>
-      <c r="C103" s="38"/>
+      <c r="A103" s="39" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B103" s="38" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C103" s="39" t="s">
+        <v>1287</v>
+      </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="38"/>
@@ -8712,35 +8725,35 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="9" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B108" s="56" t="s">
         <v>1256</v>
       </c>
-      <c r="B108" s="56" t="s">
+      <c r="C108" s="56" t="s">
         <v>1257</v>
-      </c>
-      <c r="C108" s="56" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="9" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B109" s="56" t="s">
         <v>1262</v>
       </c>
-      <c r="B109" s="56" t="s">
+      <c r="C109" s="56" t="s">
         <v>1263</v>
-      </c>
-      <c r="C109" s="56" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="40" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B110" s="56" t="s">
         <v>1283</v>
       </c>
-      <c r="B110" s="56" t="s">
+      <c r="C110" s="56" t="s">
         <v>1284</v>
-      </c>
-      <c r="C110" s="56" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -8830,8 +8843,8 @@
       <c r="B5" s="32" t="s">
         <v>1037</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>1038</v>
+      <c r="C5" s="59" t="s">
+        <v>1288</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8917,10 +8930,10 @@
         <v>308</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.8">
@@ -8928,7 +8941,7 @@
         <v>1033</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C14" s="30" t="s">
         <v>1036</v>
@@ -8939,32 +8952,32 @@
         <v>1034</v>
       </c>
       <c r="B15" s="45" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>1041</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="24" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B16" s="43" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C16" s="44" t="s">
         <v>1209</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="124.2">
       <c r="A17" s="24" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
   </sheetData>
@@ -9013,7 +9026,7 @@
         <v>312</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9065,10 +9078,10 @@
         <v>325</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -9087,10 +9100,10 @@
         <v>984</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9098,32 +9111,32 @@
         <v>985</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="24" customFormat="1" ht="14.4" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="24" customFormat="1">
       <c r="A13" s="24" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -9142,10 +9155,10 @@
         <v>332</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.9" customHeight="1">
@@ -9356,10 +9369,10 @@
         <v>379</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -9570,7 +9583,7 @@
         <v>427</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>428</v>
@@ -9603,7 +9616,7 @@
         <v>435</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>436</v>
@@ -10462,10 +10475,10 @@
         <v>648</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>1175</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -10484,10 +10497,10 @@
         <v>652</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -10539,10 +10552,10 @@
         <v>665</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.8">
@@ -10553,7 +10566,7 @@
         <v>667</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.8">
@@ -10564,7 +10577,7 @@
         <v>669</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.8">
@@ -10583,10 +10596,10 @@
         <v>673</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -10605,7 +10618,7 @@
         <v>677</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C15" t="s">
         <v>678</v>
@@ -10660,10 +10673,10 @@
         <v>753</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -10682,45 +10695,45 @@
         <v>757</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E23" s="30"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E24" s="30"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -10863,7 +10876,7 @@
         <v>719</v>
       </c>
       <c r="C40" s="34" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -10893,7 +10906,7 @@
         <v>726</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C43" t="s">
         <v>727</v>
@@ -10937,10 +10950,10 @@
         <v>737</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -10978,134 +10991,134 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C51" s="24" t="s">
         <v>1085</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="34" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="34" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="34" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="37" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B56" s="24" t="s">
         <v>1137</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="C56" s="24" t="s">
         <v>1138</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="37" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16.8">
       <c r="A58" s="37" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="37" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="37" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="37" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B62" s="24" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C62" s="24" t="s">
         <v>1277</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="37" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="37" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
   </sheetData>
